--- a/公司项目/认知作战/文档/软件概要设计-模块功能拆分.xlsx
+++ b/公司项目/认知作战/文档/软件概要设计-模块功能拆分.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="32400" windowHeight="18375" activeTab="1"/>
+    <workbookView windowWidth="28800" windowHeight="12420" firstSheet="2" activeTab="5"/>
   </bookViews>
   <sheets>
     <sheet name="模块清单总览" sheetId="1" r:id="rId1"/>
@@ -3220,7 +3220,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="36">
+  <fills count="37">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -3242,6 +3242,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFE2EFDA"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -3577,7 +3583,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="2">
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="2">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
@@ -3601,16 +3607,16 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="5">
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="5">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="6">
+    <xf numFmtId="0" fontId="13" fillId="8" borderId="6">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="7" borderId="5">
+    <xf numFmtId="0" fontId="14" fillId="8" borderId="5">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="8" borderId="7">
+    <xf numFmtId="0" fontId="15" fillId="9" borderId="7">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="8">
@@ -3619,89 +3625,89 @@
     <xf numFmtId="0" fontId="17" fillId="0" borderId="9">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0">
+    <xf numFmtId="0" fontId="18" fillId="10" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0">
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0">
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="12" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="13" borderId="0">
+    <xf numFmtId="0" fontId="21" fillId="13" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="14" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="15" borderId="0">
+    <xf numFmtId="0" fontId="22" fillId="15" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="16" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="17" borderId="0">
+    <xf numFmtId="0" fontId="21" fillId="17" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="18" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="0">
+    <xf numFmtId="0" fontId="22" fillId="19" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="20" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="21" borderId="0">
+    <xf numFmtId="0" fontId="21" fillId="21" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="22" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="23" borderId="0">
+    <xf numFmtId="0" fontId="22" fillId="23" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="24" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="25" borderId="0">
+    <xf numFmtId="0" fontId="21" fillId="25" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="26" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="27" borderId="0">
+    <xf numFmtId="0" fontId="22" fillId="27" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="28" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="29" borderId="0">
+    <xf numFmtId="0" fontId="21" fillId="29" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="30" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="31" borderId="0">
+    <xf numFmtId="0" fontId="22" fillId="31" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="32" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="33" borderId="0">
+    <xf numFmtId="0" fontId="21" fillId="33" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="34" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="35" borderId="0">
+    <xf numFmtId="0" fontId="22" fillId="35" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="36" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -3719,6 +3725,9 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -9848,7 +9857,7 @@
       <c r="A19" s="6" t="s">
         <v>205</v>
       </c>
-      <c r="B19" s="6" t="s">
+      <c r="B19" s="7" t="s">
         <v>923</v>
       </c>
       <c r="C19" s="6" t="s">
@@ -9874,7 +9883,7 @@
       <c r="A20" s="6" t="s">
         <v>205</v>
       </c>
-      <c r="B20" s="6" t="s">
+      <c r="B20" s="7" t="s">
         <v>928</v>
       </c>
       <c r="C20" s="6" t="s">
@@ -9900,7 +9909,7 @@
       <c r="A21" s="6" t="s">
         <v>205</v>
       </c>
-      <c r="B21" s="6" t="s">
+      <c r="B21" s="7" t="s">
         <v>932</v>
       </c>
       <c r="C21" s="6" t="s">
@@ -9926,7 +9935,7 @@
       <c r="A22" s="6" t="s">
         <v>205</v>
       </c>
-      <c r="B22" s="6" t="s">
+      <c r="B22" s="7" t="s">
         <v>936</v>
       </c>
       <c r="C22" s="6" t="s">
@@ -9952,7 +9961,7 @@
       <c r="A23" s="6" t="s">
         <v>205</v>
       </c>
-      <c r="B23" s="6" t="s">
+      <c r="B23" s="7" t="s">
         <v>940</v>
       </c>
       <c r="C23" s="6" t="s">

--- a/公司项目/认知作战/文档/软件概要设计-模块功能拆分.xlsx
+++ b/公司项目/认知作战/文档/软件概要设计-模块功能拆分.xlsx
@@ -23,7 +23,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="23">
+  <fonts count="24">
     <font>
       <name val="宋体"/>
       <charset val="134"/>
@@ -195,6 +195,9 @@
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
     </font>
   </fonts>
   <fills count="37">
@@ -415,7 +418,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="10">
+  <borders count="11">
     <border>
       <left/>
       <right/>
@@ -535,6 +538,20 @@
         <color theme="4"/>
       </bottom>
       <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00BFBFBF"/>
+      </left>
+      <right style="thin">
+        <color rgb="00BFBFBF"/>
+      </right>
+      <top style="thin">
+        <color rgb="00BFBFBF"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00BFBFBF"/>
+      </bottom>
     </border>
   </borders>
   <cellStyleXfs count="49">
@@ -684,7 +701,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -705,6 +722,9 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -7453,7 +7473,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H25"/>
+  <dimension ref="A1:H28"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="18"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -8336,7 +8356,7 @@
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>F-SWM-06-01 有效性评测(线上MC作业效果统计)；F-SWM-06-02 稳定性与合规性评估(离线数据集benchmark评测)；F-SWM-06-03 迭代/淘汰决策与反馈闭环</t>
+          <t>F-SWM-06-01 有效性评测(线上MC作业效果统计)；F-SWM-06-02 评测数据集管理；F-SWM-06-03 批量跑题执行；F-SWM-06-04 答案对比与打分；F-SWM-06-05 评分汇总与报告；F-SWM-06-06 迭代/淘汰决策与反馈闭环</t>
         </is>
       </c>
       <c r="G22" s="5" t="inlineStr">
@@ -8346,7 +8366,7 @@
       </c>
       <c r="H22" s="5" t="inlineStr">
         <is>
-          <t>对应 R-SWM-004。06-01 为线上效果统计(触达/互动/完成率)、06-02 为离线数据集评测(标准题集+预期答案+对比打分)，一在线一离线互补评估智能体质量；决策与反馈(06-03)内聚不拆。</t>
+          <t>对应 R-SWM-004。06-01 为线上效果统计(触达/互动/完成率)；06-02~05 为离线数据集评测流程(录入题集→跑题→打分→汇总)，按流程环节拆4个功能；一在线一离线互补评估；06-06 综合双轨结论做决策与反馈。</t>
         </is>
       </c>
     </row>
@@ -8393,84 +8413,210 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="6" t="inlineStr">
-        <is>
-          <t>③功能</t>
-        </is>
-      </c>
-      <c r="B24" s="6" t="inlineStr">
+      <c r="A24" s="8" t="inlineStr">
+        <is>
+          <t>③功能</t>
+        </is>
+      </c>
+      <c r="B24" s="8" t="inlineStr">
         <is>
           <t>F-SWM-06-02</t>
         </is>
       </c>
-      <c r="C24" s="6" t="inlineStr">
-        <is>
-          <t>稳定性与合规性评估</t>
-        </is>
-      </c>
-      <c r="D24" s="6" t="inlineStr">
+      <c r="C24" s="8" t="inlineStr">
+        <is>
+          <t>评测数据集管理</t>
+        </is>
+      </c>
+      <c r="D24" s="8" t="inlineStr">
         <is>
           <t>R-SWM-004</t>
         </is>
       </c>
-      <c r="E24" s="6" t="inlineStr">
-        <is>
-          <t>基于标准评测数据集（人工编辑的测试题集，含问题+预期答案+评分维度）对智能体进行离线 benchmark 评测：批量跑题收集实际回答 → 对比预期答案打分 → 按稳定性/合规性/人设一致性维度汇总得分，评估智能体在受控测试集上的表现质量。</t>
-        </is>
-      </c>
-      <c r="F24" s="6" t="inlineStr">
-        <is>
-          <t>评测数据集录入与管理(问题/预期答案/评分维度)；批量执行评测(跑题,调用SWM定义+IRS推理收集回答)；答案对比与打分(人工评判/规则匹配/LLM-as-judge)；评分汇总与报告(稳定性/合规性/人设一致性得分)</t>
-        </is>
-      </c>
-      <c r="G24" s="6" t="inlineStr">
-        <is>
-          <t>SRS R-SWM-004；离线数据集评测</t>
-        </is>
-      </c>
-      <c r="H24" s="6" t="inlineStr">
-        <is>
-          <t>数据来自 R-MC-008</t>
+      <c r="E24" s="8" t="inlineStr">
+        <is>
+          <t>管理智能体评测用的标准数据集：提示词工程师编辑测试用例集，每条用例含问题、预期答案、评分标准（规则匹配/关键词/LLM裁判/人工评判）、权重与所属评分维度（稳定性/合规性/人设一致性）；支持数据集创建、用例录入/批量导入/修改/删除与版本管理。</t>
+        </is>
+      </c>
+      <c r="F24" s="8" t="inlineStr">
+        <is>
+          <t>数据集创建与元信息(适用人设/评分维度)；用例录入(问题/预期答案/评分标准/权重/维度)；批量导入；用例增删改查；数据集版本管理</t>
+        </is>
+      </c>
+      <c r="G24" s="8" t="inlineStr">
+        <is>
+          <t>SRS R-SWM-004</t>
+        </is>
+      </c>
+      <c r="H24" s="8" t="inlineStr">
+        <is>
+          <t>数据集是离线评测的可复现基准，固定题集可对不同版本反复评测对比演进</t>
         </is>
       </c>
     </row>
     <row r="25" ht="33" customHeight="1">
-      <c r="A25" s="6" t="inlineStr">
-        <is>
-          <t>③功能</t>
-        </is>
-      </c>
-      <c r="B25" s="6" t="inlineStr">
+      <c r="A25" s="8" t="inlineStr">
+        <is>
+          <t>③功能</t>
+        </is>
+      </c>
+      <c r="B25" s="8" t="inlineStr">
         <is>
           <t>F-SWM-06-03</t>
         </is>
       </c>
-      <c r="C25" s="6" t="inlineStr">
+      <c r="C25" s="8" t="inlineStr">
+        <is>
+          <t>批量跑题执行</t>
+        </is>
+      </c>
+      <c r="D25" s="8" t="inlineStr">
+        <is>
+          <t>R-SWM-004</t>
+        </is>
+      </c>
+      <c r="E25" s="8" t="inlineStr">
+        <is>
+          <t>对指定 agent_id 按数据集逐题执行评测：系统将每题问题连同智能体定义（提示词+人设+记忆）交由 IRS 本地大模型推理（不经执行网关），收集智能体的实际回答；支持异步批量执行、进度跟踪与失败重跑。</t>
+        </is>
+      </c>
+      <c r="F25" s="8" t="inlineStr">
+        <is>
+          <t>逐题调IRS推理收集实际回答；推理不经执行网关(CON-10)；异步批量执行；进度跟踪；失败题重跑</t>
+        </is>
+      </c>
+      <c r="G25" s="8" t="inlineStr">
+        <is>
+          <t>SRS R-SWM-004</t>
+        </is>
+      </c>
+      <c r="H25" s="8" t="inlineStr">
+        <is>
+          <t>对接 II-08/EI-06 本地推理</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="8" t="inlineStr">
+        <is>
+          <t>③功能</t>
+        </is>
+      </c>
+      <c r="B26" s="8" t="inlineStr">
+        <is>
+          <t>F-SWM-06-04</t>
+        </is>
+      </c>
+      <c r="C26" s="8" t="inlineStr">
+        <is>
+          <t>答案对比与打分</t>
+        </is>
+      </c>
+      <c r="D26" s="8" t="inlineStr">
+        <is>
+          <t>R-SWM-004</t>
+        </is>
+      </c>
+      <c r="E26" s="8" t="inlineStr">
+        <is>
+          <t>将跑题收集的实际回答与用例预期答案按评分标准对比打分，支持规则匹配、LLM裁判（LLM-as-judge）与人工评判三种模式，按用例逐题配置；LLM裁判置信度低时标记待人工评判。</t>
+        </is>
+      </c>
+      <c r="F26" s="8" t="inlineStr">
+        <is>
+          <t>规则匹配(精确/关键词)；LLM-as-judge(本地模型裁判)；人工评判；逐题配置评分模式；置信度低转人工</t>
+        </is>
+      </c>
+      <c r="G26" s="8" t="inlineStr">
+        <is>
+          <t>SRS R-SWM-004</t>
+        </is>
+      </c>
+      <c r="H26" s="8" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="8" t="inlineStr">
+        <is>
+          <t>③功能</t>
+        </is>
+      </c>
+      <c r="B27" s="8" t="inlineStr">
+        <is>
+          <t>F-SWM-06-05</t>
+        </is>
+      </c>
+      <c r="C27" s="8" t="inlineStr">
+        <is>
+          <t>评分汇总与报告</t>
+        </is>
+      </c>
+      <c r="D27" s="8" t="inlineStr">
+        <is>
+          <t>R-SWM-004</t>
+        </is>
+      </c>
+      <c r="E27" s="8" t="inlineStr">
+        <is>
+          <t>按评分维度（稳定性/合规性/人设一致性）汇总各维度得分、通过率、人设漂移维度，对比历史基线与上次同题集得分，输出评测报告；报告含质量等级、薄弱用例与改进建议。</t>
+        </is>
+      </c>
+      <c r="F27" s="8" t="inlineStr">
+        <is>
+          <t>维度得分汇总(稳定性/合规性/人设一致性)；通过率/人设漂移维度；历史基线对比；版本演进对比；评测报告输出</t>
+        </is>
+      </c>
+      <c r="G27" s="8" t="inlineStr">
+        <is>
+          <t>SRS R-SWM-004</t>
+        </is>
+      </c>
+      <c r="H27" s="8" t="inlineStr">
+        <is>
+          <t>供 F-SWM-06-06 决策消费</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="8" t="inlineStr">
+        <is>
+          <t>③功能</t>
+        </is>
+      </c>
+      <c r="B28" s="8" t="inlineStr">
+        <is>
+          <t>F-SWM-06-06</t>
+        </is>
+      </c>
+      <c r="C28" s="8" t="inlineStr">
         <is>
           <t>迭代/淘汰决策与反馈闭环</t>
         </is>
       </c>
-      <c r="D25" s="6" t="inlineStr">
+      <c r="D28" s="8" t="inlineStr">
         <is>
           <t>R-SWM-004</t>
         </is>
       </c>
-      <c r="E25" s="6" t="inlineStr">
-        <is>
-          <t>对低效定义提出淘汰、对高价值定义提出迭代优化；反馈至M-SWM-02(驱动模板迭代)与M-SWM-05(驱动定义重建)形成闭环。</t>
-        </is>
-      </c>
-      <c r="F25" s="6" t="inlineStr">
-        <is>
-          <t>淘汰/迭代决策；反馈构建侧形成闭环</t>
-        </is>
-      </c>
-      <c r="G25" s="6" t="inlineStr">
+      <c r="E28" s="8" t="inlineStr">
+        <is>
+          <t>综合 F-SWM-06-01 线上有效性统计与 F-SWM-06-05 离线数据集评测报告，对低效定义提出淘汰、对高价值定义提出迭代优化，形成评测决策；反馈至 M-SWM-02（驱动模板迭代）与 M-SWM-05（驱动定义重建）形成闭环。</t>
+        </is>
+      </c>
+      <c r="F28" s="8" t="inlineStr">
+        <is>
+          <t>综合线上+离线双轨结论；淘汰/迭代决策；反馈M-SWM-02模板迭代；反馈M-SWM-05定义重建；闭环</t>
+        </is>
+      </c>
+      <c r="G28" s="8" t="inlineStr">
         <is>
           <t>SRS R-SWM-004</t>
         </is>
       </c>
-      <c r="H25" s="6" t="inlineStr"/>
+      <c r="H28" s="8" t="inlineStr">
+        <is>
+          <t>原 F-SWM-06-03 顺延而来</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/公司项目/认知作战/文档/软件概要设计-模块功能拆分.xlsx
+++ b/公司项目/认知作战/文档/软件概要设计-模块功能拆分.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowWidth="28800" windowHeight="12420" tabRatio="600" firstSheet="2" activeTab="5" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowWidth="28800" windowHeight="12420" tabRatio="600" firstSheet="2" activeTab="7" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="模块清单总览" sheetId="1" state="visible" r:id="rId1"/>
@@ -23,7 +23,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="24">
+  <fonts count="26">
     <font>
       <name val="宋体"/>
       <charset val="134"/>
@@ -199,8 +199,17 @@
     <font>
       <sz val="10"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <sz val="10"/>
+    </font>
   </fonts>
-  <fills count="37">
+  <fills count="40">
     <fill>
       <patternFill/>
     </fill>
@@ -415,6 +424,21 @@
       <patternFill patternType="solid">
         <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00305496"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00DDEBF7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E2EFDA"/>
       </patternFill>
     </fill>
   </fills>
@@ -701,7 +725,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -725,6 +749,15 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="37" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="38" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="39" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -7474,7 +7507,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:H28"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="18"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
@@ -7487,926 +7520,926 @@
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="9" t="inlineStr">
         <is>
           <t>层级</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="9" t="inlineStr">
         <is>
           <t>编号</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" s="9" t="inlineStr">
         <is>
           <t>名称</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" s="9" t="inlineStr">
         <is>
           <t>对应需求</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" s="9" t="inlineStr">
         <is>
           <t>职责简述</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" s="9" t="inlineStr">
         <is>
           <t>关键能力点（功能）</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" s="9" t="inlineStr">
         <is>
           <t>来源依据</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" s="9" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="132" customHeight="1">
-      <c r="A2" s="2" t="inlineStr">
+    <row r="2">
+      <c r="A2" s="10" t="inlineStr">
         <is>
           <t>①子系统</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="B2" s="10" t="inlineStr">
         <is>
           <t>M-SWM-00</t>
         </is>
       </c>
-      <c r="C2" s="3" t="inlineStr">
+      <c r="C2" s="10" t="inlineStr">
         <is>
           <t>蜂群智能体子系统</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="D2" s="10" t="inlineStr">
         <is>
           <t>R-SWM-001~004</t>
         </is>
       </c>
-      <c r="E2" s="3" t="inlineStr">
+      <c r="E2" s="10" t="inlineStr">
         <is>
           <t>执行层的「智能体定义与记忆中心」：根据人设(画像/账号属性)编写驱动智能体作业的提示词与记忆，将智能体定义(人设标签/提示词/记忆/作业策略)以agent_id同步下发至MC持存；承担智能体构建、评测、提示词与人设管理、记忆管理；不直接操作设备。</t>
         </is>
       </c>
-      <c r="F2" s="3" t="inlineStr">
+      <c r="F2" s="10" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G2" s="3" t="inlineStr">
+      <c r="G2" s="10" t="inlineStr">
         <is>
           <t>SRS §引言/SWM</t>
         </is>
       </c>
-      <c r="H2" s="3" t="inlineStr">
+      <c r="H2" s="10" t="inlineStr">
         <is>
           <t>R-SWM-001(提示词与人设管理)含人设标签、提示词模板库、场景适配调用三个异构关注点(元数据/文本资产/运行时决策)，故拆3模块；智能体定义组装与同步下发归构建模块(M-SWM-05)，迭代优化决策归评测模块(M-SWM-06)。</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="49.5" customHeight="1">
-      <c r="A3" s="4" t="inlineStr">
+    <row r="3">
+      <c r="A3" s="11" t="inlineStr">
         <is>
           <t>②模块</t>
         </is>
       </c>
-      <c r="B3" s="4" t="inlineStr">
+      <c r="B3" s="11" t="inlineStr">
         <is>
           <t>M-SWM-01</t>
         </is>
       </c>
-      <c r="C3" s="5" t="inlineStr">
+      <c r="C3" s="11" t="inlineStr">
         <is>
           <t>人设标签管理（智能体人格定义中心）</t>
         </is>
       </c>
-      <c r="D3" s="4" t="inlineStr">
+      <c r="D3" s="11" t="inlineStr">
         <is>
           <t>R-SWM-001(人设)</t>
         </is>
       </c>
-      <c r="E3" s="5" t="inlineStr">
+      <c r="E3" s="11" t="inlineStr">
         <is>
           <t>为每个 agent_id 绑定人设标签(身份特征/立场倾向/语言风格/兴趣领域等画像属性)；人设挂 agent_id，经 agent_id↔account_id 1:1 绑定间接对应账号；不复制账号主数据。</t>
         </is>
       </c>
-      <c r="F3" s="5" t="inlineStr">
+      <c r="F3" s="11" t="inlineStr">
         <is>
           <t>F-SWM-01-01 人设标签绑定；F-SWM-01-02 人设标签体系维护</t>
         </is>
       </c>
-      <c r="G3" s="5" t="inlineStr">
+      <c r="G3" s="11" t="inlineStr">
         <is>
           <t>SRS R-SWM-001(人设)</t>
         </is>
       </c>
-      <c r="H3" s="5" t="inlineStr">
-        <is>
-          <t>R-SWM-001 的人设标签(元数据体系)与提示词(文本资产)、运行时选择是不同职责域，故拆。</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="33" customHeight="1">
-      <c r="A4" s="6" t="inlineStr">
-        <is>
-          <t>③功能</t>
-        </is>
-      </c>
-      <c r="B4" s="6" t="inlineStr">
+      <c r="H3" s="11" t="inlineStr">
+        <is>
+          <t>FR-SWM-001 的人设标签(元数据体系)与提示词(文本资产)、运行时选择是不同职责域，故拆。</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="8" t="inlineStr">
+        <is>
+          <t>③功能</t>
+        </is>
+      </c>
+      <c r="B4" s="8" t="inlineStr">
         <is>
           <t>F-SWM-01-01</t>
         </is>
       </c>
-      <c r="C4" s="6" t="inlineStr">
+      <c r="C4" s="8" t="inlineStr">
         <is>
           <t>人设标签绑定</t>
         </is>
       </c>
-      <c r="D4" s="6" t="inlineStr">
+      <c r="D4" s="8" t="inlineStr">
         <is>
           <t>R-SWM-001</t>
         </is>
       </c>
-      <c r="E4" s="6" t="inlineStr">
+      <c r="E4" s="8" t="inlineStr">
         <is>
           <t>为每个 agent_id 绑定人设标签，标签涵盖身份特征、立场倾向、语言风格、兴趣领域等画像属性。</t>
         </is>
       </c>
-      <c r="F4" s="6" t="inlineStr">
+      <c r="F4" s="8" t="inlineStr">
         <is>
           <t>人设绑agent_id；画像属性涵盖</t>
         </is>
       </c>
-      <c r="G4" s="6" t="inlineStr">
+      <c r="G4" s="8" t="inlineStr">
         <is>
           <t>SRS R-SWM-001</t>
         </is>
       </c>
-      <c r="H4" s="6" t="inlineStr"/>
+      <c r="H4" s="8" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="6" t="inlineStr">
-        <is>
-          <t>③功能</t>
-        </is>
-      </c>
-      <c r="B5" s="6" t="inlineStr">
+      <c r="A5" s="8" t="inlineStr">
+        <is>
+          <t>③功能</t>
+        </is>
+      </c>
+      <c r="B5" s="8" t="inlineStr">
         <is>
           <t>F-SWM-01-02</t>
         </is>
       </c>
-      <c r="C5" s="6" t="inlineStr">
+      <c r="C5" s="8" t="inlineStr">
         <is>
           <t>人设标签体系维护</t>
         </is>
       </c>
-      <c r="D5" s="6" t="inlineStr">
+      <c r="D5" s="8" t="inlineStr">
         <is>
           <t>R-SWM-001</t>
         </is>
       </c>
-      <c r="E5" s="6" t="inlineStr">
+      <c r="E5" s="8" t="inlineStr">
         <is>
           <t>维护人设标签体系定义；人设标签冲突时提示人工裁定。</t>
         </is>
       </c>
-      <c r="F5" s="6" t="inlineStr">
+      <c r="F5" s="8" t="inlineStr">
         <is>
           <t>标签体系维护；冲突人工裁定</t>
         </is>
       </c>
-      <c r="G5" s="6" t="inlineStr">
+      <c r="G5" s="8" t="inlineStr">
         <is>
           <t>SRS R-SWM-001</t>
         </is>
       </c>
-      <c r="H5" s="6" t="inlineStr"/>
-    </row>
-    <row r="6" ht="49.5" customHeight="1">
-      <c r="A6" s="4" t="inlineStr">
+      <c r="H5" s="8" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="11" t="inlineStr">
         <is>
           <t>②模块</t>
         </is>
       </c>
-      <c r="B6" s="4" t="inlineStr">
+      <c r="B6" s="11" t="inlineStr">
         <is>
           <t>M-SWM-02</t>
         </is>
       </c>
-      <c r="C6" s="5" t="inlineStr">
+      <c r="C6" s="11" t="inlineStr">
         <is>
           <t>提示词模板库与版本管理（提示词资产管理）</t>
         </is>
       </c>
-      <c r="D6" s="4" t="inlineStr">
+      <c r="D6" s="11" t="inlineStr">
         <is>
           <t>R-SWM-001(资产)</t>
         </is>
       </c>
-      <c r="E6" s="5" t="inlineStr">
+      <c r="E6" s="11" t="inlineStr">
         <is>
           <t>建立提示词模板库并按用途/平台/目标分类管理；对提示词进行版本管理，以 agent_id 为主键索引，支持版本对比/回滚/变更记录。</t>
         </is>
       </c>
-      <c r="F6" s="5" t="inlineStr">
+      <c r="F6" s="11" t="inlineStr">
         <is>
           <t>F-SWM-02-01 提示词模板库分类管理；F-SWM-02-02 提示词版本管理</t>
         </is>
       </c>
-      <c r="G6" s="5" t="inlineStr">
+      <c r="G6" s="11" t="inlineStr">
         <is>
           <t>SRS R-SWM-001(资产)</t>
         </is>
       </c>
-      <c r="H6" s="5" t="inlineStr">
-        <is>
-          <t>R-SWM-001 的提示词模板库(文本资产)是独立关注点；版本管理横切于人设与提示词。</t>
+      <c r="H6" s="11" t="inlineStr">
+        <is>
+          <t>FR-SWM-001 的提示词模板库(文本资产)是独立关注点；版本管理横切于人设与提示词。</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="6" t="inlineStr">
-        <is>
-          <t>③功能</t>
-        </is>
-      </c>
-      <c r="B7" s="6" t="inlineStr">
+      <c r="A7" s="8" t="inlineStr">
+        <is>
+          <t>③功能</t>
+        </is>
+      </c>
+      <c r="B7" s="8" t="inlineStr">
         <is>
           <t>F-SWM-02-01</t>
         </is>
       </c>
-      <c r="C7" s="6" t="inlineStr">
+      <c r="C7" s="8" t="inlineStr">
         <is>
           <t>提示词模板库分类管理</t>
         </is>
       </c>
-      <c r="D7" s="6" t="inlineStr">
+      <c r="D7" s="8" t="inlineStr">
         <is>
           <t>R-SWM-001</t>
         </is>
       </c>
-      <c r="E7" s="6" t="inlineStr">
+      <c r="E7" s="8" t="inlineStr">
         <is>
           <t>建立提示词模板库并按用途、平台、目标进行分类管理。</t>
         </is>
       </c>
-      <c r="F7" s="6" t="inlineStr">
+      <c r="F7" s="8" t="inlineStr">
         <is>
           <t>模板库；按用途/平台/目标分类</t>
         </is>
       </c>
-      <c r="G7" s="6" t="inlineStr">
+      <c r="G7" s="8" t="inlineStr">
         <is>
           <t>SRS R-SWM-001</t>
         </is>
       </c>
-      <c r="H7" s="6" t="inlineStr"/>
-    </row>
-    <row r="8" ht="33" customHeight="1">
-      <c r="A8" s="6" t="inlineStr">
-        <is>
-          <t>③功能</t>
-        </is>
-      </c>
-      <c r="B8" s="6" t="inlineStr">
+      <c r="H7" s="8" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="8" t="inlineStr">
+        <is>
+          <t>③功能</t>
+        </is>
+      </c>
+      <c r="B8" s="8" t="inlineStr">
         <is>
           <t>F-SWM-02-02</t>
         </is>
       </c>
-      <c r="C8" s="6" t="inlineStr">
+      <c r="C8" s="8" t="inlineStr">
         <is>
           <t>提示词版本管理</t>
         </is>
       </c>
-      <c r="D8" s="6" t="inlineStr">
+      <c r="D8" s="8" t="inlineStr">
         <is>
           <t>R-SWM-001</t>
         </is>
       </c>
-      <c r="E8" s="6" t="inlineStr">
+      <c r="E8" s="8" t="inlineStr">
         <is>
           <t>对提示词进行版本管理，以 agent_id 为主键索引，支持版本对比、回滚与变更记录；版本回滚失败时告警。</t>
         </is>
       </c>
-      <c r="F8" s="6" t="inlineStr">
+      <c r="F8" s="8" t="inlineStr">
         <is>
           <t>agent_id主键版本管理；对比/回滚/变更记录</t>
         </is>
       </c>
-      <c r="G8" s="6" t="inlineStr">
+      <c r="G8" s="8" t="inlineStr">
         <is>
           <t>SRS R-SWM-001</t>
         </is>
       </c>
-      <c r="H8" s="6" t="inlineStr"/>
-    </row>
-    <row r="9" ht="49.5" customHeight="1">
-      <c r="A9" s="4" t="inlineStr">
+      <c r="H8" s="8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="11" t="inlineStr">
         <is>
           <t>②模块</t>
         </is>
       </c>
-      <c r="B9" s="4" t="inlineStr">
+      <c r="B9" s="11" t="inlineStr">
         <is>
           <t>M-SWM-03</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
+      <c r="C9" s="11" t="inlineStr">
         <is>
           <t>提示词场景适配与动态调用（提示词运行时引擎）</t>
         </is>
       </c>
-      <c r="D9" s="4" t="inlineStr">
+      <c r="D9" s="11" t="inlineStr">
         <is>
           <t>R-SWM-001(运行时)</t>
         </is>
       </c>
-      <c r="E9" s="5" t="inlineStr">
+      <c r="E9" s="11" t="inlineStr">
         <is>
           <t>按作业场景(人设标签/目标受众/当前态势)适配提示词，作业时动态调用并填充生成最终作业指令。</t>
         </is>
       </c>
-      <c r="F9" s="5" t="inlineStr">
+      <c r="F9" s="11" t="inlineStr">
         <is>
           <t>F-SWM-03-01 场景适配；F-SWM-03-02 动态调用与指令生成</t>
         </is>
       </c>
-      <c r="G9" s="5" t="inlineStr">
+      <c r="G9" s="11" t="inlineStr">
         <is>
           <t>SRS R-SWM-001(运行时)</t>
         </is>
       </c>
-      <c r="H9" s="5" t="inlineStr">
-        <is>
-          <t>R-SWM-001 的场景适配与动态调用是运行时决策关注点，与模板库资产管理分离。</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="33" customHeight="1">
-      <c r="A10" s="6" t="inlineStr">
-        <is>
-          <t>③功能</t>
-        </is>
-      </c>
-      <c r="B10" s="6" t="inlineStr">
+      <c r="H9" s="11" t="inlineStr">
+        <is>
+          <t>FR-SWM-001 的场景适配与动态调用是运行时决策关注点，与模板库资产管理分离。</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="8" t="inlineStr">
+        <is>
+          <t>③功能</t>
+        </is>
+      </c>
+      <c r="B10" s="8" t="inlineStr">
         <is>
           <t>F-SWM-03-01</t>
         </is>
       </c>
-      <c r="C10" s="6" t="inlineStr">
+      <c r="C10" s="8" t="inlineStr">
         <is>
           <t>场景适配</t>
         </is>
       </c>
-      <c r="D10" s="6" t="inlineStr">
+      <c r="D10" s="8" t="inlineStr">
         <is>
           <t>R-SWM-001</t>
         </is>
       </c>
-      <c r="E10" s="6" t="inlineStr">
+      <c r="E10" s="8" t="inlineStr">
         <is>
           <t>按作业场景(人设标签/目标受众/当前态势)选择合适模板；模板填充失败时降级为默认模板。</t>
         </is>
       </c>
-      <c r="F10" s="6" t="inlineStr">
+      <c r="F10" s="8" t="inlineStr">
         <is>
           <t>场景适配模板；填充失败降级默认</t>
         </is>
       </c>
-      <c r="G10" s="6" t="inlineStr">
+      <c r="G10" s="8" t="inlineStr">
         <is>
           <t>SRS R-SWM-001</t>
         </is>
       </c>
-      <c r="H10" s="6" t="inlineStr"/>
+      <c r="H10" s="8" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="6" t="inlineStr">
-        <is>
-          <t>③功能</t>
-        </is>
-      </c>
-      <c r="B11" s="6" t="inlineStr">
+      <c r="A11" s="8" t="inlineStr">
+        <is>
+          <t>③功能</t>
+        </is>
+      </c>
+      <c r="B11" s="8" t="inlineStr">
         <is>
           <t>F-SWM-03-02</t>
         </is>
       </c>
-      <c r="C11" s="6" t="inlineStr">
+      <c r="C11" s="8" t="inlineStr">
         <is>
           <t>动态调用与指令生成</t>
         </is>
       </c>
-      <c r="D11" s="6" t="inlineStr">
+      <c r="D11" s="8" t="inlineStr">
         <is>
           <t>R-SWM-001</t>
         </is>
       </c>
-      <c r="E11" s="6" t="inlineStr">
+      <c r="E11" s="8" t="inlineStr">
         <is>
           <t>智能体作业时动态调用并填充提示词，生成最终作业指令。</t>
         </is>
       </c>
-      <c r="F11" s="6" t="inlineStr">
+      <c r="F11" s="8" t="inlineStr">
         <is>
           <t>动态调用填充；生成作业指令</t>
         </is>
       </c>
-      <c r="G11" s="6" t="inlineStr">
+      <c r="G11" s="8" t="inlineStr">
         <is>
           <t>SRS R-SWM-001</t>
         </is>
       </c>
-      <c r="H11" s="6" t="inlineStr">
+      <c r="H11" s="8" t="inlineStr">
         <is>
           <t>对接 II-09</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="49.5" customHeight="1">
-      <c r="A12" s="4" t="inlineStr">
+    <row r="12">
+      <c r="A12" s="11" t="inlineStr">
         <is>
           <t>②模块</t>
         </is>
       </c>
-      <c r="B12" s="4" t="inlineStr">
+      <c r="B12" s="11" t="inlineStr">
         <is>
           <t>M-SWM-04</t>
         </is>
       </c>
-      <c r="C12" s="5" t="inlineStr">
+      <c r="C12" s="11" t="inlineStr">
         <is>
           <t>蜂群记忆管理（智能体记忆中枢）</t>
         </is>
       </c>
-      <c r="D12" s="4" t="inlineStr">
+      <c r="D12" s="11" t="inlineStr">
         <is>
           <t>R-SWM-002</t>
         </is>
       </c>
-      <c r="E12" s="5" t="inlineStr">
+      <c r="E12" s="11" t="inlineStr">
         <is>
           <t>实现智能体作业记忆的存储、场景沉淀、历史复用与个性化状态延续，使智能体长期行为符合人设且不断演进。</t>
         </is>
       </c>
-      <c r="F12" s="5" t="inlineStr">
+      <c r="F12" s="11" t="inlineStr">
         <is>
           <t>F-SWM-04-01 作业记忆存储；F-SWM-04-02 场景记忆沉淀；F-SWM-04-03 历史记忆复用；F-SWM-04-04 个性化状态延续</t>
         </is>
       </c>
-      <c r="G12" s="5" t="inlineStr">
+      <c r="G12" s="11" t="inlineStr">
         <is>
           <t>SRS R-SWM-002</t>
         </is>
       </c>
-      <c r="H12" s="5" t="inlineStr">
+      <c r="H12" s="11" t="inlineStr">
         <is>
           <t>对应 R-SWM-002，记忆存储/沉淀/复用/延续是同一记忆对象的生命周期环节，内聚不拆。</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="33" customHeight="1">
-      <c r="A13" s="6" t="inlineStr">
-        <is>
-          <t>③功能</t>
-        </is>
-      </c>
-      <c r="B13" s="6" t="inlineStr">
+    <row r="13">
+      <c r="A13" s="8" t="inlineStr">
+        <is>
+          <t>③功能</t>
+        </is>
+      </c>
+      <c r="B13" s="8" t="inlineStr">
         <is>
           <t>F-SWM-04-01</t>
         </is>
       </c>
-      <c r="C13" s="6" t="inlineStr">
+      <c r="C13" s="8" t="inlineStr">
         <is>
           <t>作业记忆存储</t>
         </is>
       </c>
-      <c r="D13" s="6" t="inlineStr">
+      <c r="D13" s="8" t="inlineStr">
         <is>
           <t>R-SWM-002</t>
         </is>
       </c>
-      <c r="E13" s="6" t="inlineStr">
+      <c r="E13" s="8" t="inlineStr">
         <is>
           <t>对智能体作业过程中的关键信息(已完成任务/互动对象/立场表达等)进行记忆存储。</t>
         </is>
       </c>
-      <c r="F13" s="6" t="inlineStr">
+      <c r="F13" s="8" t="inlineStr">
         <is>
           <t>关键信息记忆存储</t>
         </is>
       </c>
-      <c r="G13" s="6" t="inlineStr">
+      <c r="G13" s="8" t="inlineStr">
         <is>
           <t>SRS R-SWM-002</t>
         </is>
       </c>
-      <c r="H13" s="6" t="inlineStr"/>
+      <c r="H13" s="8" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="6" t="inlineStr">
-        <is>
-          <t>③功能</t>
-        </is>
-      </c>
-      <c r="B14" s="6" t="inlineStr">
+      <c r="A14" s="8" t="inlineStr">
+        <is>
+          <t>③功能</t>
+        </is>
+      </c>
+      <c r="B14" s="8" t="inlineStr">
         <is>
           <t>F-SWM-04-02</t>
         </is>
       </c>
-      <c r="C14" s="6" t="inlineStr">
+      <c r="C14" s="8" t="inlineStr">
         <is>
           <t>场景记忆沉淀</t>
         </is>
       </c>
-      <c r="D14" s="6" t="inlineStr">
+      <c r="D14" s="8" t="inlineStr">
         <is>
           <t>R-SWM-002</t>
         </is>
       </c>
-      <c r="E14" s="6" t="inlineStr">
+      <c r="E14" s="8" t="inlineStr">
         <is>
           <t>将重复场景下的经验沉淀为场景记忆，形成可复用行为模式。</t>
         </is>
       </c>
-      <c r="F14" s="6" t="inlineStr">
+      <c r="F14" s="8" t="inlineStr">
         <is>
           <t>场景经验沉淀为模式</t>
         </is>
       </c>
-      <c r="G14" s="6" t="inlineStr">
+      <c r="G14" s="8" t="inlineStr">
         <is>
           <t>SRS R-SWM-002</t>
         </is>
       </c>
-      <c r="H14" s="6" t="inlineStr"/>
+      <c r="H14" s="8" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="6" t="inlineStr">
-        <is>
-          <t>③功能</t>
-        </is>
-      </c>
-      <c r="B15" s="6" t="inlineStr">
+      <c r="A15" s="8" t="inlineStr">
+        <is>
+          <t>③功能</t>
+        </is>
+      </c>
+      <c r="B15" s="8" t="inlineStr">
         <is>
           <t>F-SWM-04-03</t>
         </is>
       </c>
-      <c r="C15" s="6" t="inlineStr">
+      <c r="C15" s="8" t="inlineStr">
         <is>
           <t>历史记忆复用</t>
         </is>
       </c>
-      <c r="D15" s="6" t="inlineStr">
+      <c r="D15" s="8" t="inlineStr">
         <is>
           <t>R-SWM-002</t>
         </is>
       </c>
-      <c r="E15" s="6" t="inlineStr">
+      <c r="E15" s="8" t="inlineStr">
         <is>
           <t>在相似作业中复用历史记忆，提升作业连贯性与效率。</t>
         </is>
       </c>
-      <c r="F15" s="6" t="inlineStr">
+      <c r="F15" s="8" t="inlineStr">
         <is>
           <t>相似作业复用历史记忆</t>
         </is>
       </c>
-      <c r="G15" s="6" t="inlineStr">
+      <c r="G15" s="8" t="inlineStr">
         <is>
           <t>SRS R-SWM-002</t>
         </is>
       </c>
-      <c r="H15" s="6" t="inlineStr"/>
+      <c r="H15" s="8" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="6" t="inlineStr">
-        <is>
-          <t>③功能</t>
-        </is>
-      </c>
-      <c r="B16" s="6" t="inlineStr">
+      <c r="A16" s="8" t="inlineStr">
+        <is>
+          <t>③功能</t>
+        </is>
+      </c>
+      <c r="B16" s="8" t="inlineStr">
         <is>
           <t>F-SWM-04-04</t>
         </is>
       </c>
-      <c r="C16" s="6" t="inlineStr">
+      <c r="C16" s="8" t="inlineStr">
         <is>
           <t>个性化状态延续</t>
         </is>
       </c>
-      <c r="D16" s="6" t="inlineStr">
+      <c r="D16" s="8" t="inlineStr">
         <is>
           <t>R-SWM-002</t>
         </is>
       </c>
-      <c r="E16" s="6" t="inlineStr">
+      <c r="E16" s="8" t="inlineStr">
         <is>
           <t>基于记忆维持智能体个性化状态延续，使其长期行为符合人设且不断演进。</t>
         </is>
       </c>
-      <c r="F16" s="6" t="inlineStr">
+      <c r="F16" s="8" t="inlineStr">
         <is>
           <t>个性化状态延续；符合人设演进</t>
         </is>
       </c>
-      <c r="G16" s="6" t="inlineStr">
+      <c r="G16" s="8" t="inlineStr">
         <is>
           <t>SRS R-SWM-002</t>
         </is>
       </c>
-      <c r="H16" s="6" t="inlineStr"/>
-    </row>
-    <row r="17" ht="82.5" customHeight="1">
-      <c r="A17" s="4" t="inlineStr">
+      <c r="H16" s="8" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="11" t="inlineStr">
         <is>
           <t>②模块</t>
         </is>
       </c>
-      <c r="B17" s="4" t="inlineStr">
+      <c r="B17" s="11" t="inlineStr">
         <is>
           <t>M-SWM-05</t>
         </is>
       </c>
-      <c r="C17" s="5" t="inlineStr">
+      <c r="C17" s="11" t="inlineStr">
         <is>
           <t>智能体构建与定义下发（智能体装配工厂）</t>
         </is>
       </c>
-      <c r="D17" s="4" t="inlineStr">
+      <c r="D17" s="11" t="inlineStr">
         <is>
           <t>R-SWM-003</t>
         </is>
       </c>
-      <c r="E17" s="5" t="inlineStr">
+      <c r="E17" s="11" t="inlineStr">
         <is>
           <t>根据人设标签编写提示词与记忆初值、配置作业策略，组装为完整智能体定义并以 agent_id 为标识，经 II-15 同步至 MC 持存、供 OCC 作战编排引用。</t>
         </is>
       </c>
-      <c r="F17" s="5" t="inlineStr">
+      <c r="F17" s="11" t="inlineStr">
         <is>
           <t>F-SWM-05-01 智能体定义构建；F-SWM-05-02 账号绑定引用；F-SWM-05-03 同步至MC持存；F-SWM-05-04 OCC智能体节点定义来源</t>
         </is>
       </c>
-      <c r="G17" s="5" t="inlineStr">
+      <c r="G17" s="11" t="inlineStr">
         <is>
           <t>SRS R-SWM-003</t>
         </is>
       </c>
-      <c r="H17" s="5" t="inlineStr">
-        <is>
-          <t>对应 R-SWM-003，构建是装配链(编写初值+配置策略+组装+下发)，内聚不拆；吸收 R-SWM-001 中『组装与同步下发』能力作为定义交付出口。</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="33" customHeight="1">
-      <c r="A18" s="6" t="inlineStr">
-        <is>
-          <t>③功能</t>
-        </is>
-      </c>
-      <c r="B18" s="6" t="inlineStr">
+      <c r="H17" s="11" t="inlineStr">
+        <is>
+          <t>对应 R-SWM-003，构建是装配链(编写初值+配置策略+组装+下发)，内聚不拆；吸收 FR-SWM-001 中『组装与同步下发』能力作为定义交付出口。</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="8" t="inlineStr">
+        <is>
+          <t>③功能</t>
+        </is>
+      </c>
+      <c r="B18" s="8" t="inlineStr">
         <is>
           <t>F-SWM-05-01</t>
         </is>
       </c>
-      <c r="C18" s="6" t="inlineStr">
+      <c r="C18" s="8" t="inlineStr">
         <is>
           <t>智能体定义构建</t>
         </is>
       </c>
-      <c r="D18" s="6" t="inlineStr">
+      <c r="D18" s="8" t="inlineStr">
         <is>
           <t>R-SWM-003</t>
         </is>
       </c>
-      <c r="E18" s="6" t="inlineStr">
+      <c r="E18" s="8" t="inlineStr">
         <is>
           <t>按人设标签编写提示词初值与记忆初值并配置作业策略(目标/场景/边界)，组装为完整智能体定义，以全局唯一 agent_id 为标识。</t>
         </is>
       </c>
-      <c r="F18" s="6" t="inlineStr">
+      <c r="F18" s="8" t="inlineStr">
         <is>
           <t>人设+提示词初值+记忆初值+作业策略；agent_id标识</t>
         </is>
       </c>
-      <c r="G18" s="6" t="inlineStr">
+      <c r="G18" s="8" t="inlineStr">
         <is>
           <t>SRS R-SWM-003</t>
         </is>
       </c>
-      <c r="H18" s="6" t="inlineStr"/>
-    </row>
-    <row r="19" ht="33" customHeight="1">
-      <c r="A19" s="6" t="inlineStr">
-        <is>
-          <t>③功能</t>
-        </is>
-      </c>
-      <c r="B19" s="6" t="inlineStr">
+      <c r="H18" s="8" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="8" t="inlineStr">
+        <is>
+          <t>③功能</t>
+        </is>
+      </c>
+      <c r="B19" s="8" t="inlineStr">
         <is>
           <t>F-SWM-05-02</t>
         </is>
       </c>
-      <c r="C19" s="6" t="inlineStr">
+      <c r="C19" s="8" t="inlineStr">
         <is>
           <t>账号绑定引用</t>
         </is>
       </c>
-      <c r="D19" s="6" t="inlineStr">
+      <c r="D19" s="8" t="inlineStr">
         <is>
           <t>R-SWM-003</t>
         </is>
       </c>
-      <c r="E19" s="6" t="inlineStr">
+      <c r="E19" s="8" t="inlineStr">
         <is>
           <t>智能体定义与账号严格1:1绑定(agent_id↔account_id)，绑定关系由MC维护，本子系统构建时引用account_id。</t>
         </is>
       </c>
-      <c r="F19" s="6" t="inlineStr">
+      <c r="F19" s="8" t="inlineStr">
         <is>
           <t>agent_id↔account_id 1:1；构建时引用account_id</t>
         </is>
       </c>
-      <c r="G19" s="6" t="inlineStr">
+      <c r="G19" s="8" t="inlineStr">
         <is>
           <t>SRS R-SWM-003</t>
         </is>
       </c>
-      <c r="H19" s="6" t="inlineStr">
+      <c r="H19" s="8" t="inlineStr">
         <is>
           <t>绑定关系归 MC</t>
         </is>
       </c>
     </row>
-    <row r="20" ht="33" customHeight="1">
-      <c r="A20" s="6" t="inlineStr">
-        <is>
-          <t>③功能</t>
-        </is>
-      </c>
-      <c r="B20" s="6" t="inlineStr">
+    <row r="20">
+      <c r="A20" s="8" t="inlineStr">
+        <is>
+          <t>③功能</t>
+        </is>
+      </c>
+      <c r="B20" s="8" t="inlineStr">
         <is>
           <t>F-SWM-05-03</t>
         </is>
       </c>
-      <c r="C20" s="6" t="inlineStr">
+      <c r="C20" s="8" t="inlineStr">
         <is>
           <t>同步至MC持存</t>
         </is>
       </c>
-      <c r="D20" s="6" t="inlineStr">
+      <c r="D20" s="8" t="inlineStr">
         <is>
           <t>R-SWM-003</t>
         </is>
       </c>
-      <c r="E20" s="6" t="inlineStr">
+      <c r="E20" s="8" t="inlineStr">
         <is>
           <t>构建完成的智能体定义经II-15同步至MC持存，取得持存版本号；定义更新时以同一agent_id重新同步。</t>
         </is>
       </c>
-      <c r="F20" s="6" t="inlineStr">
+      <c r="F20" s="8" t="inlineStr">
         <is>
           <t>经II-15同步；取得版本号；更新重同步</t>
         </is>
       </c>
-      <c r="G20" s="6" t="inlineStr">
+      <c r="G20" s="8" t="inlineStr">
         <is>
           <t>SRS R-SWM-003</t>
         </is>
       </c>
-      <c r="H20" s="6" t="inlineStr">
+      <c r="H20" s="8" t="inlineStr">
         <is>
           <t>对接 II-15</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="6" t="inlineStr">
-        <is>
-          <t>③功能</t>
-        </is>
-      </c>
-      <c r="B21" s="6" t="inlineStr">
+      <c r="A21" s="8" t="inlineStr">
+        <is>
+          <t>③功能</t>
+        </is>
+      </c>
+      <c r="B21" s="8" t="inlineStr">
         <is>
           <t>F-SWM-05-04</t>
         </is>
       </c>
-      <c r="C21" s="6" t="inlineStr">
+      <c r="C21" s="8" t="inlineStr">
         <is>
           <t>OCC智能体节点定义来源</t>
         </is>
       </c>
-      <c r="D21" s="6" t="inlineStr">
+      <c r="D21" s="8" t="inlineStr">
         <is>
           <t>R-SWM-003</t>
         </is>
       </c>
-      <c r="E21" s="6" t="inlineStr">
+      <c r="E21" s="8" t="inlineStr">
         <is>
           <t>构建出的智能体定义是OCC作战编排中智能体节点的定义来源。</t>
         </is>
       </c>
-      <c r="F21" s="6" t="inlineStr">
+      <c r="F21" s="8" t="inlineStr">
         <is>
           <t>作为OCC编排智能体节点定义来源</t>
         </is>
       </c>
-      <c r="G21" s="6" t="inlineStr">
+      <c r="G21" s="8" t="inlineStr">
         <is>
           <t>SRS R-SWM-003</t>
         </is>
       </c>
-      <c r="H21" s="6" t="inlineStr">
+      <c r="H21" s="8" t="inlineStr">
         <is>
           <t>对接 II-11</t>
         </is>
       </c>
     </row>
-    <row r="22" ht="49.5" customHeight="1">
-      <c r="A22" s="4" t="inlineStr">
+    <row r="22">
+      <c r="A22" s="11" t="inlineStr">
         <is>
           <t>②模块</t>
         </is>
       </c>
-      <c r="B22" s="4" t="inlineStr">
+      <c r="B22" s="11" t="inlineStr">
         <is>
           <t>M-SWM-06</t>
         </is>
       </c>
-      <c r="C22" s="5" t="inlineStr">
+      <c r="C22" s="11" t="inlineStr">
         <is>
           <t>智能体评测与迭代决策（智能体质量裁判）</t>
         </is>
       </c>
-      <c r="D22" s="4" t="inlineStr">
+      <c r="D22" s="11" t="inlineStr">
         <is>
           <t>R-SWM-004</t>
         </is>
       </c>
-      <c r="E22" s="5" t="inlineStr">
-        <is>
-          <t>对构建出的智能体基于作业效果反馈(来自MC可观测性)与人设一致性进行质量评测，淘汰低效定义、迭代优化高价值定义，形成「构建→评测→迭代」闭环。</t>
-        </is>
-      </c>
-      <c r="F22" s="5" t="inlineStr">
-        <is>
-          <t>F-SWM-06-01 有效性评测(线上MC作业效果统计)；F-SWM-06-02 评测数据集管理；F-SWM-06-03 批量跑题执行；F-SWM-06-04 答案对比与打分；F-SWM-06-05 评分汇总与报告；F-SWM-06-06 迭代/淘汰决策与反馈闭环</t>
-        </is>
-      </c>
-      <c r="G22" s="5" t="inlineStr">
+      <c r="E22" s="11" t="inlineStr">
+        <is>
+          <t>对构建出的智能体采用「线上效果 + 离线数据集」双轨评测，淘汰低效定义、迭代优化高价值定义，形成「构建→评测→迭代」闭环。</t>
+        </is>
+      </c>
+      <c r="F22" s="11" t="inlineStr">
+        <is>
+          <t>F-SWM-06-01 有效性评测；F-SWM-06-02 评测数据集管理；F-SWM-06-03 批量跑题执行；F-SWM-06-04 答案对比与打分；F-SWM-06-05 评分汇总与报告；F-SWM-06-06 迭代/淘汰决策与反馈闭环</t>
+        </is>
+      </c>
+      <c r="G22" s="11" t="inlineStr">
         <is>
           <t>SRS R-SWM-004</t>
         </is>
       </c>
-      <c r="H22" s="5" t="inlineStr">
+      <c r="H22" s="11" t="inlineStr">
         <is>
           <t>对应 R-SWM-004。06-01 为线上效果统计(触达/互动/完成率)；06-02~05 为离线数据集评测流程(录入题集→跑题→打分→汇总)，按流程环节拆4个功能；一在线一离线互补评估；06-06 综合双轨结论做决策与反馈。</t>
         </is>
       </c>
     </row>
-    <row r="23" ht="33" customHeight="1">
-      <c r="A23" s="6" t="inlineStr">
-        <is>
-          <t>③功能</t>
-        </is>
-      </c>
-      <c r="B23" s="6" t="inlineStr">
+    <row r="23">
+      <c r="A23" s="8" t="inlineStr">
+        <is>
+          <t>③功能</t>
+        </is>
+      </c>
+      <c r="B23" s="8" t="inlineStr">
         <is>
           <t>F-SWM-06-01</t>
         </is>
       </c>
-      <c r="C23" s="6" t="inlineStr">
+      <c r="C23" s="8" t="inlineStr">
         <is>
           <t>有效性评测</t>
         </is>
       </c>
-      <c r="D23" s="6" t="inlineStr">
+      <c r="D23" s="8" t="inlineStr">
         <is>
           <t>R-SWM-004</t>
         </is>
       </c>
-      <c r="E23" s="6" t="inlineStr">
+      <c r="E23" s="8" t="inlineStr">
         <is>
           <t>基于MC可观测性上报的作业效果数据(触达/互动/任务完成率)评测智能体有效性。</t>
         </is>
       </c>
-      <c r="F23" s="6" t="inlineStr">
+      <c r="F23" s="8" t="inlineStr">
         <is>
           <t>基于MC作业效果评测有效性</t>
         </is>
       </c>
-      <c r="G23" s="6" t="inlineStr">
+      <c r="G23" s="8" t="inlineStr">
         <is>
           <t>SRS R-SWM-004</t>
         </is>
       </c>
-      <c r="H23" s="6" t="inlineStr">
+      <c r="H23" s="8" t="inlineStr">
         <is>
           <t>数据来自 R-MC-006</t>
         </is>
@@ -8450,11 +8483,11 @@
       </c>
       <c r="H24" s="8" t="inlineStr">
         <is>
-          <t>数据集是离线评测的可复现基准，固定题集可对不同版本反复评测对比演进</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="33" customHeight="1">
+          <t>数据集是离线评测的可复现基准</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
       <c r="A25" s="8" t="inlineStr">
         <is>
           <t>③功能</t>
@@ -8492,7 +8525,7 @@
       </c>
       <c r="H25" s="8" t="inlineStr">
         <is>
-          <t>对接 II-08/EI-06 本地推理</t>
+          <t>对接 II-08/EI-06</t>
         </is>
       </c>
     </row>
@@ -8612,11 +8645,7 @@
           <t>SRS R-SWM-004</t>
         </is>
       </c>
-      <c r="H28" s="8" t="inlineStr">
-        <is>
-          <t>原 F-SWM-06-03 顺延而来</t>
-        </is>
-      </c>
+      <c r="H28" s="8" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -9392,7 +9421,7 @@
           <t>③功能</t>
         </is>
       </c>
-      <c r="B13" s="6" t="inlineStr">
+      <c r="B13" s="7" t="inlineStr">
         <is>
           <t>F-OCC-03-01</t>
         </is>
@@ -9430,7 +9459,7 @@
           <t>③功能</t>
         </is>
       </c>
-      <c r="B14" s="6" t="inlineStr">
+      <c r="B14" s="7" t="inlineStr">
         <is>
           <t>F-OCC-03-02</t>
         </is>
@@ -9868,7 +9897,7 @@
           <t>③功能</t>
         </is>
       </c>
-      <c r="B25" s="6" t="inlineStr">
+      <c r="B25" s="7" t="inlineStr">
         <is>
           <t>F-OCC-06-01</t>
         </is>
@@ -9906,7 +9935,7 @@
           <t>③功能</t>
         </is>
       </c>
-      <c r="B26" s="6" t="inlineStr">
+      <c r="B26" s="7" t="inlineStr">
         <is>
           <t>F-OCC-06-02</t>
         </is>
@@ -9944,7 +9973,7 @@
           <t>③功能</t>
         </is>
       </c>
-      <c r="B27" s="6" t="inlineStr">
+      <c r="B27" s="7" t="inlineStr">
         <is>
           <t>F-OCC-06-03</t>
         </is>
@@ -9982,7 +10011,7 @@
           <t>③功能</t>
         </is>
       </c>
-      <c r="B28" s="6" t="inlineStr">
+      <c r="B28" s="7" t="inlineStr">
         <is>
           <t>F-OCC-06-04</t>
         </is>

--- a/公司项目/认知作战/文档/软件概要设计-模块功能拆分.xlsx
+++ b/公司项目/认知作战/文档/软件概要设计-模块功能拆分.xlsx
@@ -2360,8 +2360,8 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H37"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="18"/>
+  <dimension ref="A1:H38"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
@@ -2374,1486 +2374,1540 @@
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="9" t="inlineStr">
         <is>
           <t>层级</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="9" t="inlineStr">
         <is>
           <t>编号</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" s="9" t="inlineStr">
         <is>
           <t>名称</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" s="9" t="inlineStr">
         <is>
           <t>对应需求</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" s="9" t="inlineStr">
         <is>
           <t>职责简述</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" s="9" t="inlineStr">
         <is>
           <t>关键能力点（功能）</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" s="9" t="inlineStr">
         <is>
           <t>来源依据</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" s="9" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="132" customHeight="1">
-      <c r="A2" s="2" t="inlineStr">
+    <row r="2">
+      <c r="A2" s="10" t="inlineStr">
         <is>
           <t>①子系统</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="B2" s="10" t="inlineStr">
         <is>
           <t>M-DC-00</t>
         </is>
       </c>
-      <c r="C2" s="3" t="inlineStr">
+      <c r="C2" s="10" t="inlineStr">
         <is>
           <t>数据爬取子系统</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="D2" s="10" t="inlineStr">
         <is>
           <t>R-DC-001~004</t>
         </is>
       </c>
-      <c r="E2" s="3" t="inlineStr">
+      <c r="E2" s="10" t="inlineStr">
         <is>
           <t>基础设施层的数据采集与分析底座，采用「任务驱动采集」范式：采集任务由人工/情报回注注入任务池，爬虫作为执行器消费任务、按目标定向抓取；通过情报回注与目标扩散形成「分析→采集」反向闭环，对外提供情报与分析能力供 OCC 使用。</t>
         </is>
       </c>
-      <c r="F2" s="3" t="inlineStr">
+      <c r="F2" s="10" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G2" s="3" t="inlineStr">
+      <c r="G2" s="10" t="inlineStr">
         <is>
           <t>SRS §引言/DC</t>
         </is>
       </c>
-      <c r="H2" s="3" t="inlineStr">
+      <c r="H2" s="10" t="inlineStr">
         <is>
           <t>原 R-DC-001 爬取工程基础设施已并入运行环境需求（K3s/Kafka/Redis 部署）与 R-DC-001（代理池调度/任务去重/配额限流）；底座归运行环境需求，DC 内只保留调度/采集/监控/ETL/分析/扩散六个能力域。</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="99" customHeight="1">
-      <c r="A3" s="4" t="inlineStr">
+    <row r="3">
+      <c r="A3" s="11" t="inlineStr">
         <is>
           <t>②模块</t>
         </is>
       </c>
-      <c r="B3" s="4" t="inlineStr">
+      <c r="B3" s="11" t="inlineStr">
         <is>
           <t>M-DC-01</t>
         </is>
       </c>
-      <c r="C3" s="5" t="inlineStr">
+      <c r="C3" s="11" t="inlineStr">
         <is>
           <t>采集调度与资源管控（输入闸门与调度大脑）</t>
         </is>
       </c>
-      <c r="D3" s="4" t="inlineStr">
+      <c r="D3" s="11" t="inlineStr">
         <is>
           <t>R-DC-001(调度)</t>
         </is>
       </c>
-      <c r="E3" s="5" t="inlineStr">
+      <c r="E3" s="11" t="inlineStr">
         <is>
           <t>消费外部注入的采集任务，管理任务池、目标级去重、调度队列与配额限流，以及面向海外社交平台的代理网络出口（按平台/地区分配、定时轮换、可用性检测、失效剔除）。</t>
         </is>
       </c>
-      <c r="F3" s="5" t="inlineStr">
-        <is>
-          <t>F-DC-01-01 采集任务池与多来源接入；F-DC-01-02 任务类型与采集策略参数；F-DC-01-03 入池目标级去重；F-DC-01-04 调度队列与配额限流；F-DC-01-05 代理 IP 池调度；F-DC-01-06 任务状态机与断点续爬；F-DC-01-07 调度任务审计</t>
-        </is>
-      </c>
-      <c r="G3" s="5" t="inlineStr">
+      <c r="F3" s="11" t="inlineStr">
+        <is>
+          <t>F-DC-01-01 采集任务池与多来源接入；F-DC-01-02 任务类型与采集策略参数；F-DC-01-03 入池目标级去重；F-DC-01-04 调度队列分发；F-DC-01-05 配额限流；F-DC-01-06 代理 IP 池调度；F-DC-01-07 任务状态机与断点续爬；F-DC-01-08 调度任务审计</t>
+        </is>
+      </c>
+      <c r="G3" s="11" t="inlineStr">
         <is>
           <t>SRS R-DC-001(调度)</t>
         </is>
       </c>
-      <c r="H3" s="5" t="inlineStr">
+      <c r="H3" s="11" t="inlineStr">
         <is>
           <t>R-DC-001 含『调度分发』『资源管控(代理池/账号水位)』两类异构关注点，但从调度大脑视角二者紧耦合（配额依赖资源水位），故合并为一模块，采集执行与监控另列。</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="49.5" customHeight="1">
-      <c r="A4" s="6" t="inlineStr">
-        <is>
-          <t>③功能</t>
-        </is>
-      </c>
-      <c r="B4" s="6" t="inlineStr">
+    <row r="4">
+      <c r="A4" s="8" t="inlineStr">
+        <is>
+          <t>③功能</t>
+        </is>
+      </c>
+      <c r="B4" s="8" t="inlineStr">
         <is>
           <t>F-DC-01-01</t>
         </is>
       </c>
-      <c r="C4" s="6" t="inlineStr">
+      <c r="C4" s="8" t="inlineStr">
         <is>
           <t>采集任务池与多来源接入</t>
         </is>
       </c>
-      <c r="D4" s="6" t="inlineStr">
+      <c r="D4" s="8" t="inlineStr">
         <is>
           <t>R-DC-001</t>
         </is>
       </c>
-      <c r="E4" s="6" t="inlineStr">
+      <c r="E4" s="8" t="inlineStr">
         <is>
           <t>接收人工（REST/文件）、情报回注（F-DC-06-01）等多来源注入的采集任务，统一落入任务池（task_pool）。</t>
         </is>
       </c>
-      <c r="F4" s="6" t="inlineStr">
+      <c r="F4" s="8" t="inlineStr">
         <is>
           <t>REST API 批量注入；CSV/Excel 导入；情报回注回调注入；task_pool 结构(task_type/target/strategy/source/priority/status)</t>
         </is>
       </c>
-      <c r="G4" s="6" t="inlineStr">
+      <c r="G4" s="8" t="inlineStr">
         <is>
           <t>SRS R-DC-001</t>
         </is>
       </c>
-      <c r="H4" s="6" t="inlineStr"/>
-    </row>
-    <row r="5" ht="33" customHeight="1">
-      <c r="A5" s="6" t="inlineStr">
-        <is>
-          <t>③功能</t>
-        </is>
-      </c>
-      <c r="B5" s="6" t="inlineStr">
+      <c r="H4" s="8" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="8" t="inlineStr">
+        <is>
+          <t>③功能</t>
+        </is>
+      </c>
+      <c r="B5" s="8" t="inlineStr">
         <is>
           <t>F-DC-01-02</t>
         </is>
       </c>
-      <c r="C5" s="6" t="inlineStr">
+      <c r="C5" s="8" t="inlineStr">
         <is>
           <t>任务类型与采集策略参数</t>
         </is>
       </c>
-      <c r="D5" s="6" t="inlineStr">
+      <c r="D5" s="8" t="inlineStr">
         <is>
           <t>R-DC-001</t>
         </is>
       </c>
-      <c r="E5" s="6" t="inlineStr">
+      <c r="E5" s="8" t="inlineStr">
         <is>
           <t>以任务类型承载不同采集意图，使任务携带目标与策略参数支撑定向采集。</t>
         </is>
       </c>
-      <c r="F5" s="6" t="inlineStr">
+      <c r="F5" s="8" t="inlineStr">
         <is>
           <t>account定向/topic话题/keyword关键词/url_list/backfill回溯/recheck复查；类型决定采集执行逻辑</t>
         </is>
       </c>
-      <c r="G5" s="6" t="inlineStr">
+      <c r="G5" s="8" t="inlineStr">
         <is>
           <t>SRS R-DC-001</t>
         </is>
       </c>
-      <c r="H5" s="6" t="inlineStr"/>
-    </row>
-    <row r="6" ht="33" customHeight="1">
-      <c r="A6" s="6" t="inlineStr">
-        <is>
-          <t>③功能</t>
-        </is>
-      </c>
-      <c r="B6" s="6" t="inlineStr">
+      <c r="H5" s="8" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="8" t="inlineStr">
+        <is>
+          <t>③功能</t>
+        </is>
+      </c>
+      <c r="B6" s="8" t="inlineStr">
         <is>
           <t>F-DC-01-03</t>
         </is>
       </c>
-      <c r="C6" s="6" t="inlineStr">
+      <c r="C6" s="8" t="inlineStr">
         <is>
           <t>入池目标级去重</t>
         </is>
       </c>
-      <c r="D6" s="6" t="inlineStr">
+      <c r="D6" s="8" t="inlineStr">
         <is>
           <t>R-DC-001</t>
         </is>
       </c>
-      <c r="E6" s="6" t="inlineStr">
+      <c r="E6" s="8" t="inlineStr">
         <is>
           <t>任务入池时基于 Redis 对 URL 与任务做目标级去重、调度队列与分布式锁（双层去重第一层）。</t>
         </is>
       </c>
-      <c r="F6" s="6" t="inlineStr">
+      <c r="F6" s="8" t="inlineStr">
         <is>
           <t>目标规范化(URL/账号/话题/时间/策略)；target_hash 去重；Redis 调度队列+分布式锁；命中已采集目标转 recheck</t>
         </is>
       </c>
-      <c r="G6" s="6" t="inlineStr">
+      <c r="G6" s="8" t="inlineStr">
         <is>
           <t>SRS R-DC-001</t>
         </is>
       </c>
-      <c r="H6" s="6" t="inlineStr">
+      <c r="H6" s="8" t="inlineStr">
         <is>
           <t>支撑 II-16 情报回注去重</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="33" customHeight="1">
-      <c r="A7" s="6" t="inlineStr">
-        <is>
-          <t>③功能</t>
-        </is>
-      </c>
-      <c r="B7" s="6" t="inlineStr">
+    <row r="7">
+      <c r="A7" s="8" t="inlineStr">
+        <is>
+          <t>③功能</t>
+        </is>
+      </c>
+      <c r="B7" s="8" t="inlineStr">
         <is>
           <t>F-DC-01-04</t>
         </is>
       </c>
-      <c r="C7" s="6" t="inlineStr">
-        <is>
-          <t>调度队列与配额限流</t>
-        </is>
-      </c>
-      <c r="D7" s="6" t="inlineStr">
+      <c r="C7" s="8" t="inlineStr">
+        <is>
+          <t>调度队列分发</t>
+        </is>
+      </c>
+      <c r="D7" s="8" t="inlineStr">
         <is>
           <t>R-DC-001</t>
         </is>
       </c>
-      <c r="E7" s="6" t="inlineStr">
-        <is>
-          <t>维护调度队列按优先级分发爬虫执行；对采集范围、频率、并发设配额上限，超限自动限流。</t>
-        </is>
-      </c>
-      <c r="F7" s="6" t="inlineStr">
-        <is>
-          <t>优先级调度队列(P0~P4)；范围/频率/并发配额上限；超限自动限流</t>
-        </is>
-      </c>
-      <c r="G7" s="6" t="inlineStr">
+      <c r="E7" s="8" t="inlineStr">
+        <is>
+          <t>消费任务池，按优先级权重（人工&gt;情报回注&gt;侦察&gt;常规&gt;回溯 P0~P4）从 Redis ZSet 优先级队列批量领取任务，经 Kafka 分发到爬虫 Pod 执行；抢占式调度。</t>
+        </is>
+      </c>
+      <c r="F7" s="8" t="inlineStr">
+        <is>
+          <t>优先级权重五级(P0~P4)；Redis ZSet 优先级队列；DolphinScheduler 编排；Kafka 分发；抢占式调度</t>
+        </is>
+      </c>
+      <c r="G7" s="8" t="inlineStr">
         <is>
           <t>SRS R-DC-001</t>
         </is>
       </c>
-      <c r="H7" s="6" t="inlineStr"/>
-    </row>
-    <row r="8" ht="33" customHeight="1">
-      <c r="A8" s="6" t="inlineStr">
-        <is>
-          <t>③功能</t>
-        </is>
-      </c>
-      <c r="B8" s="6" t="inlineStr">
+      <c r="H7" s="8" t="inlineStr">
+        <is>
+          <t>出队调度，与配额限流分离</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="8" t="inlineStr">
+        <is>
+          <t>③功能</t>
+        </is>
+      </c>
+      <c r="B8" s="8" t="inlineStr">
         <is>
           <t>F-DC-01-05</t>
         </is>
       </c>
-      <c r="C8" s="6" t="inlineStr">
+      <c r="C8" s="8" t="inlineStr">
+        <is>
+          <t>配额限流</t>
+        </is>
+      </c>
+      <c r="D8" s="8" t="inlineStr">
+        <is>
+          <t>R-DC-001</t>
+        </is>
+      </c>
+      <c r="E8" s="8" t="inlineStr">
+        <is>
+          <t>对采集范围、频率、并发设配额上限；基于账号池/IP 池水位动态调节消费并发，水位不足时等待或降并发，水位变化反馈调节调度。</t>
+        </is>
+      </c>
+      <c r="F8" s="8" t="inlineStr">
+        <is>
+          <t>范围/频率/并发配额上限；账号/IP 水位校验；动态并发调节；超限自动限流；水位反馈调节调度</t>
+        </is>
+      </c>
+      <c r="G8" s="8" t="inlineStr">
+        <is>
+          <t>SRS R-DC-001</t>
+        </is>
+      </c>
+      <c r="H8" s="8" t="inlineStr">
+        <is>
+          <t>资源水位校验，与调度分发分离；与监控(M-DC-03)联动</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="8" t="inlineStr">
+        <is>
+          <t>③功能</t>
+        </is>
+      </c>
+      <c r="B9" s="8" t="inlineStr">
+        <is>
+          <t>F-DC-01-06</t>
+        </is>
+      </c>
+      <c r="C9" s="8" t="inlineStr">
         <is>
           <t>代理 IP 池调度</t>
         </is>
       </c>
-      <c r="D8" s="6" t="inlineStr">
+      <c r="D9" s="8" t="inlineStr">
         <is>
           <t>R-DC-001</t>
         </is>
       </c>
-      <c r="E8" s="6" t="inlineStr">
+      <c r="E9" s="8" t="inlineStr">
         <is>
           <t>对接 VPS 代理链路，按平台与地区分配代理 IP 并定时轮换，进行可用性检测与失效剔除。</t>
         </is>
       </c>
-      <c r="F8" s="6" t="inlineStr">
+      <c r="F9" s="8" t="inlineStr">
         <is>
           <t>按平台/地区分配；定时轮换；可用性检测；失效剔除；全失效时告警暂停受影响采集</t>
         </is>
       </c>
-      <c r="G8" s="6" t="inlineStr">
+      <c r="G9" s="8" t="inlineStr">
         <is>
           <t>SRS R-DC-001</t>
         </is>
       </c>
-      <c r="H8" s="6" t="inlineStr">
+      <c r="H9" s="8" t="inlineStr">
         <is>
           <t>对接 EI-02</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="49.5" customHeight="1">
-      <c r="A9" s="6" t="inlineStr">
-        <is>
-          <t>③功能</t>
-        </is>
-      </c>
-      <c r="B9" s="6" t="inlineStr">
-        <is>
-          <t>F-DC-01-06</t>
-        </is>
-      </c>
-      <c r="C9" s="6" t="inlineStr">
+    <row r="10">
+      <c r="A10" s="8" t="inlineStr">
+        <is>
+          <t>③功能</t>
+        </is>
+      </c>
+      <c r="B10" s="8" t="inlineStr">
+        <is>
+          <t>F-DC-01-07</t>
+        </is>
+      </c>
+      <c r="C10" s="8" t="inlineStr">
         <is>
           <t>任务状态机与断点续爬</t>
         </is>
       </c>
-      <c r="D9" s="6" t="inlineStr">
+      <c r="D10" s="8" t="inlineStr">
         <is>
           <t>R-DC-001</t>
         </is>
       </c>
-      <c r="E9" s="6" t="inlineStr">
+      <c r="E10" s="8" t="inlineStr">
         <is>
           <t>任务在 pending/claimed/running/done/failed/timeout/retry/dead/skipped 间流转；失败回池重排，重启续跑。</t>
         </is>
       </c>
-      <c r="F9" s="6" t="inlineStr">
+      <c r="F10" s="8" t="inlineStr">
         <is>
           <t>九态状态机；断点续爬(status 回 pending)；指数退避重试≤3次；超限进死信</t>
         </is>
       </c>
-      <c r="G9" s="6" t="inlineStr">
+      <c r="G10" s="8" t="inlineStr">
         <is>
           <t>SRS R-DC-001</t>
         </is>
       </c>
-      <c r="H9" s="6" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="6" t="inlineStr">
-        <is>
-          <t>③功能</t>
-        </is>
-      </c>
-      <c r="B10" s="6" t="inlineStr">
-        <is>
-          <t>F-DC-01-07</t>
-        </is>
-      </c>
-      <c r="C10" s="6" t="inlineStr">
+      <c r="H10" s="8" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="8" t="inlineStr">
+        <is>
+          <t>③功能</t>
+        </is>
+      </c>
+      <c r="B11" s="8" t="inlineStr">
+        <is>
+          <t>F-DC-01-08</t>
+        </is>
+      </c>
+      <c r="C11" s="8" t="inlineStr">
         <is>
           <t>调度任务审计</t>
         </is>
       </c>
-      <c r="D10" s="6" t="inlineStr">
+      <c r="D11" s="8" t="inlineStr">
         <is>
           <t>R-DC-001</t>
         </is>
       </c>
-      <c r="E10" s="6" t="inlineStr">
+      <c r="E11" s="8" t="inlineStr">
         <is>
           <t>记录任务来源、来源标识与注入时间，满足情报可审计性。</t>
         </is>
       </c>
-      <c r="F10" s="6" t="inlineStr">
+      <c r="F11" s="8" t="inlineStr">
         <is>
           <t>source_type/source_ref/injected_at 全程留痕</t>
         </is>
       </c>
-      <c r="G10" s="6" t="inlineStr">
+      <c r="G11" s="8" t="inlineStr">
         <is>
           <t>SRS R-DC-001</t>
         </is>
       </c>
-      <c r="H10" s="6" t="inlineStr">
+      <c r="H11" s="8" t="inlineStr">
         <is>
           <t>与数据血缘 F-DC-04-04 关联</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="82.5" customHeight="1">
-      <c r="A11" s="4" t="inlineStr">
+    <row r="12">
+      <c r="A12" s="11" t="inlineStr">
         <is>
           <t>②模块</t>
         </is>
       </c>
-      <c r="B11" s="4" t="inlineStr">
+      <c r="B12" s="11" t="inlineStr">
         <is>
           <t>M-DC-02</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr">
+      <c r="C12" s="11" t="inlineStr">
         <is>
           <t>社交媒体数据采集（爬虫执行器）</t>
         </is>
       </c>
-      <c r="D11" s="4" t="inlineStr">
+      <c r="D12" s="11" t="inlineStr">
         <is>
           <t>R-DC-001(执行)</t>
         </is>
       </c>
-      <c r="E11" s="5" t="inlineStr">
+      <c r="E12" s="11" t="inlineStr">
         <is>
           <t>消费任务池下发的任务，按任务目标从 TikTok/Instagram/Facebook/YouTube/X 等海外社交平台采集原始数据（用户/内容/互动/关系），并基于历史指标自适应优化采集策略。</t>
         </is>
       </c>
-      <c r="F11" s="5" t="inlineStr">
+      <c r="F12" s="11" t="inlineStr">
         <is>
           <t>F-DC-02-01 多平台采集适配；F-DC-02-02 采集手段切换与容错；F-DC-02-03 代理与维护账号应用；F-DC-02-04 采集策略自优化</t>
         </is>
       </c>
-      <c r="G11" s="5" t="inlineStr">
+      <c r="G12" s="11" t="inlineStr">
         <is>
           <t>SRS R-DC-001(执行)</t>
         </is>
       </c>
-      <c r="H11" s="5" t="inlineStr">
+      <c r="H12" s="11" t="inlineStr">
         <is>
           <t>R-DC-001 的『采集执行』与『调度分发』是两种关注点（执行器 vs 调度大脑），故从 M-DC-01 拆出；策略自优化是执行器的学习闭环能力。</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="33" customHeight="1">
-      <c r="A12" s="6" t="inlineStr">
-        <is>
-          <t>③功能</t>
-        </is>
-      </c>
-      <c r="B12" s="6" t="inlineStr">
+    <row r="13">
+      <c r="A13" s="8" t="inlineStr">
+        <is>
+          <t>③功能</t>
+        </is>
+      </c>
+      <c r="B13" s="8" t="inlineStr">
         <is>
           <t>F-DC-02-01</t>
         </is>
       </c>
-      <c r="C12" s="6" t="inlineStr">
+      <c r="C13" s="8" t="inlineStr">
         <is>
           <t>多平台采集适配</t>
         </is>
       </c>
-      <c r="D12" s="6" t="inlineStr">
+      <c r="D13" s="8" t="inlineStr">
         <is>
           <t>R-DC-001</t>
         </is>
       </c>
-      <c r="E12" s="6" t="inlineStr">
+      <c r="E13" s="8" t="inlineStr">
         <is>
           <t>各平台采集适配器，按平台采用不同手段采集推荐/人物/Reels 等数据。</t>
         </is>
       </c>
-      <c r="F12" s="6" t="inlineStr">
+      <c r="F13" s="8" t="inlineStr">
         <is>
           <t>逆向采集(IG/TikTok/FB/X)；官方 API；模拟点击；网页解析；覆盖 TikTok/IG/FB/YouTube/X</t>
         </is>
       </c>
-      <c r="G12" s="6" t="inlineStr">
+      <c r="G13" s="8" t="inlineStr">
         <is>
           <t>SRS R-DC-001</t>
         </is>
       </c>
-      <c r="H12" s="6" t="inlineStr">
+      <c r="H13" s="8" t="inlineStr">
         <is>
           <t>对接 EI-01</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="33" customHeight="1">
-      <c r="A13" s="6" t="inlineStr">
-        <is>
-          <t>③功能</t>
-        </is>
-      </c>
-      <c r="B13" s="6" t="inlineStr">
+    <row r="14">
+      <c r="A14" s="8" t="inlineStr">
+        <is>
+          <t>③功能</t>
+        </is>
+      </c>
+      <c r="B14" s="8" t="inlineStr">
         <is>
           <t>F-DC-02-02</t>
         </is>
       </c>
-      <c r="C13" s="6" t="inlineStr">
+      <c r="C14" s="8" t="inlineStr">
         <is>
           <t>采集手段切换与容错</t>
         </is>
       </c>
-      <c r="D13" s="6" t="inlineStr">
+      <c r="D14" s="8" t="inlineStr">
         <is>
           <t>R-DC-001</t>
         </is>
       </c>
-      <c r="E13" s="6" t="inlineStr">
+      <c r="E14" s="8" t="inlineStr">
         <is>
           <t>逆向接口失效或改版时告警并切换备用采集方式；API 限流按限额退避重试；账号被封自动切换备用账号。</t>
         </is>
       </c>
-      <c r="F13" s="6" t="inlineStr">
+      <c r="F14" s="8" t="inlineStr">
         <is>
           <t>手段可切换；限流退避重试；被封自动切换备用账号</t>
         </is>
       </c>
-      <c r="G13" s="6" t="inlineStr">
+      <c r="G14" s="8" t="inlineStr">
         <is>
           <t>SRS R-DC-001</t>
         </is>
       </c>
-      <c r="H13" s="6" t="inlineStr">
+      <c r="H14" s="8" t="inlineStr">
         <is>
           <t>被动应对单次异常</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="6" t="inlineStr">
-        <is>
-          <t>③功能</t>
-        </is>
-      </c>
-      <c r="B14" s="6" t="inlineStr">
+    <row r="15">
+      <c r="A15" s="8" t="inlineStr">
+        <is>
+          <t>③功能</t>
+        </is>
+      </c>
+      <c r="B15" s="8" t="inlineStr">
         <is>
           <t>F-DC-02-03</t>
         </is>
       </c>
-      <c r="C14" s="6" t="inlineStr">
+      <c r="C15" s="8" t="inlineStr">
         <is>
           <t>代理与维护账号应用</t>
         </is>
       </c>
-      <c r="D14" s="6" t="inlineStr">
+      <c r="D15" s="8" t="inlineStr">
         <is>
           <t>R-DC-001</t>
         </is>
       </c>
-      <c r="E14" s="6" t="inlineStr">
+      <c r="E15" s="8" t="inlineStr">
         <is>
           <t>采集过程使用代理 IP 与维护账号，应对平台访问限制。</t>
         </is>
       </c>
-      <c r="F14" s="6" t="inlineStr">
+      <c r="F15" s="8" t="inlineStr">
         <is>
           <t>采集绑定代理 IP；使用维护账号；应对访问限制</t>
         </is>
       </c>
-      <c r="G14" s="6" t="inlineStr">
+      <c r="G15" s="8" t="inlineStr">
         <is>
           <t>SRS R-DC-001</t>
         </is>
       </c>
-      <c r="H14" s="6" t="inlineStr"/>
-    </row>
-    <row r="15" ht="33" customHeight="1">
-      <c r="A15" s="6" t="inlineStr">
-        <is>
-          <t>③功能</t>
-        </is>
-      </c>
-      <c r="B15" s="6" t="inlineStr">
+      <c r="H15" s="8" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="8" t="inlineStr">
+        <is>
+          <t>③功能</t>
+        </is>
+      </c>
+      <c r="B16" s="8" t="inlineStr">
         <is>
           <t>F-DC-02-04</t>
         </is>
       </c>
-      <c r="C15" s="6" t="inlineStr">
+      <c r="C16" s="8" t="inlineStr">
         <is>
           <t>采集策略自优化</t>
         </is>
       </c>
-      <c r="D15" s="6" t="inlineStr">
+      <c r="D16" s="8" t="inlineStr">
         <is>
           <t>R-DC-001</t>
         </is>
       </c>
-      <c r="E15" s="6" t="inlineStr">
+      <c r="E16" s="8" t="inlineStr">
         <is>
           <t>基于历史采集指标（封禁率/成功率/反爬升级信号/各手段有效率）对采集策略主动调整，随平台反爬强度自适应演进。</t>
         </is>
       </c>
-      <c r="F15" s="6" t="inlineStr">
+      <c r="F16" s="8" t="inlineStr">
         <is>
           <t>手段优先级排序；请求频率/并发调节；代理与账号选择策略优化；指标不足或波动过大维持上一稳定策略并告警</t>
         </is>
       </c>
-      <c r="G15" s="6" t="inlineStr">
+      <c r="G16" s="8" t="inlineStr">
         <is>
           <t>SRS R-DC-001</t>
         </is>
       </c>
-      <c r="H15" s="6" t="inlineStr">
+      <c r="H16" s="8" t="inlineStr">
         <is>
           <t>主动学习闭环，区别于 F-DC-02-02 被动切换</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="82.5" customHeight="1">
-      <c r="A16" s="4" t="inlineStr">
+    <row r="17">
+      <c r="A17" s="11" t="inlineStr">
         <is>
           <t>②模块</t>
         </is>
       </c>
-      <c r="B16" s="4" t="inlineStr">
+      <c r="B17" s="11" t="inlineStr">
         <is>
           <t>M-DC-03</t>
         </is>
       </c>
-      <c r="C16" s="5" t="inlineStr">
+      <c r="C17" s="11" t="inlineStr">
         <is>
           <t>采集监控告警（采集系统的「眼睛」）</t>
         </is>
       </c>
-      <c r="D16" s="4" t="inlineStr">
+      <c r="D17" s="11" t="inlineStr">
         <is>
           <t>R-DC-001(支撑)</t>
         </is>
       </c>
-      <c r="E16" s="5" t="inlineStr">
+      <c r="E17" s="11" t="inlineStr">
         <is>
           <t>分钟级感知任务池积压、账号池耗尽、Kafka 积压、爬虫封禁等异常并反馈调节调度；DC 采集健康度专属，与平台级 OM 分工。</t>
         </is>
       </c>
-      <c r="F16" s="5" t="inlineStr">
+      <c r="F17" s="11" t="inlineStr">
         <is>
           <t>F-DC-03-01 指标采集（系统+业务）；F-DC-03-02 告警分级与路由；F-DC-03-03 监控大盘；F-DC-03-04 全链路追踪；F-DC-03-05 SLO 与反馈调节</t>
         </is>
       </c>
-      <c r="G16" s="5" t="inlineStr">
+      <c r="G17" s="11" t="inlineStr">
         <is>
           <t>SRS R-DC-001(支撑)</t>
         </is>
       </c>
-      <c r="H16" s="5" t="inlineStr">
+      <c r="H17" s="11" t="inlineStr">
         <is>
           <t>R-DC-001 的『监控反馈调节』是独立关注点（感知-反馈控制回路），与调度/执行分离；聚焦 DC 采集健康度，平台级运维归 OM。</t>
         </is>
       </c>
     </row>
-    <row r="17" ht="33" customHeight="1">
-      <c r="A17" s="6" t="inlineStr">
-        <is>
-          <t>③功能</t>
-        </is>
-      </c>
-      <c r="B17" s="6" t="inlineStr">
+    <row r="18">
+      <c r="A18" s="8" t="inlineStr">
+        <is>
+          <t>③功能</t>
+        </is>
+      </c>
+      <c r="B18" s="8" t="inlineStr">
         <is>
           <t>F-DC-03-01</t>
         </is>
       </c>
-      <c r="C17" s="6" t="inlineStr">
+      <c r="C18" s="8" t="inlineStr">
         <is>
           <t>指标采集（系统+业务）</t>
         </is>
       </c>
-      <c r="D17" s="6" t="inlineStr">
+      <c r="D18" s="8" t="inlineStr">
         <is>
           <t>R-DC-001</t>
         </is>
       </c>
-      <c r="E17" s="6" t="inlineStr">
+      <c r="E18" s="8" t="inlineStr">
         <is>
           <t>Prometheus 采集系统指标(节点/Kafka/存储/调度)与业务指标(任务池水位/采集成功率/封禁率/去重命中率/端到端延迟)。</t>
         </is>
       </c>
-      <c r="F17" s="6" t="inlineStr">
+      <c r="F18" s="8" t="inlineStr">
         <is>
           <t>系统指标+业务指标双覆盖；业务指标优先</t>
         </is>
       </c>
-      <c r="G17" s="6" t="inlineStr">
+      <c r="G18" s="8" t="inlineStr">
         <is>
           <t>SRS R-DC-001</t>
         </is>
       </c>
-      <c r="H17" s="6" t="inlineStr"/>
-    </row>
-    <row r="18" ht="33" customHeight="1">
-      <c r="A18" s="6" t="inlineStr">
-        <is>
-          <t>③功能</t>
-        </is>
-      </c>
-      <c r="B18" s="6" t="inlineStr">
+      <c r="H18" s="8" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="8" t="inlineStr">
+        <is>
+          <t>③功能</t>
+        </is>
+      </c>
+      <c r="B19" s="8" t="inlineStr">
         <is>
           <t>F-DC-03-02</t>
         </is>
       </c>
-      <c r="C18" s="6" t="inlineStr">
+      <c r="C19" s="8" t="inlineStr">
         <is>
           <t>告警分级与路由</t>
         </is>
       </c>
-      <c r="D18" s="6" t="inlineStr">
+      <c r="D19" s="8" t="inlineStr">
         <is>
           <t>R-DC-001</t>
         </is>
       </c>
-      <c r="E18" s="6" t="inlineStr">
+      <c r="E19" s="8" t="inlineStr">
         <is>
           <t>四级告警(致命/严重/警告/提示)差异化响应时效与通知方式，含告警抑制与聚合防风暴。</t>
         </is>
       </c>
-      <c r="F18" s="6" t="inlineStr">
+      <c r="F19" s="8" t="inlineStr">
         <is>
           <t>致命&lt;5min电话+IM+邮件；告警抑制聚合；Alertmanager 路由</t>
         </is>
       </c>
-      <c r="G18" s="6" t="inlineStr">
+      <c r="G19" s="8" t="inlineStr">
         <is>
           <t>SRS R-DC-001</t>
         </is>
       </c>
-      <c r="H18" s="6" t="inlineStr"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="6" t="inlineStr">
-        <is>
-          <t>③功能</t>
-        </is>
-      </c>
-      <c r="B19" s="6" t="inlineStr">
+      <c r="H19" s="8" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="8" t="inlineStr">
+        <is>
+          <t>③功能</t>
+        </is>
+      </c>
+      <c r="B20" s="8" t="inlineStr">
         <is>
           <t>F-DC-03-03</t>
         </is>
       </c>
-      <c r="C19" s="6" t="inlineStr">
+      <c r="C20" s="8" t="inlineStr">
         <is>
           <t>监控大盘</t>
         </is>
       </c>
-      <c r="D19" s="6" t="inlineStr">
+      <c r="D20" s="8" t="inlineStr">
         <is>
           <t>R-DC-001</t>
         </is>
       </c>
-      <c r="E19" s="6" t="inlineStr">
+      <c r="E20" s="8" t="inlineStr">
         <is>
           <t>Grafana 提供总览/任务池/平台维度/资源池/质量/调度六类大盘可视化。</t>
         </is>
       </c>
-      <c r="F19" s="6" t="inlineStr">
+      <c r="F20" s="8" t="inlineStr">
         <is>
           <t>六类大盘可视化</t>
         </is>
       </c>
-      <c r="G19" s="6" t="inlineStr">
+      <c r="G20" s="8" t="inlineStr">
         <is>
           <t>SRS R-DC-001</t>
         </is>
       </c>
-      <c r="H19" s="6" t="inlineStr"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="6" t="inlineStr">
-        <is>
-          <t>③功能</t>
-        </is>
-      </c>
-      <c r="B20" s="6" t="inlineStr">
+      <c r="H20" s="8" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="8" t="inlineStr">
+        <is>
+          <t>③功能</t>
+        </is>
+      </c>
+      <c r="B21" s="8" t="inlineStr">
         <is>
           <t>F-DC-03-04</t>
         </is>
       </c>
-      <c r="C20" s="6" t="inlineStr">
+      <c r="C21" s="8" t="inlineStr">
         <is>
           <t>全链路追踪</t>
         </is>
       </c>
-      <c r="D20" s="6" t="inlineStr">
+      <c r="D21" s="8" t="inlineStr">
         <is>
           <t>R-DC-001</t>
         </is>
       </c>
-      <c r="E20" s="6" t="inlineStr">
+      <c r="E21" s="8" t="inlineStr">
         <is>
           <t>OpenTelemetry 任务级 trace，从入池到入库全链路可追踪。</t>
         </is>
       </c>
-      <c r="F20" s="6" t="inlineStr">
+      <c r="F21" s="8" t="inlineStr">
         <is>
           <t>OpenTelemetry；任务级 trace(入池→调度→抓取→入库)</t>
         </is>
       </c>
-      <c r="G20" s="6" t="inlineStr">
+      <c r="G21" s="8" t="inlineStr">
         <is>
           <t>SRS R-DC-001</t>
         </is>
       </c>
-      <c r="H20" s="6" t="inlineStr">
+      <c r="H21" s="8" t="inlineStr">
         <is>
           <t>与审计/血缘关联</t>
         </is>
       </c>
     </row>
-    <row r="21" ht="33" customHeight="1">
-      <c r="A21" s="6" t="inlineStr">
-        <is>
-          <t>③功能</t>
-        </is>
-      </c>
-      <c r="B21" s="6" t="inlineStr">
+    <row r="22">
+      <c r="A22" s="8" t="inlineStr">
+        <is>
+          <t>③功能</t>
+        </is>
+      </c>
+      <c r="B22" s="8" t="inlineStr">
         <is>
           <t>F-DC-03-05</t>
         </is>
       </c>
-      <c r="C21" s="6" t="inlineStr">
+      <c r="C22" s="8" t="inlineStr">
         <is>
           <t>SLO 与反馈调节</t>
         </is>
       </c>
-      <c r="D21" s="6" t="inlineStr">
+      <c r="D22" s="8" t="inlineStr">
         <is>
           <t>R-DC-001</t>
         </is>
       </c>
-      <c r="E21" s="6" t="inlineStr">
+      <c r="E22" s="8" t="inlineStr">
         <is>
           <t>定义 SLO(入池→落地 P99&lt;10min)，监控指标反馈调节调度(封禁率升则降速、任务池积压则扩并发)。</t>
         </is>
       </c>
-      <c r="F21" s="6" t="inlineStr">
+      <c r="F22" s="8" t="inlineStr">
         <is>
           <t>SLO 定义；历史指标长期存储；监控→调度反馈调节</t>
         </is>
       </c>
-      <c r="G21" s="6" t="inlineStr">
+      <c r="G22" s="8" t="inlineStr">
         <is>
           <t>SRS R-DC-001</t>
         </is>
       </c>
-      <c r="H21" s="6" t="inlineStr"/>
-    </row>
-    <row r="22" ht="49.5" customHeight="1">
-      <c r="A22" s="4" t="inlineStr">
+      <c r="H22" s="8" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="11" t="inlineStr">
         <is>
           <t>②模块</t>
         </is>
       </c>
-      <c r="B22" s="4" t="inlineStr">
+      <c r="B23" s="11" t="inlineStr">
         <is>
           <t>M-DC-04</t>
         </is>
       </c>
-      <c r="C22" s="5" t="inlineStr">
+      <c r="C23" s="11" t="inlineStr">
         <is>
           <t>数据处理与存储（采集系统的「免疫系统」）</t>
         </is>
       </c>
-      <c r="D22" s="4" t="inlineStr">
+      <c r="D23" s="11" t="inlineStr">
         <is>
           <t>R-DC-002</t>
         </is>
       </c>
-      <c r="E22" s="5" t="inlineStr">
+      <c r="E23" s="11" t="inlineStr">
         <is>
           <t>对原始数据清洗加工并持久化存储，提供标准 ETL 链路 + 双层去重 + 质量校验 + 全字段血缘。</t>
         </is>
       </c>
-      <c r="F22" s="5" t="inlineStr">
-        <is>
-          <t>F-DC-04-01 分布式 ETL 加工；F-DC-04-02 入库内容指纹去重；F-DC-04-03 数据质量校验；F-DC-04-04 数据血缘与可追溯；F-DC-04-05 多存储分发</t>
-        </is>
-      </c>
-      <c r="G22" s="5" t="inlineStr">
+      <c r="F23" s="11" t="inlineStr">
+        <is>
+          <t>F-DC-04-01 分布式 ETL 加工；F-DC-04-02 入库内容指纹去重；F-DC-04-03 质量校验流水线编排；F-DC-04-04 校验规则管理；F-DC-04-05 数据血缘与可追溯；F-DC-04-06 多存储分发</t>
+        </is>
+      </c>
+      <c r="G23" s="11" t="inlineStr">
         <is>
           <t>SRS R-DC-002</t>
         </is>
       </c>
-      <c r="H22" s="5" t="inlineStr">
+      <c r="H23" s="11" t="inlineStr">
         <is>
           <t>对应 R-DC-002 ETL，内容指纹去重为双层去重第二层（第一层在 M-DC-01）。</t>
         </is>
       </c>
     </row>
-    <row r="23" ht="33" customHeight="1">
-      <c r="A23" s="6" t="inlineStr">
-        <is>
-          <t>③功能</t>
-        </is>
-      </c>
-      <c r="B23" s="6" t="inlineStr">
+    <row r="24">
+      <c r="A24" s="8" t="inlineStr">
+        <is>
+          <t>③功能</t>
+        </is>
+      </c>
+      <c r="B24" s="8" t="inlineStr">
         <is>
           <t>F-DC-04-01</t>
         </is>
       </c>
-      <c r="C23" s="6" t="inlineStr">
+      <c r="C24" s="8" t="inlineStr">
         <is>
           <t>分布式 ETL 加工</t>
         </is>
       </c>
-      <c r="D23" s="6" t="inlineStr">
+      <c r="D24" s="8" t="inlineStr">
         <is>
           <t>R-DC-002</t>
         </is>
       </c>
-      <c r="E23" s="6" t="inlineStr">
+      <c r="E24" s="8" t="inlineStr">
         <is>
           <t>基于 Spark/MapReduce 分布式批处理完成清洗、字段提取、格式标准化、去重与关联；节点失败自动重试或转移。</t>
         </is>
       </c>
-      <c r="F23" s="6" t="inlineStr">
+      <c r="F24" s="8" t="inlineStr">
         <is>
           <t>Spark/MapReduce；清洗/提取/标准化/去重/关联；失败重试或转移</t>
         </is>
       </c>
-      <c r="G23" s="6" t="inlineStr">
+      <c r="G24" s="8" t="inlineStr">
         <is>
           <t>SRS R-DC-002</t>
         </is>
       </c>
-      <c r="H23" s="6" t="inlineStr"/>
-    </row>
-    <row r="24" ht="33" customHeight="1">
-      <c r="A24" s="6" t="inlineStr">
-        <is>
-          <t>③功能</t>
-        </is>
-      </c>
-      <c r="B24" s="6" t="inlineStr">
+      <c r="H24" s="8" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="8" t="inlineStr">
+        <is>
+          <t>③功能</t>
+        </is>
+      </c>
+      <c r="B25" s="8" t="inlineStr">
         <is>
           <t>F-DC-04-02</t>
         </is>
       </c>
-      <c r="C24" s="6" t="inlineStr">
+      <c r="C25" s="8" t="inlineStr">
         <is>
           <t>入库内容指纹去重</t>
         </is>
       </c>
-      <c r="D24" s="6" t="inlineStr">
+      <c r="D25" s="8" t="inlineStr">
         <is>
           <t>R-DC-002</t>
         </is>
       </c>
-      <c r="E24" s="6" t="inlineStr">
+      <c r="E25" s="8" t="inlineStr">
         <is>
           <t>双层去重第二层：入库时按内容指纹去重，解决多任务交叉命中同一条内容。</t>
         </is>
       </c>
-      <c r="F24" s="6" t="inlineStr">
+      <c r="F25" s="8" t="inlineStr">
         <is>
           <t>精确去重(URL/平台主键)；SimHash(64位,Hamming≤3)；MinHash+LSH 语义(Jaccard≥0.85)</t>
         </is>
       </c>
-      <c r="G24" s="6" t="inlineStr">
+      <c r="G25" s="8" t="inlineStr">
         <is>
           <t>SRS R-DC-002</t>
         </is>
       </c>
-      <c r="H24" s="6" t="inlineStr">
+      <c r="H25" s="8" t="inlineStr">
         <is>
           <t>双层去重第二层</t>
         </is>
       </c>
     </row>
-    <row r="25" ht="33" customHeight="1">
-      <c r="A25" s="6" t="inlineStr">
-        <is>
-          <t>③功能</t>
-        </is>
-      </c>
-      <c r="B25" s="6" t="inlineStr">
+    <row r="26">
+      <c r="A26" s="8" t="inlineStr">
+        <is>
+          <t>③功能</t>
+        </is>
+      </c>
+      <c r="B26" s="8" t="inlineStr">
         <is>
           <t>F-DC-04-03</t>
         </is>
       </c>
-      <c r="C25" s="6" t="inlineStr">
-        <is>
-          <t>数据质量校验</t>
-        </is>
-      </c>
-      <c r="D25" s="6" t="inlineStr">
+      <c r="C26" s="8" t="inlineStr">
+        <is>
+          <t>质量校验流水线编排</t>
+        </is>
+      </c>
+      <c r="D26" s="8" t="inlineStr">
+        <is>
+          <t>R-DC-003</t>
+        </is>
+      </c>
+      <c r="E26" s="8" t="inlineStr">
+        <is>
+          <t>ETL 管道内串行执行六类校验，任一失败即进隔离区不入主库；编排校验执行顺序、隔离区写入与人工抽检闭环（每日0.1%抽样复核校准规则）。</t>
+        </is>
+      </c>
+      <c r="F26" s="8" t="inlineStr">
+        <is>
+          <t>串行六类校验编排；任一失败进隔离区(OSS dirty_zone)；人工抽检闭环(每日0.1%)</t>
+        </is>
+      </c>
+      <c r="G26" s="8" t="inlineStr">
+        <is>
+          <t>SRS R-DC-003</t>
+        </is>
+      </c>
+      <c r="H26" s="8" t="inlineStr">
+        <is>
+          <t>校验'流程'编排，与校验'规则配置'分离</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="8" t="inlineStr">
+        <is>
+          <t>③功能</t>
+        </is>
+      </c>
+      <c r="B27" s="8" t="inlineStr">
+        <is>
+          <t>F-DC-04-04</t>
+        </is>
+      </c>
+      <c r="C27" s="8" t="inlineStr">
+        <is>
+          <t>校验规则管理</t>
+        </is>
+      </c>
+      <c r="D27" s="8" t="inlineStr">
+        <is>
+          <t>R-DC-003</t>
+        </is>
+      </c>
+      <c r="E27" s="8" t="inlineStr">
+        <is>
+          <t>维护六类校验规则的定义与配置：Schema(字段完整性/类型/必填)、时间合理性、内容有效性、数值边界、平台一致性、异常检测；规则可配置可调整。</t>
+        </is>
+      </c>
+      <c r="F27" s="8" t="inlineStr">
+        <is>
+          <t>六类校验规则可配(Schema/时间/内容/数值/平台一致性/异常检测)；规则版本管理</t>
+        </is>
+      </c>
+      <c r="G27" s="8" t="inlineStr">
+        <is>
+          <t>SRS R-DC-003</t>
+        </is>
+      </c>
+      <c r="H27" s="8" t="inlineStr">
+        <is>
+          <t>校验'规则配置'，供流水线编排调用</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="8" t="inlineStr">
+        <is>
+          <t>③功能</t>
+        </is>
+      </c>
+      <c r="B28" s="8" t="inlineStr">
+        <is>
+          <t>F-DC-04-05</t>
+        </is>
+      </c>
+      <c r="C28" s="8" t="inlineStr">
+        <is>
+          <t>数据血缘与可追溯</t>
+        </is>
+      </c>
+      <c r="D28" s="8" t="inlineStr">
         <is>
           <t>R-DC-002</t>
         </is>
       </c>
-      <c r="E25" s="6" t="inlineStr">
-        <is>
-          <t>ETL 管道内串行六类校验，任一失败进隔离区不入主库。</t>
-        </is>
-      </c>
-      <c r="F25" s="6" t="inlineStr">
-        <is>
-          <t>Schema/时间/内容/数值/平台一致性/异常检测六类校验；脏数据隔离区；人工抽检闭环</t>
-        </is>
-      </c>
-      <c r="G25" s="6" t="inlineStr">
+      <c r="E28" s="8" t="inlineStr">
+        <is>
+          <t>每条数据带全字段血缘，满足认知战情报可审计性。</t>
+        </is>
+      </c>
+      <c r="F28" s="8" t="inlineStr">
+        <is>
+          <t>source_task_id/crawl_task_id/crawl_account_id/crawl_proxy_ip/raw_payload_url 等全字段血缘</t>
+        </is>
+      </c>
+      <c r="G28" s="8" t="inlineStr">
         <is>
           <t>SRS R-DC-002</t>
         </is>
       </c>
-      <c r="H25" s="6" t="inlineStr"/>
-    </row>
-    <row r="26" ht="33" customHeight="1">
-      <c r="A26" s="6" t="inlineStr">
-        <is>
-          <t>③功能</t>
-        </is>
-      </c>
-      <c r="B26" s="6" t="inlineStr">
-        <is>
-          <t>F-DC-04-04</t>
-        </is>
-      </c>
-      <c r="C26" s="6" t="inlineStr">
-        <is>
-          <t>数据血缘与可追溯</t>
-        </is>
-      </c>
-      <c r="D26" s="6" t="inlineStr">
+      <c r="H28" s="8" t="inlineStr">
+        <is>
+          <t>与 F-DC-01-07 审计关联</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="8" t="inlineStr">
+        <is>
+          <t>③功能</t>
+        </is>
+      </c>
+      <c r="B29" s="8" t="inlineStr">
+        <is>
+          <t>F-DC-04-06</t>
+        </is>
+      </c>
+      <c r="C29" s="8" t="inlineStr">
+        <is>
+          <t>多存储分发</t>
+        </is>
+      </c>
+      <c r="D29" s="8" t="inlineStr">
         <is>
           <t>R-DC-002</t>
         </is>
       </c>
-      <c r="E26" s="6" t="inlineStr">
-        <is>
-          <t>每条数据带全字段血缘，满足认知战情报可审计性。</t>
-        </is>
-      </c>
-      <c r="F26" s="6" t="inlineStr">
-        <is>
-          <t>source_task_id/crawl_task_id/crawl_account_id/crawl_proxy_ip/raw_payload_url 等全字段血缘</t>
-        </is>
-      </c>
-      <c r="G26" s="6" t="inlineStr">
+      <c r="E29" s="8" t="inlineStr">
+        <is>
+          <t>加工结果多存储分发：结构化结果写 HBase，元数据索引写关系库，关系数据写图数据库。</t>
+        </is>
+      </c>
+      <c r="F29" s="8" t="inlineStr">
+        <is>
+          <t>HBase(列式)；PG/MySQL(元数据索引)；图数据库(关系)；OSS(多媒体/归档)</t>
+        </is>
+      </c>
+      <c r="G29" s="8" t="inlineStr">
         <is>
           <t>SRS R-DC-002</t>
         </is>
       </c>
-      <c r="H26" s="6" t="inlineStr">
-        <is>
-          <t>与 F-DC-01-07 审计关联</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="33" customHeight="1">
-      <c r="A27" s="6" t="inlineStr">
-        <is>
-          <t>③功能</t>
-        </is>
-      </c>
-      <c r="B27" s="6" t="inlineStr">
-        <is>
-          <t>F-DC-04-05</t>
-        </is>
-      </c>
-      <c r="C27" s="6" t="inlineStr">
-        <is>
-          <t>多存储分发</t>
-        </is>
-      </c>
-      <c r="D27" s="6" t="inlineStr">
-        <is>
-          <t>R-DC-002</t>
-        </is>
-      </c>
-      <c r="E27" s="6" t="inlineStr">
-        <is>
-          <t>加工结果多存储分发：结构化结果写 HBase，元数据索引写关系库，关系数据写图数据库。</t>
-        </is>
-      </c>
-      <c r="F27" s="6" t="inlineStr">
-        <is>
-          <t>HBase(列式)；PG/MySQL(元数据索引)；图数据库(关系)；OSS(多媒体/归档)</t>
-        </is>
-      </c>
-      <c r="G27" s="6" t="inlineStr">
-        <is>
-          <t>SRS R-DC-002</t>
-        </is>
-      </c>
-      <c r="H27" s="6" t="inlineStr">
+      <c r="H29" s="8" t="inlineStr">
         <is>
           <t>DR-06</t>
         </is>
       </c>
     </row>
-    <row r="28" ht="49.5" customHeight="1">
-      <c r="A28" s="4" t="inlineStr">
+    <row r="30">
+      <c r="A30" s="11" t="inlineStr">
         <is>
           <t>②模块</t>
         </is>
       </c>
-      <c r="B28" s="4" t="inlineStr">
+      <c r="B30" s="11" t="inlineStr">
         <is>
           <t>M-DC-05</t>
         </is>
       </c>
-      <c r="C28" s="5" t="inlineStr">
+      <c r="C30" s="11" t="inlineStr">
         <is>
           <t>数据分析与情报（情报分析大脑）</t>
         </is>
       </c>
-      <c r="D28" s="4" t="inlineStr">
+      <c r="D30" s="11" t="inlineStr">
         <is>
           <t>R-DC-003</t>
         </is>
       </c>
-      <c r="E28" s="5" t="inlineStr">
+      <c r="E30" s="11" t="inlineStr">
         <is>
           <t>对加工数据进行分析，提供从群体到个体的筛选、关系图谱、情报检索、可视化与文本智能分析，支撑目标识别与内容研判，供 OCC 使用，并向 M-DC-06 输出情报驱动反向闭环的情报产出。</t>
         </is>
       </c>
-      <c r="F28" s="5" t="inlineStr">
-        <is>
-          <t>F-DC-05-01 群体到个体筛选；F-DC-05-02 关系图谱与图查询；F-DC-05-03 情报检索与实体档案；F-DC-05-04 文本智能分析；F-DC-05-05 可视化展示；F-DC-05-06 推理容错与降级</t>
-        </is>
-      </c>
-      <c r="G28" s="5" t="inlineStr">
+      <c r="F30" s="11" t="inlineStr">
+        <is>
+          <t>F-DC-05-01 群体到个体筛选；F-DC-05-02 关系图谱与图查询；F-DC-05-03 文本智能分析；F-DC-05-04 可视化展示；F-DC-05-05 推理容错与降级</t>
+        </is>
+      </c>
+      <c r="G30" s="11" t="inlineStr">
         <is>
           <t>SRS R-DC-003</t>
         </is>
       </c>
-      <c r="H28" s="5" t="inlineStr">
+      <c r="H30" s="11" t="inlineStr">
         <is>
           <t>对应 R-DC-003 分析，其情报产出是 M-DC-06 反向闭环的输入。</t>
         </is>
       </c>
     </row>
-    <row r="29" ht="33" customHeight="1">
-      <c r="A29" s="6" t="inlineStr">
-        <is>
-          <t>③功能</t>
-        </is>
-      </c>
-      <c r="B29" s="6" t="inlineStr">
+    <row r="31">
+      <c r="A31" s="8" t="inlineStr">
+        <is>
+          <t>③功能</t>
+        </is>
+      </c>
+      <c r="B31" s="8" t="inlineStr">
         <is>
           <t>F-DC-05-01</t>
         </is>
       </c>
-      <c r="C29" s="6" t="inlineStr">
+      <c r="C31" s="8" t="inlineStr">
         <is>
           <t>群体到个体筛选</t>
         </is>
       </c>
-      <c r="D29" s="6" t="inlineStr">
+      <c r="D31" s="8" t="inlineStr">
         <is>
           <t>R-DC-003</t>
         </is>
       </c>
-      <c r="E29" s="6" t="inlineStr">
+      <c r="E31" s="8" t="inlineStr">
         <is>
           <t>结合 AI 算法实现从群体到个体的逐层下钻筛选，从大范围群体定位目标个体。</t>
         </is>
       </c>
-      <c r="F29" s="6" t="inlineStr">
+      <c r="F31" s="8" t="inlineStr">
         <is>
           <t>AI 算法逐层下钻；群体→个体定位</t>
         </is>
       </c>
-      <c r="G29" s="6" t="inlineStr">
+      <c r="G31" s="8" t="inlineStr">
         <is>
           <t>SRS R-DC-003</t>
         </is>
       </c>
-      <c r="H29" s="6" t="inlineStr"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="6" t="inlineStr">
-        <is>
-          <t>③功能</t>
-        </is>
-      </c>
-      <c r="B30" s="6" t="inlineStr">
+      <c r="H31" s="8" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="8" t="inlineStr">
+        <is>
+          <t>③功能</t>
+        </is>
+      </c>
+      <c r="B32" s="8" t="inlineStr">
         <is>
           <t>F-DC-05-02</t>
         </is>
       </c>
-      <c r="C30" s="6" t="inlineStr">
+      <c r="C32" s="8" t="inlineStr">
         <is>
           <t>关系图谱与图查询</t>
         </is>
       </c>
-      <c r="D30" s="6" t="inlineStr">
+      <c r="D32" s="8" t="inlineStr">
         <is>
           <t>R-DC-003</t>
         </is>
       </c>
-      <c r="E30" s="6" t="inlineStr">
+      <c r="E32" s="8" t="inlineStr">
         <is>
           <t>基于实体与关联数据绘制关系图谱并支持图查询；数据量过大时分页或限流。</t>
         </is>
       </c>
-      <c r="F30" s="6" t="inlineStr">
+      <c r="F32" s="8" t="inlineStr">
         <is>
           <t>关系图谱绘制；图查询；分页/限流</t>
         </is>
       </c>
-      <c r="G30" s="6" t="inlineStr">
+      <c r="G32" s="8" t="inlineStr">
         <is>
           <t>SRS R-DC-003</t>
         </is>
       </c>
-      <c r="H30" s="6" t="inlineStr"/>
-    </row>
-    <row r="31" ht="33" customHeight="1">
-      <c r="A31" s="6" t="inlineStr">
-        <is>
-          <t>③功能</t>
-        </is>
-      </c>
-      <c r="B31" s="6" t="inlineStr">
+      <c r="H32" s="8" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="8" t="inlineStr">
+        <is>
+          <t>③功能</t>
+        </is>
+      </c>
+      <c r="B33" s="8" t="inlineStr">
         <is>
           <t>F-DC-05-03</t>
         </is>
       </c>
-      <c r="C31" s="6" t="inlineStr">
-        <is>
-          <t>情报检索与实体档案</t>
-        </is>
-      </c>
-      <c r="D31" s="6" t="inlineStr">
+      <c r="C33" s="8" t="inlineStr">
+        <is>
+          <t>文本智能分析</t>
+        </is>
+      </c>
+      <c r="D33" s="8" t="inlineStr">
         <is>
           <t>R-DC-003</t>
         </is>
       </c>
-      <c r="E31" s="6" t="inlineStr">
-        <is>
-          <t>按账号/昵称/标识检索实体；输出关联拓扑与情报标签；聚合多来源形成实体全维度档案。</t>
-        </is>
-      </c>
-      <c r="F31" s="6" t="inlineStr">
-        <is>
-          <t>多维检索；关联拓扑；情报标签；实体全维度档案</t>
-        </is>
-      </c>
-      <c r="G31" s="6" t="inlineStr">
+      <c r="E33" s="8" t="inlineStr">
+        <is>
+          <t>对文本内容结合文本模型与关键词库进行规则匹配与分类筛选（立场/情感/观点）；模型不可用回退关键词规则。</t>
+        </is>
+      </c>
+      <c r="F33" s="8" t="inlineStr">
+        <is>
+          <t>文本模型+关键词库；规则匹配与分类筛选；降级回退关键词</t>
+        </is>
+      </c>
+      <c r="G33" s="8" t="inlineStr">
         <is>
           <t>SRS R-DC-003</t>
         </is>
       </c>
-      <c r="H31" s="6" t="inlineStr"/>
-    </row>
-    <row r="32" ht="33" customHeight="1">
-      <c r="A32" s="6" t="inlineStr">
-        <is>
-          <t>③功能</t>
-        </is>
-      </c>
-      <c r="B32" s="6" t="inlineStr">
+      <c r="H33" s="8" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="8" t="inlineStr">
+        <is>
+          <t>③功能</t>
+        </is>
+      </c>
+      <c r="B34" s="8" t="inlineStr">
         <is>
           <t>F-DC-05-04</t>
         </is>
       </c>
-      <c r="C32" s="6" t="inlineStr">
-        <is>
-          <t>文本智能分析</t>
-        </is>
-      </c>
-      <c r="D32" s="6" t="inlineStr">
+      <c r="C34" s="8" t="inlineStr">
+        <is>
+          <t>可视化展示</t>
+        </is>
+      </c>
+      <c r="D34" s="8" t="inlineStr">
         <is>
           <t>R-DC-003</t>
         </is>
       </c>
-      <c r="E32" s="6" t="inlineStr">
-        <is>
-          <t>对文本内容结合文本模型与关键词库进行规则匹配与分类筛选（立场/情感/观点）；模型不可用回退关键词规则。</t>
-        </is>
-      </c>
-      <c r="F32" s="6" t="inlineStr">
-        <is>
-          <t>文本模型+关键词库；规则匹配与分类筛选；降级回退关键词</t>
-        </is>
-      </c>
-      <c r="G32" s="6" t="inlineStr">
+      <c r="E34" s="8" t="inlineStr">
+        <is>
+          <t>分析结果可视化展示界面，支撑情报分析人员研判。</t>
+        </is>
+      </c>
+      <c r="F34" s="8" t="inlineStr">
+        <is>
+          <t>可视化展示界面</t>
+        </is>
+      </c>
+      <c r="G34" s="8" t="inlineStr">
         <is>
           <t>SRS R-DC-003</t>
         </is>
       </c>
-      <c r="H32" s="6" t="inlineStr"/>
-    </row>
-    <row r="33">
-      <c r="A33" s="6" t="inlineStr">
-        <is>
-          <t>③功能</t>
-        </is>
-      </c>
-      <c r="B33" s="6" t="inlineStr">
+      <c r="H34" s="8" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="8" t="inlineStr">
+        <is>
+          <t>③功能</t>
+        </is>
+      </c>
+      <c r="B35" s="8" t="inlineStr">
         <is>
           <t>F-DC-05-05</t>
         </is>
       </c>
-      <c r="C33" s="6" t="inlineStr">
-        <is>
-          <t>可视化展示</t>
-        </is>
-      </c>
-      <c r="D33" s="6" t="inlineStr">
+      <c r="C35" s="8" t="inlineStr">
+        <is>
+          <t>推理容错与降级</t>
+        </is>
+      </c>
+      <c r="D35" s="8" t="inlineStr">
         <is>
           <t>R-DC-003</t>
         </is>
       </c>
-      <c r="E33" s="6" t="inlineStr">
-        <is>
-          <t>分析结果可视化展示界面，支撑情报分析人员研判。</t>
-        </is>
-      </c>
-      <c r="F33" s="6" t="inlineStr">
-        <is>
-          <t>可视化展示界面</t>
-        </is>
-      </c>
-      <c r="G33" s="6" t="inlineStr">
+      <c r="E35" s="8" t="inlineStr">
+        <is>
+          <t>算法推理超时或失败时降级返回部分结果并告警，保障分析可用性。</t>
+        </is>
+      </c>
+      <c r="F35" s="8" t="inlineStr">
+        <is>
+          <t>推理超时/失败降级返回部分结果并告警</t>
+        </is>
+      </c>
+      <c r="G35" s="8" t="inlineStr">
         <is>
           <t>SRS R-DC-003</t>
         </is>
       </c>
-      <c r="H33" s="6" t="inlineStr"/>
-    </row>
-    <row r="34">
-      <c r="A34" s="6" t="inlineStr">
-        <is>
-          <t>③功能</t>
-        </is>
-      </c>
-      <c r="B34" s="6" t="inlineStr">
-        <is>
-          <t>F-DC-05-06</t>
-        </is>
-      </c>
-      <c r="C34" s="6" t="inlineStr">
-        <is>
-          <t>推理容错与降级</t>
-        </is>
-      </c>
-      <c r="D34" s="6" t="inlineStr">
-        <is>
-          <t>R-DC-003</t>
-        </is>
-      </c>
-      <c r="E34" s="6" t="inlineStr">
-        <is>
-          <t>算法推理超时或失败时降级返回部分结果并告警，保障分析可用性。</t>
-        </is>
-      </c>
-      <c r="F34" s="6" t="inlineStr">
-        <is>
-          <t>推理超时/失败降级返回部分结果并告警</t>
-        </is>
-      </c>
-      <c r="G34" s="6" t="inlineStr">
-        <is>
-          <t>SRS R-DC-003</t>
-        </is>
-      </c>
-      <c r="H34" s="6" t="inlineStr"/>
-    </row>
-    <row r="35" ht="49.5" customHeight="1">
-      <c r="A35" s="4" t="inlineStr">
+      <c r="H35" s="8" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="11" t="inlineStr">
         <is>
           <t>②模块</t>
         </is>
       </c>
-      <c r="B35" s="4" t="inlineStr">
+      <c r="B36" s="11" t="inlineStr">
         <is>
           <t>M-DC-06</t>
         </is>
       </c>
-      <c r="C35" s="5" t="inlineStr">
+      <c r="C36" s="11" t="inlineStr">
         <is>
           <t>情报驱动采集与目标扩散（反向驱动大脑）</t>
         </is>
       </c>
-      <c r="D35" s="4" t="inlineStr">
+      <c r="D36" s="11" t="inlineStr">
         <is>
           <t>R-DC-004</t>
         </is>
       </c>
-      <c r="E35" s="5" t="inlineStr">
+      <c r="E36" s="11" t="inlineStr">
         <is>
           <t>打通「分析→采集」反向链路，使 M-DC-05 情报产出（目标个体/关联实体/传播节点）回注任务池并按关系扩散采集，形成「发现线索→定向扩散采集→锁定目标」的情报驱动闭环。</t>
         </is>
       </c>
-      <c r="F35" s="5" t="inlineStr">
+      <c r="F36" s="11" t="inlineStr">
         <is>
           <t>F-DC-06-01 情报回注采集；F-DC-06-02 目标扩散采集</t>
         </is>
       </c>
-      <c r="G35" s="5" t="inlineStr">
+      <c r="G36" s="11" t="inlineStr">
         <is>
           <t>SRS R-DC-004</t>
         </is>
       </c>
-      <c r="H35" s="5" t="inlineStr">
+      <c r="H36" s="11" t="inlineStr">
         <is>
           <t>对应 R-DC-004 反向闭环，是 DC 从单向采集管道升级为情报驱动闭环的关键。</t>
         </is>
       </c>
     </row>
-    <row r="36" ht="49.5" customHeight="1">
-      <c r="A36" s="6" t="inlineStr">
-        <is>
-          <t>③功能</t>
-        </is>
-      </c>
-      <c r="B36" s="6" t="inlineStr">
+    <row r="37">
+      <c r="A37" s="8" t="inlineStr">
+        <is>
+          <t>③功能</t>
+        </is>
+      </c>
+      <c r="B37" s="8" t="inlineStr">
         <is>
           <t>F-DC-06-01</t>
         </is>
       </c>
-      <c r="C36" s="6" t="inlineStr">
+      <c r="C37" s="8" t="inlineStr">
         <is>
           <t>情报回注采集</t>
         </is>
       </c>
-      <c r="D36" s="6" t="inlineStr">
+      <c r="D37" s="8" t="inlineStr">
         <is>
           <t>R-DC-004</t>
         </is>
       </c>
-      <c r="E36" s="6" t="inlineStr">
+      <c r="E37" s="8" t="inlineStr">
         <is>
           <t>将分析产出的高价值目标/关联实体/传播节点按规则自动或经人工确认生成定向采集任务回注任务池，携带 source_type=intel_feedback；经目标级去重，命中已采集目标转 recheck。</t>
         </is>
       </c>
-      <c r="F36" s="6" t="inlineStr">
+      <c r="F37" s="8" t="inlineStr">
         <is>
           <t>情报→任务自动/人工回注；source_type=intel_feedback；目标级去重转 recheck；人工确认闸门(高扩散/批量/敏感)；全程审计</t>
         </is>
       </c>
-      <c r="G36" s="6" t="inlineStr">
+      <c r="G37" s="8" t="inlineStr">
         <is>
           <t>SRS R-DC-004</t>
         </is>
       </c>
-      <c r="H36" s="6" t="inlineStr">
+      <c r="H37" s="8" t="inlineStr">
         <is>
           <t>反向接口 II-16</t>
         </is>
       </c>
     </row>
-    <row r="37" ht="49.5" customHeight="1">
-      <c r="A37" s="6" t="inlineStr">
-        <is>
-          <t>③功能</t>
-        </is>
-      </c>
-      <c r="B37" s="6" t="inlineStr">
+    <row r="38">
+      <c r="A38" s="8" t="inlineStr">
+        <is>
+          <t>③功能</t>
+        </is>
+      </c>
+      <c r="B38" s="8" t="inlineStr">
         <is>
           <t>F-DC-06-02</t>
         </is>
       </c>
-      <c r="C37" s="6" t="inlineStr">
+      <c r="C38" s="8" t="inlineStr">
         <is>
           <t>目标扩散采集</t>
         </is>
       </c>
-      <c r="D37" s="6" t="inlineStr">
+      <c r="D38" s="8" t="inlineStr">
         <is>
           <t>R-DC-004</t>
         </is>
       </c>
-      <c r="E37" s="6" t="inlineStr">
+      <c r="E38" s="8" t="inlineStr">
         <is>
           <t>以已采集目标为起点按关系类型(关注/粉丝/互动/转发链/评论链)与扩散层数图扩展式采集，新节点经去重生成新任务，受配额与层数上限约束，新目标回流后可再次触发回注，形成迭代扩散。</t>
         </is>
       </c>
-      <c r="F37" s="6" t="inlineStr">
+      <c r="F38" s="8" t="inlineStr">
         <is>
           <t>按关系+层数 BFS 扩散；新节点去重生成任务；层数/单层节点数/总数上限；迭代扩散回流；超限停止告警</t>
         </is>
       </c>
-      <c r="G37" s="6" t="inlineStr">
+      <c r="G38" s="8" t="inlineStr">
         <is>
           <t>SRS R-DC-004</t>
         </is>
       </c>
-      <c r="H37" s="6" t="inlineStr">
+      <c r="H38" s="8" t="inlineStr">
         <is>
           <t>区别于 OCC 扩散趋势预判(本期暂不实现)</t>
         </is>
@@ -3870,8 +3924,8 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H66"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="18"/>
+  <dimension ref="A1:H71"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
@@ -3884,2608 +3938,2826 @@
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="9" t="inlineStr">
         <is>
           <t>层级</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="9" t="inlineStr">
         <is>
           <t>编号</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" s="9" t="inlineStr">
         <is>
           <t>名称</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" s="9" t="inlineStr">
         <is>
           <t>对应需求</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" s="9" t="inlineStr">
         <is>
           <t>职责简述</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" s="9" t="inlineStr">
         <is>
           <t>关键能力点（功能）</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" s="9" t="inlineStr">
         <is>
           <t>来源依据</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" s="9" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="115.5" customHeight="1">
-      <c r="A2" s="2" t="inlineStr">
+    <row r="2">
+      <c r="A2" s="10" t="inlineStr">
         <is>
           <t>①子系统</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="B2" s="10" t="inlineStr">
         <is>
           <t>M-MC-00</t>
         </is>
       </c>
-      <c r="C2" s="3" t="inlineStr">
+      <c r="C2" s="10" t="inlineStr">
         <is>
           <t>多设备矩阵自动化群控子系统</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="D2" s="10" t="inlineStr">
         <is>
           <t>R-MC-001~008</t>
         </is>
       </c>
-      <c r="E2" s="3" t="inlineStr">
+      <c r="E2" s="10" t="inlineStr">
         <is>
           <t>统一自动化执行引擎与多终端执行网关：统一管理移动端（真机/云手机/ARM板卡/虚拟化真机）与桌面端（反指纹浏览器 Profile）四类执行终端；收口所有终端动作（可观测/可审计/可熔断）；承担账号资源平台级权威源与智能体执行宿主两项职责。</t>
         </is>
       </c>
-      <c r="F2" s="3" t="inlineStr">
+      <c r="F2" s="10" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G2" s="3" t="inlineStr">
+      <c r="G2" s="10" t="inlineStr">
         <is>
           <t>SRS §引言/MC</t>
         </is>
       </c>
-      <c r="H2" s="3" t="inlineStr">
+      <c r="H2" s="10" t="inlineStr">
         <is>
           <t>FB（指纹浏览器管理）与 SR（共享资源管理）已合并入 MC：桌面端 Profile 管理+CDP 执行网关、账号主数据权威源、智能体执行宿主统一收口到 MC 的统一执行网关（CON-07/11）。</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="99" customHeight="1">
-      <c r="A3" s="4" t="inlineStr">
+    <row r="3">
+      <c r="A3" s="11" t="inlineStr">
         <is>
           <t>②模块</t>
         </is>
       </c>
-      <c r="B3" s="4" t="inlineStr">
+      <c r="B3" s="11" t="inlineStr">
         <is>
           <t>M-MC-01</t>
         </is>
       </c>
-      <c r="C3" s="5" t="inlineStr">
+      <c r="C3" s="11" t="inlineStr">
         <is>
           <t>执行终端接入与台账（终端资源池管理者）</t>
         </is>
       </c>
-      <c r="D3" s="4" t="inlineStr">
+      <c r="D3" s="11" t="inlineStr">
         <is>
           <t>R-MC-001(接入)</t>
         </is>
       </c>
-      <c r="E3" s="5" t="inlineStr">
+      <c r="E3" s="11" t="inlineStr">
         <is>
           <t>统一管理四类执行终端的接入、创建、分组、状态登记与批量操作，提供执行终端资源池。</t>
         </is>
       </c>
-      <c r="F3" s="5" t="inlineStr">
+      <c r="F3" s="11" t="inlineStr">
         <is>
           <t>F-MC-01-01 移动端终端接入与台账；F-MC-01-02 浏览器 Profile 创建与 CDP 接入；F-MC-01-03 终端分组与标签；F-MC-01-04 终端批量操作</t>
         </is>
       </c>
-      <c r="G3" s="5" t="inlineStr">
+      <c r="G3" s="11" t="inlineStr">
         <is>
           <t>SRS R-MC-001(接入)</t>
         </is>
       </c>
-      <c r="H3" s="5" t="inlineStr">
+      <c r="H3" s="11" t="inlineStr">
         <is>
           <t>R-MC-001 含『终端作为资源进入系统』『让终端像真人且互不关联』『终端健康感知与风险应对』三个异构关注点，故拆 3 模块。本模块聚焦终端接入与台账。</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="33" customHeight="1">
-      <c r="A4" s="6" t="inlineStr">
-        <is>
-          <t>③功能</t>
-        </is>
-      </c>
-      <c r="B4" s="6" t="inlineStr">
+    <row r="4">
+      <c r="A4" s="8" t="inlineStr">
+        <is>
+          <t>③功能</t>
+        </is>
+      </c>
+      <c r="B4" s="8" t="inlineStr">
         <is>
           <t>F-MC-01-01</t>
         </is>
       </c>
-      <c r="C4" s="6" t="inlineStr">
+      <c r="C4" s="8" t="inlineStr">
         <is>
           <t>移动端终端接入与台账</t>
         </is>
       </c>
-      <c r="D4" s="6" t="inlineStr">
+      <c r="D4" s="8" t="inlineStr">
         <is>
           <t>R-MC-001</t>
         </is>
       </c>
-      <c r="E4" s="6" t="inlineStr">
+      <c r="E4" s="8" t="inlineStr">
         <is>
           <t>移动端 Agent 启动后注册并建立长连接，记录设备类型(真机/云手机/ARM板卡/虚拟化真机)、版本、型号、分组与标签，形成执行终端台账。</t>
         </is>
       </c>
-      <c r="F4" s="6" t="inlineStr">
+      <c r="F4" s="8" t="inlineStr">
         <is>
           <t>Agent 注册+长连接；设备类型区分虚拟/实体；台账记录</t>
         </is>
       </c>
-      <c r="G4" s="6" t="inlineStr">
+      <c r="G4" s="8" t="inlineStr">
         <is>
           <t>SRS R-MC-001</t>
         </is>
       </c>
-      <c r="H4" s="6" t="inlineStr"/>
-    </row>
-    <row r="5" ht="33" customHeight="1">
-      <c r="A5" s="6" t="inlineStr">
-        <is>
-          <t>③功能</t>
-        </is>
-      </c>
-      <c r="B5" s="6" t="inlineStr">
+      <c r="H4" s="8" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="8" t="inlineStr">
+        <is>
+          <t>③功能</t>
+        </is>
+      </c>
+      <c r="B5" s="8" t="inlineStr">
         <is>
           <t>F-MC-01-02</t>
         </is>
       </c>
-      <c r="C5" s="6" t="inlineStr">
+      <c r="C5" s="8" t="inlineStr">
         <is>
           <t>浏览器 Profile 创建与 CDP 接入</t>
         </is>
       </c>
-      <c r="D5" s="6" t="inlineStr">
+      <c r="D5" s="8" t="inlineStr">
         <is>
           <t>R-MC-001</t>
         </is>
       </c>
-      <c r="E5" s="6" t="inlineStr">
+      <c r="E5" s="8" t="inlineStr">
         <is>
           <t>基于开源 BotBrowser 定制内核创建浏览器 Profile，经 CDP 向服务端注册，记录 Profile 标识、Chromium 内核版本、分组与标签。</t>
         </is>
       </c>
-      <c r="F5" s="6" t="inlineStr">
+      <c r="F5" s="8" t="inlineStr">
         <is>
           <t>Profile 创建；CDP 注册；分组与标签管理</t>
         </is>
       </c>
-      <c r="G5" s="6" t="inlineStr">
+      <c r="G5" s="8" t="inlineStr">
         <is>
           <t>SRS R-MC-001；CON-12</t>
         </is>
       </c>
-      <c r="H5" s="6" t="inlineStr"/>
-    </row>
-    <row r="6" ht="33" customHeight="1">
-      <c r="A6" s="6" t="inlineStr">
-        <is>
-          <t>③功能</t>
-        </is>
-      </c>
-      <c r="B6" s="6" t="inlineStr">
+      <c r="H5" s="8" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="8" t="inlineStr">
+        <is>
+          <t>③功能</t>
+        </is>
+      </c>
+      <c r="B6" s="8" t="inlineStr">
         <is>
           <t>F-MC-01-03</t>
         </is>
       </c>
-      <c r="C6" s="6" t="inlineStr">
+      <c r="C6" s="8" t="inlineStr">
         <is>
           <t>终端分组与标签</t>
         </is>
       </c>
-      <c r="D6" s="6" t="inlineStr">
+      <c r="D6" s="8" t="inlineStr">
         <is>
           <t>R-MC-001</t>
         </is>
       </c>
-      <c r="E6" s="6" t="inlineStr">
+      <c r="E6" s="8" t="inlineStr">
         <is>
           <t>按业务目标、平台、地区等维度对执行终端分组与打标，支撑任务调度按分组选终端。</t>
         </is>
       </c>
-      <c r="F6" s="6" t="inlineStr">
+      <c r="F6" s="8" t="inlineStr">
         <is>
           <t>多维度分组；标签管理；按分组选终端</t>
         </is>
       </c>
-      <c r="G6" s="6" t="inlineStr">
+      <c r="G6" s="8" t="inlineStr">
         <is>
           <t>SRS R-MC-001</t>
         </is>
       </c>
-      <c r="H6" s="6" t="inlineStr"/>
-    </row>
-    <row r="7" ht="33" customHeight="1">
-      <c r="A7" s="6" t="inlineStr">
-        <is>
-          <t>③功能</t>
-        </is>
-      </c>
-      <c r="B7" s="6" t="inlineStr">
+      <c r="H6" s="8" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="8" t="inlineStr">
+        <is>
+          <t>③功能</t>
+        </is>
+      </c>
+      <c r="B7" s="8" t="inlineStr">
         <is>
           <t>F-MC-01-04</t>
         </is>
       </c>
-      <c r="C7" s="6" t="inlineStr">
+      <c r="C7" s="8" t="inlineStr">
         <is>
           <t>终端批量操作</t>
         </is>
       </c>
-      <c r="D7" s="6" t="inlineStr">
+      <c r="D7" s="8" t="inlineStr">
         <is>
           <t>R-MC-001</t>
         </is>
       </c>
-      <c r="E7" s="6" t="inlineStr">
+      <c r="E7" s="8" t="inlineStr">
         <is>
           <t>对终端集合批量操作：移动端批量安装/卸载App、重启、截图；浏览器Profile批量创建/启动/关闭/截图；经对象存储临时链接上传下载。</t>
         </is>
       </c>
-      <c r="F7" s="6" t="inlineStr">
+      <c r="F7" s="8" t="inlineStr">
         <is>
           <t>移动端批量(安装/卸载/重启/截图)；Profile批量(创建/启动/关闭/截图)；对象存储临时链接</t>
         </is>
       </c>
-      <c r="G7" s="6" t="inlineStr">
+      <c r="G7" s="8" t="inlineStr">
         <is>
           <t>SRS R-MC-001</t>
         </is>
       </c>
-      <c r="H7" s="6" t="inlineStr">
+      <c r="H7" s="8" t="inlineStr">
         <is>
           <t>对接 EI-05</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="66" customHeight="1">
-      <c r="A8" s="4" t="inlineStr">
+    <row r="8">
+      <c r="A8" s="11" t="inlineStr">
         <is>
           <t>②模块</t>
         </is>
       </c>
-      <c r="B8" s="4" t="inlineStr">
+      <c r="B8" s="11" t="inlineStr">
         <is>
           <t>M-MC-02</t>
         </is>
       </c>
-      <c r="C8" s="5" t="inlineStr">
+      <c r="C8" s="11" t="inlineStr">
         <is>
           <t>终端指纹与环境隔离（终端身份伪造与隔离底座）</t>
         </is>
       </c>
-      <c r="D8" s="4" t="inlineStr">
+      <c r="D8" s="11" t="inlineStr">
         <is>
           <t>R-MC-001(风控基建)</t>
         </is>
       </c>
-      <c r="E8" s="5" t="inlineStr">
+      <c r="E8" s="11" t="inlineStr">
         <is>
           <t>通过终端指纹管理（移动端硬件指纹 + 桌面端 Profile 指纹固化）、代理分配固定绑定、终端间环境隔离，让终端长期呈现稳定真人身份且互不关联，降低被风控识别的概率。</t>
         </is>
       </c>
-      <c r="F8" s="5" t="inlineStr">
+      <c r="F8" s="11" t="inlineStr">
         <is>
           <t>F-MC-02-01 浏览器 Profile 指纹固化；F-MC-02-02 移动端设备指纹管理；F-MC-02-03 代理分配与固定绑定；F-MC-02-04 终端间环境隔离</t>
         </is>
       </c>
-      <c r="G8" s="5" t="inlineStr">
+      <c r="G8" s="11" t="inlineStr">
         <is>
           <t>SRS R-MC-001(风控基建)</t>
         </is>
       </c>
-      <c r="H8" s="5" t="inlineStr">
+      <c r="H8" s="11" t="inlineStr">
         <is>
           <t>R-MC-001 的『让终端像真人且互不关联』是风控基建关注点（指纹/代理/隔离），与接入台账、健康感知分离。</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="49.5" customHeight="1">
-      <c r="A9" s="6" t="inlineStr">
-        <is>
-          <t>③功能</t>
-        </is>
-      </c>
-      <c r="B9" s="6" t="inlineStr">
+    <row r="9">
+      <c r="A9" s="8" t="inlineStr">
+        <is>
+          <t>③功能</t>
+        </is>
+      </c>
+      <c r="B9" s="8" t="inlineStr">
         <is>
           <t>F-MC-02-01</t>
         </is>
       </c>
-      <c r="C9" s="6" t="inlineStr">
+      <c r="C9" s="8" t="inlineStr">
         <is>
           <t>浏览器 Profile 指纹固化</t>
         </is>
       </c>
-      <c r="D9" s="6" t="inlineStr">
+      <c r="D9" s="8" t="inlineStr">
         <is>
           <t>R-MC-001</t>
         </is>
       </c>
-      <c r="E9" s="6" t="inlineStr">
+      <c r="E9" s="8" t="inlineStr">
         <is>
           <t>Profile 创建时生成并固化 20+ 维渲染层指纹(Canvas/WebGL/字体/时区/Audio/UA)，使 Profile 长期呈现一致的设备身份；一Profile对应一套固化指纹与一账号身份。</t>
         </is>
       </c>
-      <c r="F9" s="6" t="inlineStr">
+      <c r="F9" s="8" t="inlineStr">
         <is>
           <t>20+维指纹固化；指纹长期一致；一Profile一身份</t>
         </is>
       </c>
-      <c r="G9" s="6" t="inlineStr">
+      <c r="G9" s="8" t="inlineStr">
         <is>
           <t>SRS R-MC-001；CON-12</t>
         </is>
       </c>
-      <c r="H9" s="6" t="inlineStr"/>
-    </row>
-    <row r="10" ht="33" customHeight="1">
-      <c r="A10" s="6" t="inlineStr">
-        <is>
-          <t>③功能</t>
-        </is>
-      </c>
-      <c r="B10" s="6" t="inlineStr">
+      <c r="H9" s="8" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="8" t="inlineStr">
+        <is>
+          <t>③功能</t>
+        </is>
+      </c>
+      <c r="B10" s="8" t="inlineStr">
         <is>
           <t>F-MC-02-02</t>
         </is>
       </c>
-      <c r="C10" s="6" t="inlineStr">
+      <c r="C10" s="8" t="inlineStr">
         <is>
           <t>移动端设备指纹管理</t>
         </is>
       </c>
-      <c r="D10" s="6" t="inlineStr">
+      <c r="D10" s="8" t="inlineStr">
         <is>
           <t>R-MC-001</t>
         </is>
       </c>
-      <c r="E10" s="6" t="inlineStr">
+      <c r="E10" s="8" t="inlineStr">
         <is>
           <t>管理真机/云手机/ARM板卡/虚拟化真机等移动端设备的硬件与软件指纹，支持按需配置。</t>
         </is>
       </c>
-      <c r="F10" s="6" t="inlineStr">
+      <c r="F10" s="8" t="inlineStr">
         <is>
           <t>移动端硬件/软件指纹管理；按需配置</t>
         </is>
       </c>
-      <c r="G10" s="6" t="inlineStr">
+      <c r="G10" s="8" t="inlineStr">
         <is>
           <t>SRS R-MC-001</t>
         </is>
       </c>
-      <c r="H10" s="6" t="inlineStr"/>
-    </row>
-    <row r="11" ht="33" customHeight="1">
-      <c r="A11" s="6" t="inlineStr">
-        <is>
-          <t>③功能</t>
-        </is>
-      </c>
-      <c r="B11" s="6" t="inlineStr">
+      <c r="H10" s="8" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="8" t="inlineStr">
+        <is>
+          <t>③功能</t>
+        </is>
+      </c>
+      <c r="B11" s="8" t="inlineStr">
         <is>
           <t>F-MC-02-03</t>
         </is>
       </c>
-      <c r="C11" s="6" t="inlineStr">
+      <c r="C11" s="8" t="inlineStr">
         <is>
           <t>代理分配与固定绑定</t>
         </is>
       </c>
-      <c r="D11" s="6" t="inlineStr">
+      <c r="D11" s="8" t="inlineStr">
         <is>
           <t>R-MC-001</t>
         </is>
       </c>
-      <c r="E11" s="6" t="inlineStr">
+      <c r="E11" s="8" t="inlineStr">
         <is>
           <t>为每个执行终端分配独立代理 IP 并固定绑定（一终端一IP），实现网络环境隔离；代理默认随终端固定，仅失效时切换并重新固定。</t>
         </is>
       </c>
-      <c r="F11" s="6" t="inlineStr">
+      <c r="F11" s="8" t="inlineStr">
         <is>
           <t>一终端一IP；代理固定绑定；失效时切换重新固定</t>
         </is>
       </c>
-      <c r="G11" s="6" t="inlineStr">
+      <c r="G11" s="8" t="inlineStr">
         <is>
           <t>SRS R-MC-001</t>
         </is>
       </c>
-      <c r="H11" s="6" t="inlineStr">
+      <c r="H11" s="8" t="inlineStr">
         <is>
           <t>对接 EI-02</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="33" customHeight="1">
-      <c r="A12" s="6" t="inlineStr">
-        <is>
-          <t>③功能</t>
-        </is>
-      </c>
-      <c r="B12" s="6" t="inlineStr">
+    <row r="12">
+      <c r="A12" s="8" t="inlineStr">
+        <is>
+          <t>③功能</t>
+        </is>
+      </c>
+      <c r="B12" s="8" t="inlineStr">
         <is>
           <t>F-MC-02-04</t>
         </is>
       </c>
-      <c r="C12" s="6" t="inlineStr">
+      <c r="C12" s="8" t="inlineStr">
         <is>
           <t>终端间环境隔离</t>
         </is>
       </c>
-      <c r="D12" s="6" t="inlineStr">
+      <c r="D12" s="8" t="inlineStr">
         <is>
           <t>R-MC-001</t>
         </is>
       </c>
-      <c r="E12" s="6" t="inlineStr">
+      <c r="E12" s="8" t="inlineStr">
         <is>
           <t>对终端间指纹、网络、账号、Cookie/缓存相互隔离；浏览器Profile间Cookie/LocalStorage/缓存独立隔离。</t>
         </is>
       </c>
-      <c r="F12" s="6" t="inlineStr">
+      <c r="F12" s="8" t="inlineStr">
         <is>
           <t>指纹/网络/账号/Cookie隔离；Profile间独立隔离</t>
         </is>
       </c>
-      <c r="G12" s="6" t="inlineStr">
+      <c r="G12" s="8" t="inlineStr">
         <is>
           <t>SRS R-MC-001</t>
         </is>
       </c>
-      <c r="H12" s="6" t="inlineStr"/>
-    </row>
-    <row r="13" ht="66" customHeight="1">
-      <c r="A13" s="4" t="inlineStr">
+      <c r="H12" s="8" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="11" t="inlineStr">
         <is>
           <t>②模块</t>
         </is>
       </c>
-      <c r="B13" s="4" t="inlineStr">
+      <c r="B13" s="11" t="inlineStr">
         <is>
           <t>M-MC-03</t>
         </is>
       </c>
-      <c r="C13" s="5" t="inlineStr">
+      <c r="C13" s="11" t="inlineStr">
         <is>
           <t>终端监控与风控对抗（终端健康哨兵与风控对抗）</t>
         </is>
       </c>
-      <c r="D13" s="4" t="inlineStr">
+      <c r="D13" s="11" t="inlineStr">
         <is>
           <t>R-MC-001(健康感知)</t>
         </is>
       </c>
-      <c r="E13" s="5" t="inlineStr">
+      <c r="E13" s="11" t="inlineStr">
         <is>
           <t>持续监控终端状态指标，按指纹真实度进行风控分级，识别平台风控信号并采取规避策略；指标异常或风控持续触发时降级或暂停终端任务。</t>
         </is>
       </c>
-      <c r="F13" s="5" t="inlineStr">
+      <c r="F13" s="11" t="inlineStr">
         <is>
           <t>F-MC-03-01 终端状态与指标监控；F-MC-03-02 设备风控分级；F-MC-03-03 风控信号识别与规避</t>
         </is>
       </c>
-      <c r="G13" s="5" t="inlineStr">
+      <c r="G13" s="11" t="inlineStr">
         <is>
           <t>SRS R-MC-001(健康感知)</t>
         </is>
       </c>
-      <c r="H13" s="5" t="inlineStr">
+      <c r="H13" s="11" t="inlineStr">
         <is>
           <t>R-MC-001 的『终端健康感知与风险应对』是独立关注点（监控+风控对抗），与接入台账、指纹环境分离。</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="33" customHeight="1">
-      <c r="A14" s="6" t="inlineStr">
-        <is>
-          <t>③功能</t>
-        </is>
-      </c>
-      <c r="B14" s="6" t="inlineStr">
+    <row r="14">
+      <c r="A14" s="8" t="inlineStr">
+        <is>
+          <t>③功能</t>
+        </is>
+      </c>
+      <c r="B14" s="8" t="inlineStr">
         <is>
           <t>F-MC-03-01</t>
         </is>
       </c>
-      <c r="C14" s="6" t="inlineStr">
+      <c r="C14" s="8" t="inlineStr">
         <is>
           <t>终端状态与指标监控</t>
         </is>
       </c>
-      <c r="D14" s="6" t="inlineStr">
+      <c r="D14" s="8" t="inlineStr">
         <is>
           <t>R-MC-001</t>
         </is>
       </c>
-      <c r="E14" s="6" t="inlineStr">
+      <c r="E14" s="8" t="inlineStr">
         <is>
           <t>持续采集并监控移动端在线/离线状态、电量、CPU、内存、存储、网络，以及浏览器 Profile 运行状态与资源占用。</t>
         </is>
       </c>
-      <c r="F14" s="6" t="inlineStr">
+      <c r="F14" s="8" t="inlineStr">
         <is>
           <t>移动端多指标监控；Profile 运行状态监控</t>
         </is>
       </c>
-      <c r="G14" s="6" t="inlineStr">
+      <c r="G14" s="8" t="inlineStr">
         <is>
           <t>SRS R-MC-001</t>
         </is>
       </c>
-      <c r="H14" s="6" t="inlineStr"/>
-    </row>
-    <row r="15" ht="33" customHeight="1">
-      <c r="A15" s="6" t="inlineStr">
-        <is>
-          <t>③功能</t>
-        </is>
-      </c>
-      <c r="B15" s="6" t="inlineStr">
+      <c r="H14" s="8" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="8" t="inlineStr">
+        <is>
+          <t>③功能</t>
+        </is>
+      </c>
+      <c r="B15" s="8" t="inlineStr">
         <is>
           <t>F-MC-03-02</t>
         </is>
       </c>
-      <c r="C15" s="6" t="inlineStr">
+      <c r="C15" s="8" t="inlineStr">
         <is>
           <t>设备风控分级</t>
         </is>
       </c>
-      <c r="D15" s="6" t="inlineStr">
+      <c r="D15" s="8" t="inlineStr">
         <is>
           <t>R-MC-001</t>
         </is>
       </c>
-      <c r="E15" s="6" t="inlineStr">
+      <c r="E15" s="8" t="inlineStr">
         <is>
           <t>按指纹真实度对终端风控分级：真机与ARM板卡(高)、虚拟化真机(中高)、云手机与浏览器Profile(中)；养号等敏感场景优先选用高真实度终端。</t>
         </is>
       </c>
-      <c r="F15" s="6" t="inlineStr">
+      <c r="F15" s="8" t="inlineStr">
         <is>
           <t>按指纹真实度分级；养号优先高真实度终端</t>
         </is>
       </c>
-      <c r="G15" s="6" t="inlineStr">
+      <c r="G15" s="8" t="inlineStr">
         <is>
           <t>SRS R-MC-001；CON-09</t>
         </is>
       </c>
-      <c r="H15" s="6" t="inlineStr"/>
-    </row>
-    <row r="16" ht="33" customHeight="1">
-      <c r="A16" s="6" t="inlineStr">
-        <is>
-          <t>③功能</t>
-        </is>
-      </c>
-      <c r="B16" s="6" t="inlineStr">
+      <c r="H15" s="8" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="8" t="inlineStr">
+        <is>
+          <t>③功能</t>
+        </is>
+      </c>
+      <c r="B16" s="8" t="inlineStr">
         <is>
           <t>F-MC-03-03</t>
         </is>
       </c>
-      <c r="C16" s="6" t="inlineStr">
+      <c r="C16" s="8" t="inlineStr">
         <is>
           <t>风控信号识别与规避</t>
         </is>
       </c>
-      <c r="D16" s="6" t="inlineStr">
+      <c r="D16" s="8" t="inlineStr">
         <is>
           <t>R-MC-001</t>
         </is>
       </c>
-      <c r="E16" s="6" t="inlineStr">
+      <c r="E16" s="8" t="inlineStr">
         <is>
           <t>识别平台风控信号并采取规避与应对策略（覆盖移动端与桌面端），风控信号持续触发时降级或暂停该终端任务。</t>
         </is>
       </c>
-      <c r="F16" s="6" t="inlineStr">
+      <c r="F16" s="8" t="inlineStr">
         <is>
           <t>风控信号识别；规避策略；持续触发降级/暂停</t>
         </is>
       </c>
-      <c r="G16" s="6" t="inlineStr">
+      <c r="G16" s="8" t="inlineStr">
         <is>
           <t>SRS R-MC-001</t>
         </is>
       </c>
-      <c r="H16" s="6" t="inlineStr"/>
-    </row>
-    <row r="17" ht="33" customHeight="1">
-      <c r="A17" s="4" t="inlineStr">
+      <c r="H16" s="8" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="11" t="inlineStr">
         <is>
           <t>②模块</t>
         </is>
       </c>
-      <c r="B17" s="4" t="inlineStr">
+      <c r="B17" s="11" t="inlineStr">
         <is>
           <t>M-MC-04</t>
         </is>
       </c>
-      <c r="C17" s="5" t="inlineStr">
+      <c r="C17" s="11" t="inlineStr">
         <is>
           <t>远程控制（人机交互窗口）</t>
         </is>
       </c>
-      <c r="D17" s="4" t="inlineStr">
+      <c r="D17" s="11" t="inlineStr">
         <is>
           <t>R-MC-002</t>
         </is>
       </c>
-      <c r="E17" s="5" t="inlineStr">
+      <c r="E17" s="11" t="inlineStr">
         <is>
           <t>对单台及多台终端提供低延迟实时画面预览与输入控制，支持多终端同屏监控；移动端用 WebRTC、桌面端浏览器 Profile 用 RDP。</t>
         </is>
       </c>
-      <c r="F17" s="5" t="inlineStr">
+      <c r="F17" s="11" t="inlineStr">
         <is>
           <t>F-MC-04-01 移动端 WebRTC 远控；F-MC-04-02 桌面端 RDP 远控；F-MC-04-03 多终端宫格监控；F-MC-04-04 剪贴板双向同步</t>
         </is>
       </c>
-      <c r="G17" s="5" t="inlineStr">
+      <c r="G17" s="11" t="inlineStr">
         <is>
           <t>SRS R-MC-002</t>
         </is>
       </c>
-      <c r="H17" s="5" t="inlineStr">
+      <c r="H17" s="11" t="inlineStr">
         <is>
           <t>对应 R-MC-002 远控，远控通道与任务执行通道相互分离。</t>
         </is>
       </c>
     </row>
-    <row r="18" ht="33" customHeight="1">
-      <c r="A18" s="6" t="inlineStr">
-        <is>
-          <t>③功能</t>
-        </is>
-      </c>
-      <c r="B18" s="6" t="inlineStr">
+    <row r="18">
+      <c r="A18" s="8" t="inlineStr">
+        <is>
+          <t>③功能</t>
+        </is>
+      </c>
+      <c r="B18" s="8" t="inlineStr">
         <is>
           <t>F-MC-04-01</t>
         </is>
       </c>
-      <c r="C18" s="6" t="inlineStr">
+      <c r="C18" s="8" t="inlineStr">
         <is>
           <t>移动端 WebRTC 远控</t>
         </is>
       </c>
-      <c r="D18" s="6" t="inlineStr">
+      <c r="D18" s="8" t="inlineStr">
         <is>
           <t>R-MC-002</t>
         </is>
       </c>
-      <c r="E18" s="6" t="inlineStr">
+      <c r="E18" s="8" t="inlineStr">
         <is>
           <t>移动端屏幕画面基于 WebRTC 传输，鼠标键盘事件映射为触摸/点击/滑动/输入及返回/Home/多任务键；支持截图与录屏采集保存回看；弱网自动降帧。</t>
         </is>
       </c>
-      <c r="F18" s="6" t="inlineStr">
+      <c r="F18" s="8" t="inlineStr">
         <is>
           <t>WebRTC画面传输；事件映射；截图录屏；端到端≤300ms；弱网降帧</t>
         </is>
       </c>
-      <c r="G18" s="6" t="inlineStr">
+      <c r="G18" s="8" t="inlineStr">
         <is>
           <t>SRS R-MC-002；NR-P-01/05</t>
         </is>
       </c>
-      <c r="H18" s="6" t="inlineStr">
+      <c r="H18" s="8" t="inlineStr">
         <is>
           <t>对接 II-03</t>
         </is>
       </c>
     </row>
-    <row r="19" ht="33" customHeight="1">
-      <c r="A19" s="6" t="inlineStr">
-        <is>
-          <t>③功能</t>
-        </is>
-      </c>
-      <c r="B19" s="6" t="inlineStr">
+    <row r="19">
+      <c r="A19" s="8" t="inlineStr">
+        <is>
+          <t>③功能</t>
+        </is>
+      </c>
+      <c r="B19" s="8" t="inlineStr">
         <is>
           <t>F-MC-04-02</t>
         </is>
       </c>
-      <c r="C19" s="6" t="inlineStr">
+      <c r="C19" s="8" t="inlineStr">
         <is>
           <t>桌面端 RDP 远控</t>
         </is>
       </c>
-      <c r="D19" s="6" t="inlineStr">
+      <c r="D19" s="8" t="inlineStr">
         <is>
           <t>R-MC-002</t>
         </is>
       </c>
-      <c r="E19" s="6" t="inlineStr">
+      <c r="E19" s="8" t="inlineStr">
         <is>
           <t>桌面端浏览器 Profile 基于 RDP 传输画面，鼠标点击与键盘输入映射为桌面事件；远控通道与任务执行通道相互分离。</t>
         </is>
       </c>
-      <c r="F19" s="6" t="inlineStr">
+      <c r="F19" s="8" t="inlineStr">
         <is>
           <t>RDP画面传输；鼠标键盘映射；远控与执行通道分离</t>
         </is>
       </c>
-      <c r="G19" s="6" t="inlineStr">
+      <c r="G19" s="8" t="inlineStr">
         <is>
           <t>SRS R-MC-002</t>
         </is>
       </c>
-      <c r="H19" s="6" t="inlineStr"/>
+      <c r="H19" s="8" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="6" t="inlineStr">
-        <is>
-          <t>③功能</t>
-        </is>
-      </c>
-      <c r="B20" s="6" t="inlineStr">
+      <c r="A20" s="8" t="inlineStr">
+        <is>
+          <t>③功能</t>
+        </is>
+      </c>
+      <c r="B20" s="8" t="inlineStr">
         <is>
           <t>F-MC-04-03</t>
         </is>
       </c>
-      <c r="C20" s="6" t="inlineStr">
+      <c r="C20" s="8" t="inlineStr">
         <is>
           <t>多终端宫格监控</t>
         </is>
       </c>
-      <c r="D20" s="6" t="inlineStr">
+      <c r="D20" s="8" t="inlineStr">
         <is>
           <t>R-MC-002</t>
         </is>
       </c>
-      <c r="E20" s="6" t="inlineStr">
+      <c r="E20" s="8" t="inlineStr">
         <is>
           <t>以低码率同屏预览多台终端，供监控人员宫格监控。</t>
         </is>
       </c>
-      <c r="F20" s="6" t="inlineStr">
+      <c r="F20" s="8" t="inlineStr">
         <is>
           <t>低码率宫格同屏预览</t>
         </is>
       </c>
-      <c r="G20" s="6" t="inlineStr">
+      <c r="G20" s="8" t="inlineStr">
         <is>
           <t>SRS R-MC-002</t>
         </is>
       </c>
-      <c r="H20" s="6" t="inlineStr"/>
+      <c r="H20" s="8" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="6" t="inlineStr">
-        <is>
-          <t>③功能</t>
-        </is>
-      </c>
-      <c r="B21" s="6" t="inlineStr">
+      <c r="A21" s="8" t="inlineStr">
+        <is>
+          <t>③功能</t>
+        </is>
+      </c>
+      <c r="B21" s="8" t="inlineStr">
         <is>
           <t>F-MC-04-04</t>
         </is>
       </c>
-      <c r="C21" s="6" t="inlineStr">
+      <c r="C21" s="8" t="inlineStr">
         <is>
           <t>剪贴板双向同步</t>
         </is>
       </c>
-      <c r="D21" s="6" t="inlineStr">
+      <c r="D21" s="8" t="inlineStr">
         <is>
           <t>R-MC-002</t>
         </is>
       </c>
-      <c r="E21" s="6" t="inlineStr">
+      <c r="E21" s="8" t="inlineStr">
         <is>
           <t>剪贴板在操作端与终端间双向同步。</t>
         </is>
       </c>
-      <c r="F21" s="6" t="inlineStr">
+      <c r="F21" s="8" t="inlineStr">
         <is>
           <t>剪贴板双向同步</t>
         </is>
       </c>
-      <c r="G21" s="6" t="inlineStr">
+      <c r="G21" s="8" t="inlineStr">
         <is>
           <t>SRS R-MC-002</t>
         </is>
       </c>
-      <c r="H21" s="6" t="inlineStr"/>
-    </row>
-    <row r="22" ht="66" customHeight="1">
-      <c r="A22" s="4" t="inlineStr">
+      <c r="H21" s="8" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="11" t="inlineStr">
         <is>
           <t>②模块</t>
         </is>
       </c>
-      <c r="B22" s="4" t="inlineStr">
+      <c r="B22" s="11" t="inlineStr">
         <is>
           <t>M-MC-05</t>
         </is>
       </c>
-      <c r="C22" s="5" t="inlineStr">
+      <c r="C22" s="11" t="inlineStr">
         <is>
           <t>执行网关与双执行模式（统一执行网关（核心））</t>
         </is>
       </c>
-      <c r="D22" s="4" t="inlineStr">
+      <c r="D22" s="11" t="inlineStr">
         <is>
           <t>R-MC-003</t>
         </is>
       </c>
-      <c r="E22" s="5" t="inlineStr">
+      <c r="E22" s="11" t="inlineStr">
         <is>
           <t>以统一执行网关作为所有终端动作的唯一收口，提供脚本模式与智能体模式两种执行引擎，按终端类型适配控制通道（移动端ADB/无障碍、桌面端CDP），支持群控、养号与内容投放三类执行目标。</t>
         </is>
       </c>
-      <c r="F22" s="5" t="inlineStr">
+      <c r="F22" s="11" t="inlineStr">
         <is>
           <t>F-MC-05-01 脚本模式执行引擎；F-MC-05-02 智能体模式执行引擎；F-MC-05-03 控制通道适配；F-MC-05-04 统一执行网关（鉴权/记录/熔断/转发）；F-MC-05-05 三类执行目标</t>
         </is>
       </c>
-      <c r="G22" s="5" t="inlineStr">
+      <c r="G22" s="11" t="inlineStr">
         <is>
           <t>SRS R-MC-003</t>
         </is>
       </c>
-      <c r="H22" s="5" t="inlineStr">
+      <c r="H22" s="11" t="inlineStr">
         <is>
           <t>对应 R-MC-003，是 MC 的核心枢纽；动作收口（CON-07）与推理执行分离（CON-10）两条原则的落地。</t>
         </is>
       </c>
     </row>
-    <row r="23" ht="33" customHeight="1">
-      <c r="A23" s="6" t="inlineStr">
-        <is>
-          <t>③功能</t>
-        </is>
-      </c>
-      <c r="B23" s="6" t="inlineStr">
+    <row r="23">
+      <c r="A23" s="8" t="inlineStr">
+        <is>
+          <t>③功能</t>
+        </is>
+      </c>
+      <c r="B23" s="8" t="inlineStr">
         <is>
           <t>F-MC-05-01</t>
         </is>
       </c>
-      <c r="C23" s="6" t="inlineStr">
+      <c r="C23" s="8" t="inlineStr">
         <is>
           <t>脚本模式执行引擎</t>
         </is>
       </c>
-      <c r="D23" s="6" t="inlineStr">
+      <c r="D23" s="8" t="inlineStr">
         <is>
           <t>R-MC-003</t>
         </is>
       </c>
-      <c r="E23" s="6" t="inlineStr">
+      <c r="E23" s="8" t="inlineStr">
         <is>
           <t>由预先编写的固定流程驱动终端动作，适用于流程确定、高频、批量作业。</t>
         </is>
       </c>
-      <c r="F23" s="6" t="inlineStr">
+      <c r="F23" s="8" t="inlineStr">
         <is>
           <t>固定流程驱动；适配移动端与桌面端</t>
         </is>
       </c>
-      <c r="G23" s="6" t="inlineStr">
+      <c r="G23" s="8" t="inlineStr">
         <is>
           <t>SRS R-MC-003；CON-08</t>
         </is>
       </c>
-      <c r="H23" s="6" t="inlineStr"/>
-    </row>
-    <row r="24" ht="33" customHeight="1">
-      <c r="A24" s="6" t="inlineStr">
-        <is>
-          <t>③功能</t>
-        </is>
-      </c>
-      <c r="B24" s="6" t="inlineStr">
+      <c r="H23" s="8" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="8" t="inlineStr">
+        <is>
+          <t>③功能</t>
+        </is>
+      </c>
+      <c r="B24" s="8" t="inlineStr">
         <is>
           <t>F-MC-05-02</t>
         </is>
       </c>
-      <c r="C24" s="6" t="inlineStr">
+      <c r="C24" s="8" t="inlineStr">
         <is>
           <t>智能体模式执行引擎</t>
         </is>
       </c>
-      <c r="D24" s="6" t="inlineStr">
+      <c r="D24" s="8" t="inlineStr">
         <is>
           <t>R-MC-003</t>
         </is>
       </c>
-      <c r="E24" s="6" t="inlineStr">
+      <c r="E24" s="8" t="inlineStr">
         <is>
           <t>由终端 Agent 调用 IRS 本地大模型进行视觉推理与规划自主决策动作；推理不经网关，产出的动作指令再经网关落地。</t>
         </is>
       </c>
-      <c r="F24" s="6" t="inlineStr">
+      <c r="F24" s="8" t="inlineStr">
         <is>
           <t>大模型视觉推理决策；推理不经网关；动作经网关落地</t>
         </is>
       </c>
-      <c r="G24" s="6" t="inlineStr">
+      <c r="G24" s="8" t="inlineStr">
         <is>
           <t>SRS R-MC-003；CON-10</t>
         </is>
       </c>
-      <c r="H24" s="6" t="inlineStr">
+      <c r="H24" s="8" t="inlineStr">
         <is>
           <t>对接 EI-06/II-08</t>
         </is>
       </c>
     </row>
-    <row r="25" ht="33" customHeight="1">
-      <c r="A25" s="6" t="inlineStr">
-        <is>
-          <t>③功能</t>
-        </is>
-      </c>
-      <c r="B25" s="6" t="inlineStr">
+    <row r="25">
+      <c r="A25" s="8" t="inlineStr">
+        <is>
+          <t>③功能</t>
+        </is>
+      </c>
+      <c r="B25" s="8" t="inlineStr">
         <is>
           <t>F-MC-05-03</t>
         </is>
       </c>
-      <c r="C25" s="6" t="inlineStr">
+      <c r="C25" s="8" t="inlineStr">
         <is>
           <t>控制通道适配</t>
         </is>
       </c>
-      <c r="D25" s="6" t="inlineStr">
+      <c r="D25" s="8" t="inlineStr">
         <is>
           <t>R-MC-003</t>
         </is>
       </c>
-      <c r="E25" s="6" t="inlineStr">
+      <c r="E25" s="8" t="inlineStr">
         <is>
           <t>两种模式按终端类型适配底层控制通道：移动端用 ADB/无障碍，桌面端浏览器Profile用 CDP；通道对上层透明。</t>
         </is>
       </c>
-      <c r="F25" s="6" t="inlineStr">
+      <c r="F25" s="8" t="inlineStr">
         <is>
           <t>移动端ADB/无障碍；桌面端CDP；对上层透明</t>
         </is>
       </c>
-      <c r="G25" s="6" t="inlineStr">
+      <c r="G25" s="8" t="inlineStr">
         <is>
           <t>SRS R-MC-003</t>
         </is>
       </c>
-      <c r="H25" s="6" t="inlineStr"/>
-    </row>
-    <row r="26" ht="33" customHeight="1">
-      <c r="A26" s="6" t="inlineStr">
-        <is>
-          <t>③功能</t>
-        </is>
-      </c>
-      <c r="B26" s="6" t="inlineStr">
+      <c r="H25" s="8" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="8" t="inlineStr">
+        <is>
+          <t>③功能</t>
+        </is>
+      </c>
+      <c r="B26" s="8" t="inlineStr">
         <is>
           <t>F-MC-05-04</t>
         </is>
       </c>
-      <c r="C26" s="6" t="inlineStr">
+      <c r="C26" s="8" t="inlineStr">
         <is>
           <t>统一执行网关（鉴权/记录/熔断/转发）</t>
         </is>
       </c>
-      <c r="D26" s="6" t="inlineStr">
+      <c r="D26" s="8" t="inlineStr">
         <is>
           <t>R-MC-003</t>
         </is>
       </c>
-      <c r="E26" s="6" t="inlineStr">
+      <c r="E26" s="8" t="inlineStr">
         <is>
           <t>所有终端动作经网关落地：鉴权(校验来源与目标合法性)、记录(写动作日志全量上报OM)、熔断(检测风控信号或异常频率时停止后续)、转发。</t>
         </is>
       </c>
-      <c r="F26" s="6" t="inlineStr">
+      <c r="F26" s="8" t="inlineStr">
         <is>
           <t>动作鉴权；动作记录全量上报；异常熔断；转发落地</t>
         </is>
       </c>
-      <c r="G26" s="6" t="inlineStr">
+      <c r="G26" s="8" t="inlineStr">
         <is>
           <t>SRS R-MC-003；CON-07</t>
         </is>
       </c>
-      <c r="H26" s="6" t="inlineStr">
+      <c r="H26" s="8" t="inlineStr">
         <is>
           <t>对接 II-07/II-12</t>
         </is>
       </c>
     </row>
-    <row r="27" ht="49.5" customHeight="1">
-      <c r="A27" s="6" t="inlineStr">
-        <is>
-          <t>③功能</t>
-        </is>
-      </c>
-      <c r="B27" s="6" t="inlineStr">
+    <row r="27">
+      <c r="A27" s="8" t="inlineStr">
+        <is>
+          <t>③功能</t>
+        </is>
+      </c>
+      <c r="B27" s="8" t="inlineStr">
         <is>
           <t>F-MC-05-05</t>
         </is>
       </c>
-      <c r="C27" s="6" t="inlineStr">
+      <c r="C27" s="8" t="inlineStr">
         <is>
           <t>三类执行目标</t>
         </is>
       </c>
-      <c r="D27" s="6" t="inlineStr">
+      <c r="D27" s="8" t="inlineStr">
         <is>
           <t>R-MC-003</t>
         </is>
       </c>
-      <c r="E27" s="6" t="inlineStr">
+      <c r="E27" s="8" t="inlineStr">
         <is>
           <t>支撑群控(多台终端同步控制统一投放)、养号(认知作战账号经ADB/无障碍、爬虫账号经CDP，拟人化节奏由M-MC-07内置)、内容投放(下发发布素材到目标账号)三类执行目标。</t>
         </is>
       </c>
-      <c r="F27" s="6" t="inlineStr">
+      <c r="F27" s="8" t="inlineStr">
         <is>
           <t>群控；养号(移动端ADB/桌面端CDP)；内容投放</t>
         </is>
       </c>
-      <c r="G27" s="6" t="inlineStr">
+      <c r="G27" s="8" t="inlineStr">
         <is>
           <t>SRS R-MC-003</t>
         </is>
       </c>
-      <c r="H27" s="6" t="inlineStr"/>
-    </row>
-    <row r="28" ht="49.5" customHeight="1">
-      <c r="A28" s="4" t="inlineStr">
+      <c r="H27" s="8" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="11" t="inlineStr">
         <is>
           <t>②模块</t>
         </is>
       </c>
-      <c r="B28" s="4" t="inlineStr">
+      <c r="B28" s="11" t="inlineStr">
         <is>
           <t>M-MC-06</t>
         </is>
       </c>
-      <c r="C28" s="5" t="inlineStr">
+      <c r="C28" s="11" t="inlineStr">
         <is>
           <t>任务管理（任务调度中枢）</t>
         </is>
       </c>
-      <c r="D28" s="4" t="inlineStr">
+      <c r="D28" s="11" t="inlineStr">
         <is>
           <t>R-MC-004</t>
         </is>
       </c>
-      <c r="E28" s="5" t="inlineStr">
+      <c r="E28" s="11" t="inlineStr">
         <is>
           <t>把操作意图转换为设备可执行的任务并调度，支撑各类作业的排队、分发、重试与定时执行。</t>
         </is>
       </c>
-      <c r="F28" s="5" t="inlineStr">
+      <c r="F28" s="11" t="inlineStr">
         <is>
           <t>F-MC-06-01 任务创建与实例化；F-MC-06-02 多任务类型；F-MC-06-03 任务状态机流转；F-MC-06-04 失败重试与超时配置；F-MC-06-05 计划任务与定时调度</t>
         </is>
       </c>
-      <c r="G28" s="5" t="inlineStr">
+      <c r="G28" s="11" t="inlineStr">
         <is>
           <t>SRS R-MC-004</t>
         </is>
       </c>
-      <c r="H28" s="5" t="inlineStr">
+      <c r="H28" s="11" t="inlineStr">
         <is>
           <t>对应 R-MC-004 任务调度。</t>
         </is>
       </c>
     </row>
-    <row r="29" ht="33" customHeight="1">
-      <c r="A29" s="6" t="inlineStr">
-        <is>
-          <t>③功能</t>
-        </is>
-      </c>
-      <c r="B29" s="6" t="inlineStr">
+    <row r="29">
+      <c r="A29" s="8" t="inlineStr">
+        <is>
+          <t>③功能</t>
+        </is>
+      </c>
+      <c r="B29" s="8" t="inlineStr">
         <is>
           <t>F-MC-06-01</t>
         </is>
       </c>
-      <c r="C29" s="6" t="inlineStr">
+      <c r="C29" s="8" t="inlineStr">
         <is>
           <t>任务创建与实例化</t>
         </is>
       </c>
-      <c r="D29" s="6" t="inlineStr">
+      <c r="D29" s="8" t="inlineStr">
         <is>
           <t>R-MC-004</t>
         </is>
       </c>
-      <c r="E29" s="6" t="inlineStr">
+      <c r="E29" s="8" t="inlineStr">
         <is>
           <t>按任务定义选择设备或设备组，生成任务实例并入消息队列，由调度器分发到设备 Agent 执行。</t>
         </is>
       </c>
-      <c r="F29" s="6" t="inlineStr">
+      <c r="F29" s="8" t="inlineStr">
         <is>
           <t>任务定义→实例化→入队→分发</t>
         </is>
       </c>
-      <c r="G29" s="6" t="inlineStr">
+      <c r="G29" s="8" t="inlineStr">
         <is>
           <t>SRS R-MC-004</t>
         </is>
       </c>
-      <c r="H29" s="6" t="inlineStr"/>
-    </row>
-    <row r="30" ht="33" customHeight="1">
-      <c r="A30" s="6" t="inlineStr">
-        <is>
-          <t>③功能</t>
-        </is>
-      </c>
-      <c r="B30" s="6" t="inlineStr">
+      <c r="H29" s="8" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="8" t="inlineStr">
+        <is>
+          <t>③功能</t>
+        </is>
+      </c>
+      <c r="B30" s="8" t="inlineStr">
         <is>
           <t>F-MC-06-02</t>
         </is>
       </c>
-      <c r="C30" s="6" t="inlineStr">
+      <c r="C30" s="8" t="inlineStr">
         <is>
           <t>多任务类型</t>
         </is>
       </c>
-      <c r="D30" s="6" t="inlineStr">
+      <c r="D30" s="8" t="inlineStr">
         <is>
           <t>R-MC-004</t>
         </is>
       </c>
-      <c r="E30" s="6" t="inlineStr">
+      <c r="E30" s="8" t="inlineStr">
         <is>
           <t>支持 App安装启动、文件分发、内容发布、截图、数据采集、自动化脚本、设备巡检、账号状态检查等任务类型。</t>
         </is>
       </c>
-      <c r="F30" s="6" t="inlineStr">
+      <c r="F30" s="8" t="inlineStr">
         <is>
           <t>八类任务类型</t>
         </is>
       </c>
-      <c r="G30" s="6" t="inlineStr">
+      <c r="G30" s="8" t="inlineStr">
         <is>
           <t>SRS R-MC-004</t>
         </is>
       </c>
-      <c r="H30" s="6" t="inlineStr"/>
-    </row>
-    <row r="31" ht="33" customHeight="1">
-      <c r="A31" s="6" t="inlineStr">
-        <is>
-          <t>③功能</t>
-        </is>
-      </c>
-      <c r="B31" s="6" t="inlineStr">
+      <c r="H30" s="8" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="8" t="inlineStr">
+        <is>
+          <t>③功能</t>
+        </is>
+      </c>
+      <c r="B31" s="8" t="inlineStr">
         <is>
           <t>F-MC-06-03</t>
         </is>
       </c>
-      <c r="C31" s="6" t="inlineStr">
+      <c r="C31" s="8" t="inlineStr">
         <is>
           <t>任务状态机流转</t>
         </is>
       </c>
-      <c r="D31" s="6" t="inlineStr">
+      <c r="D31" s="8" t="inlineStr">
         <is>
           <t>R-MC-004</t>
         </is>
       </c>
-      <c r="E31" s="6" t="inlineStr">
+      <c r="E31" s="8" t="inlineStr">
         <is>
           <t>任务在待执行/排队中/执行中/成功/失败/已取消/超时/部分成功等状态间流转。</t>
         </is>
       </c>
-      <c r="F31" s="6" t="inlineStr">
+      <c r="F31" s="8" t="inlineStr">
         <is>
           <t>八态状态机流转</t>
         </is>
       </c>
-      <c r="G31" s="6" t="inlineStr">
+      <c r="G31" s="8" t="inlineStr">
         <is>
           <t>SRS R-MC-004</t>
         </is>
       </c>
-      <c r="H31" s="6" t="inlineStr"/>
+      <c r="H31" s="8" t="n"/>
     </row>
     <row r="32">
-      <c r="A32" s="6" t="inlineStr">
-        <is>
-          <t>③功能</t>
-        </is>
-      </c>
-      <c r="B32" s="6" t="inlineStr">
+      <c r="A32" s="8" t="inlineStr">
+        <is>
+          <t>③功能</t>
+        </is>
+      </c>
+      <c r="B32" s="8" t="inlineStr">
         <is>
           <t>F-MC-06-04</t>
         </is>
       </c>
-      <c r="C32" s="6" t="inlineStr">
+      <c r="C32" s="8" t="inlineStr">
         <is>
           <t>失败重试与超时配置</t>
         </is>
       </c>
-      <c r="D32" s="6" t="inlineStr">
+      <c r="D32" s="8" t="inlineStr">
         <is>
           <t>R-MC-004</t>
         </is>
       </c>
-      <c r="E32" s="6" t="inlineStr">
+      <c r="E32" s="8" t="inlineStr">
         <is>
           <t>支持失败重试、重试次数与超时配置；队列积压时按优先级调度并告警。</t>
         </is>
       </c>
-      <c r="F32" s="6" t="inlineStr">
+      <c r="F32" s="8" t="inlineStr">
         <is>
           <t>失败重试；重试次数/超时可配；优先级调度</t>
         </is>
       </c>
-      <c r="G32" s="6" t="inlineStr">
+      <c r="G32" s="8" t="inlineStr">
         <is>
           <t>SRS R-MC-004</t>
         </is>
       </c>
-      <c r="H32" s="6" t="inlineStr"/>
-    </row>
-    <row r="33" ht="33" customHeight="1">
-      <c r="A33" s="6" t="inlineStr">
-        <is>
-          <t>③功能</t>
-        </is>
-      </c>
-      <c r="B33" s="6" t="inlineStr">
+      <c r="H32" s="8" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="8" t="inlineStr">
+        <is>
+          <t>③功能</t>
+        </is>
+      </c>
+      <c r="B33" s="8" t="inlineStr">
         <is>
           <t>F-MC-06-05</t>
         </is>
       </c>
-      <c r="C33" s="6" t="inlineStr">
+      <c r="C33" s="8" t="inlineStr">
         <is>
           <t>计划任务与定时调度</t>
         </is>
       </c>
-      <c r="D33" s="6" t="inlineStr">
+      <c r="D33" s="8" t="inlineStr">
         <is>
           <t>R-MC-004</t>
         </is>
       </c>
-      <c r="E33" s="6" t="inlineStr">
+      <c r="E33" s="8" t="inlineStr">
         <is>
           <t>支持一次性、每日、每周与自定义 Cron 计划任务，支持最大并发数与任务优先级控制。</t>
         </is>
       </c>
-      <c r="F33" s="6" t="inlineStr">
+      <c r="F33" s="8" t="inlineStr">
         <is>
           <t>Cron定时(一次性/每日/每周/自定义)；最大并发；优先级</t>
         </is>
       </c>
-      <c r="G33" s="6" t="inlineStr">
+      <c r="G33" s="8" t="inlineStr">
         <is>
           <t>SRS R-MC-004</t>
         </is>
       </c>
-      <c r="H33" s="6" t="inlineStr"/>
-    </row>
-    <row r="34" ht="82.5" customHeight="1">
-      <c r="A34" s="4" t="inlineStr">
+      <c r="H33" s="8" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="11" t="inlineStr">
         <is>
           <t>②模块</t>
         </is>
       </c>
-      <c r="B34" s="4" t="inlineStr">
+      <c r="B34" s="11" t="inlineStr">
         <is>
           <t>M-MC-07</t>
         </is>
       </c>
-      <c r="C34" s="5" t="inlineStr">
+      <c r="C34" s="11" t="inlineStr">
         <is>
           <t>自动化管理与编排（自动化能力中枢）</t>
         </is>
       </c>
-      <c r="D34" s="4" t="inlineStr">
+      <c r="D34" s="11" t="inlineStr">
         <is>
           <t>R-MC-005</t>
         </is>
       </c>
-      <c r="E34" s="5" t="inlineStr">
+      <c r="E34" s="11" t="inlineStr">
         <is>
           <t>提供从模板任务到可视化工作流再到脚本开发的递进式编排，支持 ADB/RDP/CDP 多通道，承载养号、账号-终端绑定、登录状态维护等自动化账号操作及养号拟人化节奏（内置）；产出动作均经执行网关落地。</t>
         </is>
       </c>
-      <c r="F34" s="5" t="inlineStr">
+      <c r="F34" s="11" t="inlineStr">
         <is>
           <t>F-MC-07-01 模板化任务（第一阶段）；F-MC-07-02 可视化工作流编排（第二阶段）；F-MC-07-03 脚本开发与调试（第三阶段）；F-MC-07-04 模拟点击自动化；F-MC-07-05 养号自动化与拟人化节奏；F-MC-07-06 账号-终端-代理绑定自动化；F-MC-07-07 终端侧登录状态维护</t>
         </is>
       </c>
-      <c r="G34" s="5" t="inlineStr">
+      <c r="G34" s="11" t="inlineStr">
         <is>
           <t>SRS R-MC-005</t>
         </is>
       </c>
-      <c r="H34" s="5" t="inlineStr">
+      <c r="H34" s="11" t="inlineStr">
         <is>
           <t>对应 R-MC-005，含编排能力与账号自动化操作两类，但账号操作依赖编排产出动作，紧耦合故合并。</t>
         </is>
       </c>
     </row>
-    <row r="35" ht="33" customHeight="1">
-      <c r="A35" s="6" t="inlineStr">
-        <is>
-          <t>③功能</t>
-        </is>
-      </c>
-      <c r="B35" s="6" t="inlineStr">
+    <row r="35">
+      <c r="A35" s="8" t="inlineStr">
+        <is>
+          <t>③功能</t>
+        </is>
+      </c>
+      <c r="B35" s="8" t="inlineStr">
         <is>
           <t>F-MC-07-01</t>
         </is>
       </c>
-      <c r="C35" s="6" t="inlineStr">
+      <c r="C35" s="8" t="inlineStr">
         <is>
           <t>模板化任务（第一阶段）</t>
         </is>
       </c>
-      <c r="D35" s="6" t="inlineStr">
+      <c r="D35" s="8" t="inlineStr">
         <is>
           <t>R-MC-005</t>
         </is>
       </c>
-      <c r="E35" s="6" t="inlineStr">
+      <c r="E35" s="8" t="inlineStr">
         <is>
           <t>提供打开App/等待页面/点击/输入/上传文件/截图/返回/滑动/关闭App/设备巡检/App状态检测等模板化任务。</t>
         </is>
       </c>
-      <c r="F35" s="6" t="inlineStr">
+      <c r="F35" s="8" t="inlineStr">
         <is>
           <t>十二类模板化任务</t>
         </is>
       </c>
-      <c r="G35" s="6" t="inlineStr">
+      <c r="G35" s="8" t="inlineStr">
         <is>
           <t>SRS R-MC-005</t>
         </is>
       </c>
-      <c r="H35" s="6" t="inlineStr"/>
-    </row>
-    <row r="36" ht="33" customHeight="1">
-      <c r="A36" s="6" t="inlineStr">
-        <is>
-          <t>③功能</t>
-        </is>
-      </c>
-      <c r="B36" s="6" t="inlineStr">
+      <c r="H35" s="8" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="8" t="inlineStr">
+        <is>
+          <t>③功能</t>
+        </is>
+      </c>
+      <c r="B36" s="8" t="inlineStr">
         <is>
           <t>F-MC-07-02</t>
         </is>
       </c>
-      <c r="C36" s="6" t="inlineStr">
+      <c r="C36" s="8" t="inlineStr">
         <is>
           <t>可视化工作流编排（第二阶段）</t>
         </is>
       </c>
-      <c r="D36" s="6" t="inlineStr">
+      <c r="D36" s="8" t="inlineStr">
         <is>
           <t>R-MC-005</t>
         </is>
       </c>
-      <c r="E36" s="6" t="inlineStr">
+      <c r="E36" s="8" t="inlineStr">
         <is>
           <t>节点包括开始/设备选择/启动App/等待/点击/输入/滑动/截图/文件上传/条件判断/循环/HTTP请求/日志/审批/结束等，可视化编排。</t>
         </is>
       </c>
-      <c r="F36" s="6" t="inlineStr">
+      <c r="F36" s="8" t="inlineStr">
         <is>
           <t>十五类节点；可视化编排</t>
         </is>
       </c>
-      <c r="G36" s="6" t="inlineStr">
+      <c r="G36" s="8" t="inlineStr">
         <is>
           <t>SRS R-MC-005</t>
         </is>
       </c>
-      <c r="H36" s="6" t="inlineStr"/>
-    </row>
-    <row r="37" ht="33" customHeight="1">
-      <c r="A37" s="6" t="inlineStr">
-        <is>
-          <t>③功能</t>
-        </is>
-      </c>
-      <c r="B37" s="6" t="inlineStr">
+      <c r="H36" s="8" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="8" t="inlineStr">
+        <is>
+          <t>③功能</t>
+        </is>
+      </c>
+      <c r="B37" s="8" t="inlineStr">
         <is>
           <t>F-MC-07-03</t>
         </is>
       </c>
-      <c r="C37" s="6" t="inlineStr">
+      <c r="C37" s="8" t="inlineStr">
         <is>
           <t>脚本开发与调试（第三阶段）</t>
         </is>
       </c>
-      <c r="D37" s="6" t="inlineStr">
+      <c r="D37" s="8" t="inlineStr">
         <is>
           <t>R-MC-005</t>
         </is>
       </c>
-      <c r="E37" s="6" t="inlineStr">
+      <c r="E37" s="8" t="inlineStr">
         <is>
           <t>支持脚本编辑、调试设备、执行日志、截图回放与版本管理；脚本运行于沙箱并配置权限白名单。</t>
         </is>
       </c>
-      <c r="F37" s="6" t="inlineStr">
+      <c r="F37" s="8" t="inlineStr">
         <is>
           <t>脚本编辑/调试/回放/版本管理；沙箱+权限白名单</t>
         </is>
       </c>
-      <c r="G37" s="6" t="inlineStr">
+      <c r="G37" s="8" t="inlineStr">
         <is>
           <t>SRS R-MC-005；NR-S-05</t>
         </is>
       </c>
-      <c r="H37" s="6" t="inlineStr"/>
+      <c r="H37" s="8" t="n"/>
     </row>
     <row r="38">
-      <c r="A38" s="6" t="inlineStr">
-        <is>
-          <t>③功能</t>
-        </is>
-      </c>
-      <c r="B38" s="6" t="inlineStr">
+      <c r="A38" s="8" t="inlineStr">
+        <is>
+          <t>③功能</t>
+        </is>
+      </c>
+      <c r="B38" s="8" t="inlineStr">
         <is>
           <t>F-MC-07-04</t>
         </is>
       </c>
-      <c r="C38" s="6" t="inlineStr">
+      <c r="C38" s="8" t="inlineStr">
         <is>
           <t>模拟点击自动化</t>
         </is>
       </c>
-      <c r="D38" s="6" t="inlineStr">
+      <c r="D38" s="8" t="inlineStr">
         <is>
           <t>R-MC-005</t>
         </is>
       </c>
-      <c r="E38" s="6" t="inlineStr">
+      <c r="E38" s="8" t="inlineStr">
         <is>
           <t>针对 TikTok/Facebook 等平台实现模拟点击自动化。</t>
         </is>
       </c>
-      <c r="F38" s="6" t="inlineStr">
+      <c r="F38" s="8" t="inlineStr">
         <is>
           <t>目标平台模拟点击</t>
         </is>
       </c>
-      <c r="G38" s="6" t="inlineStr">
+      <c r="G38" s="8" t="inlineStr">
         <is>
           <t>SRS R-MC-005</t>
         </is>
       </c>
-      <c r="H38" s="6" t="inlineStr"/>
-    </row>
-    <row r="39" ht="49.5" customHeight="1">
-      <c r="A39" s="6" t="inlineStr">
-        <is>
-          <t>③功能</t>
-        </is>
-      </c>
-      <c r="B39" s="6" t="inlineStr">
+      <c r="H38" s="8" t="n"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="8" t="inlineStr">
+        <is>
+          <t>③功能</t>
+        </is>
+      </c>
+      <c r="B39" s="8" t="inlineStr">
         <is>
           <t>F-MC-07-05</t>
         </is>
       </c>
-      <c r="C39" s="6" t="inlineStr">
+      <c r="C39" s="8" t="inlineStr">
         <is>
           <t>养号自动化与拟人化节奏</t>
         </is>
       </c>
-      <c r="D39" s="6" t="inlineStr">
+      <c r="D39" s="8" t="inlineStr">
         <is>
           <t>R-MC-005</t>
         </is>
       </c>
-      <c r="E39" s="6" t="inlineStr">
+      <c r="E39" s="8" t="inlineStr">
         <is>
           <t>养号动作(发帖/关注/浏览)由本功能编排并经执行网关落地（认知作战账号经ADB/无障碍、爬虫账号经CDP）；拟人化节奏由本功能内置，不依赖蜂群智能体。</t>
         </is>
       </c>
-      <c r="F39" s="6" t="inlineStr">
+      <c r="F39" s="8" t="inlineStr">
         <is>
           <t>养号经网关落地；拟人化节奏内置；认知作战账号ADB/爬虫账号CDP</t>
         </is>
       </c>
-      <c r="G39" s="6" t="inlineStr">
+      <c r="G39" s="8" t="inlineStr">
         <is>
           <t>SRS R-MC-005</t>
         </is>
       </c>
-      <c r="H39" s="6" t="inlineStr"/>
-    </row>
-    <row r="40" ht="49.5" customHeight="1">
-      <c r="A40" s="6" t="inlineStr">
-        <is>
-          <t>③功能</t>
-        </is>
-      </c>
-      <c r="B40" s="6" t="inlineStr">
+      <c r="H39" s="8" t="n"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="8" t="inlineStr">
+        <is>
+          <t>③功能</t>
+        </is>
+      </c>
+      <c r="B40" s="8" t="inlineStr">
         <is>
           <t>F-MC-07-06</t>
         </is>
       </c>
-      <c r="C40" s="6" t="inlineStr">
+      <c r="C40" s="8" t="inlineStr">
         <is>
           <t>账号-终端-代理绑定自动化</t>
         </is>
       </c>
-      <c r="D40" s="6" t="inlineStr">
+      <c r="D40" s="8" t="inlineStr">
         <is>
           <t>R-MC-005</t>
         </is>
       </c>
-      <c r="E40" s="6" t="inlineStr">
+      <c r="E40" s="8" t="inlineStr">
         <is>
           <t>按差异化绑定规则绑定：真机/云手机/虚拟化真机「一设备一账号一IP」(未解绑前不可再绑)；反指纹浏览器Profile「一Profile一账号一IP」(实例可多开)；联动代理绑定记录。</t>
         </is>
       </c>
-      <c r="F40" s="6" t="inlineStr">
+      <c r="F40" s="8" t="inlineStr">
         <is>
           <t>一设备一账号一IP；一Profile一账号一IP；未解绑不可再绑；联动代理绑定</t>
         </is>
       </c>
-      <c r="G40" s="6" t="inlineStr">
+      <c r="G40" s="8" t="inlineStr">
         <is>
           <t>SRS R-MC-005；CON-13</t>
         </is>
       </c>
-      <c r="H40" s="6" t="inlineStr"/>
-    </row>
-    <row r="41" ht="33" customHeight="1">
-      <c r="A41" s="6" t="inlineStr">
-        <is>
-          <t>③功能</t>
-        </is>
-      </c>
-      <c r="B41" s="6" t="inlineStr">
+      <c r="H40" s="8" t="n"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="8" t="inlineStr">
+        <is>
+          <t>③功能</t>
+        </is>
+      </c>
+      <c r="B41" s="8" t="inlineStr">
         <is>
           <t>F-MC-07-07</t>
         </is>
       </c>
-      <c r="C41" s="6" t="inlineStr">
+      <c r="C41" s="8" t="inlineStr">
         <is>
           <t>终端侧登录状态维护</t>
         </is>
       </c>
-      <c r="D41" s="6" t="inlineStr">
+      <c r="D41" s="8" t="inlineStr">
         <is>
           <t>R-MC-005</t>
         </is>
       </c>
-      <c r="E41" s="6" t="inlineStr">
+      <c r="E41" s="8" t="inlineStr">
         <is>
           <t>记录账号在终端上的登录状态及其变化；账号状态变更(封禁/受限)时停止养号任务并解绑。</t>
         </is>
       </c>
-      <c r="F41" s="6" t="inlineStr">
+      <c r="F41" s="8" t="inlineStr">
         <is>
           <t>登录状态记录与变化；状态变更停止任务解绑</t>
         </is>
       </c>
-      <c r="G41" s="6" t="inlineStr">
+      <c r="G41" s="8" t="inlineStr">
         <is>
           <t>SRS R-MC-005</t>
         </is>
       </c>
-      <c r="H41" s="6" t="inlineStr"/>
-    </row>
-    <row r="42" ht="66" customHeight="1">
-      <c r="A42" s="4" t="inlineStr">
+      <c r="H41" s="8" t="n"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="11" t="inlineStr">
         <is>
           <t>②模块</t>
         </is>
       </c>
-      <c r="B42" s="4" t="inlineStr">
+      <c r="B42" s="11" t="inlineStr">
         <is>
           <t>M-MC-08</t>
         </is>
       </c>
-      <c r="C42" s="5" t="inlineStr">
+      <c r="C42" s="11" t="inlineStr">
         <is>
           <t>可观测性与作业统计复盘（全链路可观测与复盘大脑）</t>
         </is>
       </c>
-      <c r="D42" s="4" t="inlineStr">
+      <c r="D42" s="11" t="inlineStr">
         <is>
           <t>R-MC-006</t>
         </is>
       </c>
-      <c r="E42" s="5" t="inlineStr">
+      <c r="E42" s="11" t="inlineStr">
         <is>
           <t>使终端、账号、任务的每个动作可知可追溯，支撑记录、回传、告警、审计，并完成蜂群作业数据统计与任务复盘、将投送效果联动回传上游供效果评估闭环；动作留痕与作业统计同源于本功能，避免重复采集。</t>
         </is>
       </c>
-      <c r="F42" s="5" t="inlineStr">
-        <is>
-          <t>F-MC-08-01 动作留痕；F-MC-08-02 任务日志与截图回传；F-MC-08-03 异常告警；F-MC-08-04 审计日志；F-MC-08-05 蜂群作业多维统计；F-MC-08-06 任务复盘归因；F-MC-08-07 效果回调回传上游</t>
-        </is>
-      </c>
-      <c r="G42" s="5" t="inlineStr">
+      <c r="F42" s="11" t="inlineStr">
+        <is>
+          <t>F-MC-08-01 动作留痕；F-MC-08-02 任务日志与截图回传；F-MC-08-03 异常告警；F-MC-08-04 审计日志；F-MC-08-05 任务完成率统计；F-MC-08-06 内容触达与互动统计；F-MC-08-07 账号健康度统计；F-MC-08-08 任务复盘归因；F-MC-08-09 效果回调回传上游</t>
+        </is>
+      </c>
+      <c r="G42" s="11" t="inlineStr">
         <is>
           <t>SRS R-MC-006</t>
         </is>
       </c>
-      <c r="H42" s="5" t="inlineStr">
+      <c r="H42" s="11" t="inlineStr">
         <is>
           <t>对应 R-MC-006，动作留痕与作业统计同源，避免重复采集原始动作数据。</t>
         </is>
       </c>
     </row>
-    <row r="43" ht="33" customHeight="1">
-      <c r="A43" s="6" t="inlineStr">
-        <is>
-          <t>③功能</t>
-        </is>
-      </c>
-      <c r="B43" s="6" t="inlineStr">
+    <row r="43">
+      <c r="A43" s="8" t="inlineStr">
+        <is>
+          <t>③功能</t>
+        </is>
+      </c>
+      <c r="B43" s="8" t="inlineStr">
         <is>
           <t>F-MC-08-01</t>
         </is>
       </c>
-      <c r="C43" s="6" t="inlineStr">
+      <c r="C43" s="8" t="inlineStr">
         <is>
           <t>动作留痕</t>
         </is>
       </c>
-      <c r="D43" s="6" t="inlineStr">
+      <c r="D43" s="8" t="inlineStr">
         <is>
           <t>R-MC-006</t>
         </is>
       </c>
-      <c r="E43" s="6" t="inlineStr">
+      <c r="E43" s="8" t="inlineStr">
         <is>
           <t>每一个终端动作(点击/输入/安装/发布等)均留痕，记录时间、终端、账号与结果。</t>
         </is>
       </c>
-      <c r="F43" s="6" t="inlineStr">
+      <c r="F43" s="8" t="inlineStr">
         <is>
           <t>动作留痕；记录时间/终端/账号/结果</t>
         </is>
       </c>
-      <c r="G43" s="6" t="inlineStr">
+      <c r="G43" s="8" t="inlineStr">
         <is>
           <t>SRS R-MC-006</t>
         </is>
       </c>
-      <c r="H43" s="6" t="inlineStr"/>
+      <c r="H43" s="8" t="n"/>
     </row>
     <row r="44">
-      <c r="A44" s="6" t="inlineStr">
-        <is>
-          <t>③功能</t>
-        </is>
-      </c>
-      <c r="B44" s="6" t="inlineStr">
+      <c r="A44" s="8" t="inlineStr">
+        <is>
+          <t>③功能</t>
+        </is>
+      </c>
+      <c r="B44" s="8" t="inlineStr">
         <is>
           <t>F-MC-08-02</t>
         </is>
       </c>
-      <c r="C44" s="6" t="inlineStr">
+      <c r="C44" s="8" t="inlineStr">
         <is>
           <t>任务日志与截图回传</t>
         </is>
       </c>
-      <c r="D44" s="6" t="inlineStr">
+      <c r="D44" s="8" t="inlineStr">
         <is>
           <t>R-MC-006</t>
         </is>
       </c>
-      <c r="E44" s="6" t="inlineStr">
+      <c r="E44" s="8" t="inlineStr">
         <is>
           <t>Agent 回传任务执行日志与关键步骤截图。</t>
         </is>
       </c>
-      <c r="F44" s="6" t="inlineStr">
+      <c r="F44" s="8" t="inlineStr">
         <is>
           <t>任务日志回传；关键步骤截图</t>
         </is>
       </c>
-      <c r="G44" s="6" t="inlineStr">
+      <c r="G44" s="8" t="inlineStr">
         <is>
           <t>SRS R-MC-006</t>
         </is>
       </c>
-      <c r="H44" s="6" t="inlineStr">
+      <c r="H44" s="8" t="inlineStr">
         <is>
           <t>对接 II-02</t>
         </is>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="6" t="inlineStr">
-        <is>
-          <t>③功能</t>
-        </is>
-      </c>
-      <c r="B45" s="6" t="inlineStr">
+      <c r="A45" s="8" t="inlineStr">
+        <is>
+          <t>③功能</t>
+        </is>
+      </c>
+      <c r="B45" s="8" t="inlineStr">
         <is>
           <t>F-MC-08-03</t>
         </is>
       </c>
-      <c r="C45" s="6" t="inlineStr">
+      <c r="C45" s="8" t="inlineStr">
         <is>
           <t>异常告警</t>
         </is>
       </c>
-      <c r="D45" s="6" t="inlineStr">
+      <c r="D45" s="8" t="inlineStr">
         <is>
           <t>R-MC-006</t>
         </is>
       </c>
-      <c r="E45" s="6" t="inlineStr">
+      <c r="E45" s="8" t="inlineStr">
         <is>
           <t>任务失败、终端掉线、账号异常等异常事件触发告警通知。</t>
         </is>
       </c>
-      <c r="F45" s="6" t="inlineStr">
+      <c r="F45" s="8" t="inlineStr">
         <is>
           <t>异常事件告警通知</t>
         </is>
       </c>
-      <c r="G45" s="6" t="inlineStr">
+      <c r="G45" s="8" t="inlineStr">
         <is>
           <t>SRS R-MC-006</t>
         </is>
       </c>
-      <c r="H45" s="6" t="inlineStr"/>
-    </row>
-    <row r="46" ht="33" customHeight="1">
-      <c r="A46" s="6" t="inlineStr">
-        <is>
-          <t>③功能</t>
-        </is>
-      </c>
-      <c r="B46" s="6" t="inlineStr">
+      <c r="H45" s="8" t="n"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="8" t="inlineStr">
+        <is>
+          <t>③功能</t>
+        </is>
+      </c>
+      <c r="B46" s="8" t="inlineStr">
         <is>
           <t>F-MC-08-04</t>
         </is>
       </c>
-      <c r="C46" s="6" t="inlineStr">
+      <c r="C46" s="8" t="inlineStr">
         <is>
           <t>审计日志</t>
         </is>
       </c>
-      <c r="D46" s="6" t="inlineStr">
+      <c r="D46" s="8" t="inlineStr">
         <is>
           <t>R-MC-006</t>
         </is>
       </c>
-      <c r="E46" s="6" t="inlineStr">
+      <c r="E46" s="8" t="inlineStr">
         <is>
           <t>对用户与系统操作记录审计日志，记录谁在何时对哪台终端或账号做了什么。</t>
         </is>
       </c>
-      <c r="F46" s="6" t="inlineStr">
+      <c r="F46" s="8" t="inlineStr">
         <is>
           <t>操作审计；可追溯</t>
         </is>
       </c>
-      <c r="G46" s="6" t="inlineStr">
+      <c r="G46" s="8" t="inlineStr">
         <is>
           <t>SRS R-MC-006；NR-S-06</t>
         </is>
       </c>
-      <c r="H46" s="6" t="inlineStr"/>
-    </row>
-    <row r="47" ht="33" customHeight="1">
-      <c r="A47" s="6" t="inlineStr">
-        <is>
-          <t>③功能</t>
-        </is>
-      </c>
-      <c r="B47" s="6" t="inlineStr">
+      <c r="H46" s="8" t="n"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="8" t="inlineStr">
+        <is>
+          <t>③功能</t>
+        </is>
+      </c>
+      <c r="B47" s="8" t="inlineStr">
         <is>
           <t>F-MC-08-05</t>
         </is>
       </c>
-      <c r="C47" s="6" t="inlineStr">
-        <is>
-          <t>蜂群作业多维统计</t>
-        </is>
-      </c>
-      <c r="D47" s="6" t="inlineStr">
+      <c r="C47" s="8" t="inlineStr">
+        <is>
+          <t>任务完成率统计</t>
+        </is>
+      </c>
+      <c r="D47" s="8" t="inlineStr">
         <is>
           <t>R-MC-006</t>
         </is>
       </c>
-      <c r="E47" s="6" t="inlineStr">
-        <is>
-          <t>基于本功能采集上报的动作日志与任务日志对蜂群作业多维统计(任务完成率/内容触达/互动表现/账号健康度)，不重复采集原始动作数据。</t>
-        </is>
-      </c>
-      <c r="F47" s="6" t="inlineStr">
-        <is>
-          <t>多维统计；同源不重复采集</t>
-        </is>
-      </c>
-      <c r="G47" s="6" t="inlineStr">
+      <c r="E47" s="8" t="inlineStr">
+        <is>
+          <t>基于动作日志与任务日志统计蜂群作业的任务完成率、成功率、失败率、平均耗时等任务维度指标。</t>
+        </is>
+      </c>
+      <c r="F47" s="8" t="inlineStr">
+        <is>
+          <t>任务完成率/成功率/失败率/平均耗时；基于动作日志与任务日志</t>
+        </is>
+      </c>
+      <c r="G47" s="8" t="inlineStr">
         <is>
           <t>SRS R-MC-006</t>
         </is>
       </c>
-      <c r="H47" s="6" t="inlineStr"/>
+      <c r="H47" s="8" t="inlineStr">
+        <is>
+          <t>从原 F-MC-08-05 多维统计拆出，聚焦任务维度</t>
+        </is>
+      </c>
     </row>
     <row r="48">
-      <c r="A48" s="6" t="inlineStr">
-        <is>
-          <t>③功能</t>
-        </is>
-      </c>
-      <c r="B48" s="6" t="inlineStr">
+      <c r="A48" s="8" t="inlineStr">
+        <is>
+          <t>③功能</t>
+        </is>
+      </c>
+      <c r="B48" s="8" t="inlineStr">
         <is>
           <t>F-MC-08-06</t>
         </is>
       </c>
-      <c r="C48" s="6" t="inlineStr">
+      <c r="C48" s="8" t="inlineStr">
+        <is>
+          <t>内容触达与互动统计</t>
+        </is>
+      </c>
+      <c r="D48" s="8" t="inlineStr">
+        <is>
+          <t>R-MC-006</t>
+        </is>
+      </c>
+      <c r="E48" s="8" t="inlineStr">
+        <is>
+          <t>统计内容投放的触达量、曝光、互动（点赞/评论/转发）等内容效果维度指标。</t>
+        </is>
+      </c>
+      <c r="F48" s="8" t="inlineStr">
+        <is>
+          <t>触达量/曝光/互动(点赞/评论/转发)；内容效果维度</t>
+        </is>
+      </c>
+      <c r="G48" s="8" t="inlineStr">
+        <is>
+          <t>SRS R-MC-006</t>
+        </is>
+      </c>
+      <c r="H48" s="8" t="inlineStr">
+        <is>
+          <t>从原 F-MC-08-05 多维统计拆出，聚焦内容效果维度</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="8" t="inlineStr">
+        <is>
+          <t>③功能</t>
+        </is>
+      </c>
+      <c r="B49" s="8" t="inlineStr">
+        <is>
+          <t>F-MC-08-07</t>
+        </is>
+      </c>
+      <c r="C49" s="8" t="inlineStr">
+        <is>
+          <t>账号健康度统计</t>
+        </is>
+      </c>
+      <c r="D49" s="8" t="inlineStr">
+        <is>
+          <t>R-MC-006</t>
+        </is>
+      </c>
+      <c r="E49" s="8" t="inlineStr">
+        <is>
+          <t>统计智能体账号的健康度指标（活跃度、风控触发频次、封禁率、作业稳定性等）。</t>
+        </is>
+      </c>
+      <c r="F49" s="8" t="inlineStr">
+        <is>
+          <t>活跃度/风控触发频次/封禁率/作业稳定性；账号健康度维度</t>
+        </is>
+      </c>
+      <c r="G49" s="8" t="inlineStr">
+        <is>
+          <t>SRS R-MC-006</t>
+        </is>
+      </c>
+      <c r="H49" s="8" t="inlineStr">
+        <is>
+          <t>从原 F-MC-08-05 多维统计拆出，聚焦账号健康维度</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="8" t="inlineStr">
+        <is>
+          <t>③功能</t>
+        </is>
+      </c>
+      <c r="B50" s="8" t="inlineStr">
+        <is>
+          <t>F-MC-08-08</t>
+        </is>
+      </c>
+      <c r="C50" s="8" t="inlineStr">
         <is>
           <t>任务复盘归因</t>
         </is>
       </c>
-      <c r="D48" s="6" t="inlineStr">
+      <c r="D50" s="8" t="inlineStr">
         <is>
           <t>R-MC-006</t>
         </is>
       </c>
-      <c r="E48" s="6" t="inlineStr">
+      <c r="E50" s="8" t="inlineStr">
         <is>
           <t>对失败任务、异常账号、低效作业进行归因分析。</t>
         </is>
       </c>
-      <c r="F48" s="6" t="inlineStr">
+      <c r="F50" s="8" t="inlineStr">
         <is>
           <t>归因分析复盘</t>
         </is>
       </c>
-      <c r="G48" s="6" t="inlineStr">
+      <c r="G50" s="8" t="inlineStr">
         <is>
           <t>SRS R-MC-006</t>
         </is>
       </c>
-      <c r="H48" s="6" t="inlineStr"/>
-    </row>
-    <row r="49">
-      <c r="A49" s="6" t="inlineStr">
-        <is>
-          <t>③功能</t>
-        </is>
-      </c>
-      <c r="B49" s="6" t="inlineStr">
-        <is>
-          <t>F-MC-08-07</t>
-        </is>
-      </c>
-      <c r="C49" s="6" t="inlineStr">
+      <c r="H50" s="8" t="n"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="8" t="inlineStr">
+        <is>
+          <t>③功能</t>
+        </is>
+      </c>
+      <c r="B51" s="8" t="inlineStr">
+        <is>
+          <t>F-MC-08-09</t>
+        </is>
+      </c>
+      <c r="C51" s="8" t="inlineStr">
         <is>
           <t>效果回调回传上游</t>
         </is>
       </c>
-      <c r="D49" s="6" t="inlineStr">
+      <c r="D51" s="8" t="inlineStr">
         <is>
           <t>R-MC-006</t>
         </is>
       </c>
-      <c r="E49" s="6" t="inlineStr">
+      <c r="E51" s="8" t="inlineStr">
         <is>
           <t>将投送效果数据通过回调机制联动回传至 OCC，供效果评估闭环使用。</t>
         </is>
       </c>
-      <c r="F49" s="6" t="inlineStr">
+      <c r="F51" s="8" t="inlineStr">
         <is>
           <t>效果数据回调回传OCC</t>
         </is>
       </c>
-      <c r="G49" s="6" t="inlineStr">
+      <c r="G51" s="8" t="inlineStr">
         <is>
           <t>SRS R-MC-006</t>
         </is>
       </c>
-      <c r="H49" s="6" t="inlineStr">
+      <c r="H51" s="8" t="inlineStr">
         <is>
           <t>对接 II-11</t>
         </is>
       </c>
     </row>
-    <row r="50" ht="82.5" customHeight="1">
-      <c r="A50" s="4" t="inlineStr">
+    <row r="52">
+      <c r="A52" s="11" t="inlineStr">
         <is>
           <t>②模块</t>
         </is>
       </c>
-      <c r="B50" s="4" t="inlineStr">
+      <c r="B52" s="11" t="inlineStr">
         <is>
           <t>M-MC-09</t>
         </is>
       </c>
-      <c r="C50" s="5" t="inlineStr">
+      <c r="C52" s="11" t="inlineStr">
         <is>
           <t>账号资源管理（权威源）（账号资源平台级权威源）</t>
         </is>
       </c>
-      <c r="D50" s="4" t="inlineStr">
+      <c r="D52" s="11" t="inlineStr">
         <is>
           <t>R-MC-007</t>
         </is>
       </c>
-      <c r="E50" s="5" t="inlineStr">
+      <c r="E52" s="11" t="inlineStr">
         <is>
           <t>唯一维护账号主数据(注册/凭据/验证/风险评估/生命周期/账号分类)，经事件总线向 DC/SWM/OCC 共享分发 account_id；承担智能体账号分层分组、作业生命周期与 agent_id↔account_id 绑定维护；账号分爬虫账号(桌面端)与认知作战账号(移动端)两类。</t>
         </is>
       </c>
-      <c r="F50" s="5" t="inlineStr">
-        <is>
-          <t>F-MC-09-01 账号主数据维护；F-MC-09-02 账号注册流程；F-MC-09-03 账号验证与风险识别；F-MC-09-04 账号生命周期状态机；F-MC-09-05 智能体账号分层分组；F-MC-09-06 智能体账号作业生命周期；F-MC-09-07 账号状态变更事件广播；F-MC-09-08 智能体-账号绑定维护；F-MC-09-09 封号资产迁移</t>
-        </is>
-      </c>
-      <c r="G50" s="5" t="inlineStr">
+      <c r="F52" s="11" t="inlineStr">
+        <is>
+          <t>F-MC-09-01 账号主数据维护；F-MC-09-02 注册方式与流程编排；F-MC-09-03 注册结果判定与状态落地；F-MC-09-04 账号验证与风险识别；F-MC-09-05 账号生命周期状态机；F-MC-09-06 智能体账号分层分组；F-MC-09-07 智能体账号作业生命周期；F-MC-09-08 账号状态变更事件广播；F-MC-09-09 智能体-账号绑定维护；F-MC-09-10 迁移资产抽取；F-MC-09-11 迁移目标账号校验；F-MC-09-12 继承写入与绑定切换</t>
+        </is>
+      </c>
+      <c r="G52" s="11" t="inlineStr">
         <is>
           <t>SRS R-MC-007</t>
         </is>
       </c>
-      <c r="H50" s="5" t="inlineStr">
+      <c r="H52" s="11" t="inlineStr">
         <is>
           <t>对应 R-MC-007，账号主数据权威源（吸收旧 SR 子系统职责）；账号实体CRUD与智能体账号组织(分层分组/作业生命周期/绑定/迁移)紧耦合故合并。</t>
         </is>
       </c>
     </row>
-    <row r="51" ht="33" customHeight="1">
-      <c r="A51" s="6" t="inlineStr">
-        <is>
-          <t>③功能</t>
-        </is>
-      </c>
-      <c r="B51" s="6" t="inlineStr">
+    <row r="53">
+      <c r="A53" s="8" t="inlineStr">
+        <is>
+          <t>③功能</t>
+        </is>
+      </c>
+      <c r="B53" s="8" t="inlineStr">
         <is>
           <t>F-MC-09-01</t>
         </is>
       </c>
-      <c r="C51" s="6" t="inlineStr">
+      <c r="C53" s="8" t="inlineStr">
         <is>
           <t>账号主数据维护</t>
         </is>
       </c>
-      <c r="D51" s="6" t="inlineStr">
+      <c r="D53" s="8" t="inlineStr">
         <is>
           <t>R-MC-007</t>
         </is>
       </c>
-      <c r="E51" s="6" t="inlineStr">
+      <c r="E53" s="8" t="inlineStr">
         <is>
           <t>唯一维护账号主数据(凭据/平台/全局状态/生命周期/风险评估/账号分类)，凭据加密存储；其它子系统仅引用 account_id 不复制主数据。</t>
         </is>
       </c>
-      <c r="F51" s="6" t="inlineStr">
+      <c r="F53" s="8" t="inlineStr">
         <is>
           <t>主数据唯一维护；凭据加密不落明文；使用方仅引用account_id</t>
         </is>
       </c>
-      <c r="G51" s="6" t="inlineStr">
+      <c r="G53" s="8" t="inlineStr">
         <is>
           <t>SRS R-MC-007；NR-S-03</t>
         </is>
       </c>
-      <c r="H51" s="6" t="inlineStr">
+      <c r="H53" s="8" t="inlineStr">
         <is>
           <t>权威源；对接 II-01</t>
         </is>
       </c>
     </row>
-    <row r="52" ht="33" customHeight="1">
-      <c r="A52" s="6" t="inlineStr">
-        <is>
-          <t>③功能</t>
-        </is>
-      </c>
-      <c r="B52" s="6" t="inlineStr">
+    <row r="54">
+      <c r="A54" s="8" t="inlineStr">
+        <is>
+          <t>③功能</t>
+        </is>
+      </c>
+      <c r="B54" s="8" t="inlineStr">
         <is>
           <t>F-MC-09-02</t>
         </is>
       </c>
-      <c r="C52" s="6" t="inlineStr">
-        <is>
-          <t>账号注册流程</t>
-        </is>
-      </c>
-      <c r="D52" s="6" t="inlineStr">
+      <c r="C54" s="8" t="inlineStr">
+        <is>
+          <t>注册方式与流程编排</t>
+        </is>
+      </c>
+      <c r="D54" s="8" t="inlineStr">
         <is>
           <t>R-MC-007</t>
         </is>
       </c>
-      <c r="E52" s="6" t="inlineStr">
-        <is>
-          <t>承担注册入口与主数据落地，支持邮箱/手机接码/虚拟号注册；注册落到执行终端的动作经统一执行网关执行并回传结果。</t>
-        </is>
-      </c>
-      <c r="F52" s="6" t="inlineStr">
-        <is>
-          <t>邮箱/接码/虚拟号注册；注册动作经执行网关；回传判定状态</t>
-        </is>
-      </c>
-      <c r="G52" s="6" t="inlineStr">
+      <c r="E54" s="8" t="inlineStr">
+        <is>
+          <t>承担注册入口，支持邮箱/手机接码/虚拟号注册方式路由；编排注册流程（填写注册信息、接收验证码、完成登录探测），注册动作经统一执行网关执行。</t>
+        </is>
+      </c>
+      <c r="F54" s="8" t="inlineStr">
+        <is>
+          <t>邮箱/接码/虚拟号注册方式路由；注册流程编排；注册动作经执行网关(爬虫账号CDP/认知作战账号ADB)</t>
+        </is>
+      </c>
+      <c r="G54" s="8" t="inlineStr">
         <is>
           <t>SRS R-MC-007</t>
         </is>
       </c>
-      <c r="H52" s="6" t="inlineStr">
-        <is>
-          <t>对接 EI-03</t>
-        </is>
-      </c>
-    </row>
-    <row r="53" ht="33" customHeight="1">
-      <c r="A53" s="6" t="inlineStr">
-        <is>
-          <t>③功能</t>
-        </is>
-      </c>
-      <c r="B53" s="6" t="inlineStr">
+      <c r="H54" s="8" t="inlineStr">
+        <is>
+          <t>从原 F-MC-09-02 拆出，聚焦注册流程编排与执行；对接 EI-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="8" t="inlineStr">
+        <is>
+          <t>③功能</t>
+        </is>
+      </c>
+      <c r="B55" s="8" t="inlineStr">
         <is>
           <t>F-MC-09-03</t>
         </is>
       </c>
-      <c r="C53" s="6" t="inlineStr">
+      <c r="C55" s="8" t="inlineStr">
+        <is>
+          <t>注册结果判定与状态落地</t>
+        </is>
+      </c>
+      <c r="D55" s="8" t="inlineStr">
+        <is>
+          <t>R-MC-007</t>
+        </is>
+      </c>
+      <c r="E55" s="8" t="inlineStr">
+        <is>
+          <t>接收执行网关回传的注册执行结果，判定账号状态与风险等级，落地账号主数据（凭据加密存储），生成 account_id。</t>
+        </is>
+      </c>
+      <c r="F55" s="8" t="inlineStr">
+        <is>
+          <t>注册结果判定；状态与风险等级落地；凭据加密存储；生成account_id</t>
+        </is>
+      </c>
+      <c r="G55" s="8" t="inlineStr">
+        <is>
+          <t>SRS R-MC-007</t>
+        </is>
+      </c>
+      <c r="H55" s="8" t="inlineStr">
+        <is>
+          <t>从原 F-MC-09-02 拆出，聚焦结果判定与主数据落地</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="8" t="inlineStr">
+        <is>
+          <t>③功能</t>
+        </is>
+      </c>
+      <c r="B56" s="8" t="inlineStr">
+        <is>
+          <t>F-MC-09-04</t>
+        </is>
+      </c>
+      <c r="C56" s="8" t="inlineStr">
         <is>
           <t>账号验证与风险识别</t>
         </is>
       </c>
-      <c r="D53" s="6" t="inlineStr">
+      <c r="D56" s="8" t="inlineStr">
         <is>
           <t>R-MC-007</t>
         </is>
       </c>
-      <c r="E53" s="6" t="inlineStr">
+      <c r="E56" s="8" t="inlineStr">
         <is>
           <t>通过登录探测与状态识别检测可用性，识别封禁/限制/需验证等风险点，输出风险等级。</t>
         </is>
       </c>
-      <c r="F53" s="6" t="inlineStr">
+      <c r="F56" s="8" t="inlineStr">
         <is>
           <t>登录探测；状态识别；风险等级输出</t>
         </is>
       </c>
-      <c r="G53" s="6" t="inlineStr">
+      <c r="G56" s="8" t="inlineStr">
         <is>
           <t>SRS R-MC-007</t>
         </is>
       </c>
-      <c r="H53" s="6" t="inlineStr"/>
-    </row>
-    <row r="54" ht="33" customHeight="1">
-      <c r="A54" s="6" t="inlineStr">
-        <is>
-          <t>③功能</t>
-        </is>
-      </c>
-      <c r="B54" s="6" t="inlineStr">
-        <is>
-          <t>F-MC-09-04</t>
-        </is>
-      </c>
-      <c r="C54" s="6" t="inlineStr">
+      <c r="H56" s="8" t="n"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="8" t="inlineStr">
+        <is>
+          <t>③功能</t>
+        </is>
+      </c>
+      <c r="B57" s="8" t="inlineStr">
+        <is>
+          <t>F-MC-09-05</t>
+        </is>
+      </c>
+      <c r="C57" s="8" t="inlineStr">
         <is>
           <t>账号生命周期状态机</t>
         </is>
       </c>
-      <c r="D54" s="6" t="inlineStr">
+      <c r="D57" s="8" t="inlineStr">
         <is>
           <t>R-MC-007</t>
         </is>
       </c>
-      <c r="E54" s="6" t="inlineStr">
+      <c r="E57" s="8" t="inlineStr">
         <is>
           <t>账号在待登录/正常/受限/需验证/封禁/归档等状态间流转，由本子系统判定与维护。</t>
         </is>
       </c>
-      <c r="F54" s="6" t="inlineStr">
+      <c r="F57" s="8" t="inlineStr">
         <is>
           <t>六态生命周期状态机</t>
         </is>
       </c>
-      <c r="G54" s="6" t="inlineStr">
+      <c r="G57" s="8" t="inlineStr">
         <is>
           <t>SRS R-MC-007</t>
         </is>
       </c>
-      <c r="H54" s="6" t="inlineStr"/>
-    </row>
-    <row r="55" ht="33" customHeight="1">
-      <c r="A55" s="6" t="inlineStr">
-        <is>
-          <t>③功能</t>
-        </is>
-      </c>
-      <c r="B55" s="6" t="inlineStr">
-        <is>
-          <t>F-MC-09-05</t>
-        </is>
-      </c>
-      <c r="C55" s="6" t="inlineStr">
+      <c r="H57" s="8" t="n"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="8" t="inlineStr">
+        <is>
+          <t>③功能</t>
+        </is>
+      </c>
+      <c r="B58" s="8" t="inlineStr">
+        <is>
+          <t>F-MC-09-06</t>
+        </is>
+      </c>
+      <c r="C58" s="8" t="inlineStr">
         <is>
           <t>智能体账号分层分组</t>
         </is>
       </c>
-      <c r="D55" s="6" t="inlineStr">
+      <c r="D58" s="8" t="inlineStr">
         <is>
           <t>R-MC-007</t>
         </is>
       </c>
-      <c r="E55" s="6" t="inlineStr">
+      <c r="E58" s="8" t="inlineStr">
         <is>
           <t>对智能体账号按业务目标/平台/地区/风险等级等维度分层分组，形成可控账号层级结构。</t>
         </is>
       </c>
-      <c r="F55" s="6" t="inlineStr">
+      <c r="F58" s="8" t="inlineStr">
         <is>
           <t>多维度分层分组</t>
         </is>
       </c>
-      <c r="G55" s="6" t="inlineStr">
+      <c r="G58" s="8" t="inlineStr">
         <is>
           <t>SRS R-MC-007</t>
         </is>
       </c>
-      <c r="H55" s="6" t="inlineStr"/>
-    </row>
-    <row r="56" ht="33" customHeight="1">
-      <c r="A56" s="6" t="inlineStr">
-        <is>
-          <t>③功能</t>
-        </is>
-      </c>
-      <c r="B56" s="6" t="inlineStr">
-        <is>
-          <t>F-MC-09-06</t>
-        </is>
-      </c>
-      <c r="C56" s="6" t="inlineStr">
+      <c r="H58" s="8" t="n"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="8" t="inlineStr">
+        <is>
+          <t>③功能</t>
+        </is>
+      </c>
+      <c r="B59" s="8" t="inlineStr">
+        <is>
+          <t>F-MC-09-07</t>
+        </is>
+      </c>
+      <c r="C59" s="8" t="inlineStr">
         <is>
           <t>智能体账号作业生命周期</t>
         </is>
       </c>
-      <c r="D56" s="6" t="inlineStr">
+      <c r="D59" s="8" t="inlineStr">
         <is>
           <t>R-MC-007</t>
         </is>
       </c>
-      <c r="E56" s="6" t="inlineStr">
+      <c r="E59" s="8" t="inlineStr">
         <is>
           <t>管理智能体账号作业生命周期(待激活/活跃/休眠/受限/封禁/回收)，支持自动与人工流转。</t>
         </is>
       </c>
-      <c r="F56" s="6" t="inlineStr">
+      <c r="F59" s="8" t="inlineStr">
         <is>
           <t>六态作业生命周期</t>
         </is>
       </c>
-      <c r="G56" s="6" t="inlineStr">
+      <c r="G59" s="8" t="inlineStr">
         <is>
           <t>SRS R-MC-007</t>
         </is>
       </c>
-      <c r="H56" s="6" t="inlineStr"/>
-    </row>
-    <row r="57" ht="33" customHeight="1">
-      <c r="A57" s="6" t="inlineStr">
-        <is>
-          <t>③功能</t>
-        </is>
-      </c>
-      <c r="B57" s="6" t="inlineStr">
-        <is>
-          <t>F-MC-09-07</t>
-        </is>
-      </c>
-      <c r="C57" s="6" t="inlineStr">
+      <c r="H59" s="8" t="n"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="8" t="inlineStr">
+        <is>
+          <t>③功能</t>
+        </is>
+      </c>
+      <c r="B60" s="8" t="inlineStr">
+        <is>
+          <t>F-MC-09-08</t>
+        </is>
+      </c>
+      <c r="C60" s="8" t="inlineStr">
         <is>
           <t>账号状态变更事件广播</t>
         </is>
       </c>
-      <c r="D57" s="6" t="inlineStr">
+      <c r="D60" s="8" t="inlineStr">
         <is>
           <t>R-MC-007</t>
         </is>
       </c>
-      <c r="E57" s="6" t="inlineStr">
+      <c r="E60" s="8" t="inlineStr">
         <is>
           <t>账号状态变更(封禁/受限等)经事件总线广播 account.status.changed 事件，使用方订阅后立即响应，保证被封账号全网即时失效。</t>
         </is>
       </c>
-      <c r="F57" s="6" t="inlineStr">
+      <c r="F60" s="8" t="inlineStr">
         <is>
           <t>account.status.changed事件广播；使用方订阅即时响应</t>
         </is>
       </c>
-      <c r="G57" s="6" t="inlineStr">
+      <c r="G60" s="8" t="inlineStr">
         <is>
           <t>SRS R-MC-007</t>
         </is>
       </c>
-      <c r="H57" s="6" t="inlineStr">
+      <c r="H60" s="8" t="inlineStr">
         <is>
           <t>对接 II-01a</t>
         </is>
       </c>
     </row>
-    <row r="58" ht="33" customHeight="1">
-      <c r="A58" s="6" t="inlineStr">
-        <is>
-          <t>③功能</t>
-        </is>
-      </c>
-      <c r="B58" s="6" t="inlineStr">
-        <is>
-          <t>F-MC-09-08</t>
-        </is>
-      </c>
-      <c r="C58" s="6" t="inlineStr">
+    <row r="61">
+      <c r="A61" s="8" t="inlineStr">
+        <is>
+          <t>③功能</t>
+        </is>
+      </c>
+      <c r="B61" s="8" t="inlineStr">
+        <is>
+          <t>F-MC-09-09</t>
+        </is>
+      </c>
+      <c r="C61" s="8" t="inlineStr">
         <is>
           <t>智能体-账号绑定维护</t>
         </is>
       </c>
-      <c r="D58" s="6" t="inlineStr">
+      <c r="D61" s="8" t="inlineStr">
         <is>
           <t>R-MC-007</t>
         </is>
       </c>
-      <c r="E58" s="6" t="inlineStr">
+      <c r="E61" s="8" t="inlineStr">
         <is>
           <t>记录并维护 agent_id↔account_id 严格 1:1 绑定关系；agent_id 由 SWM 分配经 II-15 同步至本子系统持存。</t>
         </is>
       </c>
-      <c r="F58" s="6" t="inlineStr">
+      <c r="F61" s="8" t="inlineStr">
         <is>
           <t>agent_id↔account_id严格1:1；记录维护</t>
         </is>
       </c>
-      <c r="G58" s="6" t="inlineStr">
+      <c r="G61" s="8" t="inlineStr">
         <is>
           <t>SRS R-MC-007</t>
         </is>
       </c>
-      <c r="H58" s="6" t="inlineStr">
+      <c r="H61" s="8" t="inlineStr">
         <is>
           <t>对接 II-15</t>
         </is>
       </c>
     </row>
-    <row r="59" ht="49.5" customHeight="1">
-      <c r="A59" s="6" t="inlineStr">
-        <is>
-          <t>③功能</t>
-        </is>
-      </c>
-      <c r="B59" s="6" t="inlineStr">
-        <is>
-          <t>F-MC-09-09</t>
-        </is>
-      </c>
-      <c r="C59" s="6" t="inlineStr">
-        <is>
-          <t>封号资产迁移</t>
-        </is>
-      </c>
-      <c r="D59" s="6" t="inlineStr">
+    <row r="62">
+      <c r="A62" s="8" t="inlineStr">
+        <is>
+          <t>③功能</t>
+        </is>
+      </c>
+      <c r="B62" s="8" t="inlineStr">
+        <is>
+          <t>F-MC-09-10</t>
+        </is>
+      </c>
+      <c r="C62" s="8" t="inlineStr">
+        <is>
+          <t>迁移资产抽取</t>
+        </is>
+      </c>
+      <c r="D62" s="8" t="inlineStr">
         <is>
           <t>R-MC-007</t>
         </is>
       </c>
-      <c r="E59" s="6" t="inlineStr">
-        <is>
-          <t>账号被封禁后运营人员可对绑定智能体发起资产迁移：将原agent_id的人设标签/提示词版本/记忆整体继承到新注册未绑定agent_id的目标账号，旧绑定解绑休眠、新绑定激活。</t>
-        </is>
-      </c>
-      <c r="F59" s="6" t="inlineStr">
-        <is>
-          <t>人工触发；人设/提示词/记忆整体继承；人格连贯</t>
-        </is>
-      </c>
-      <c r="G59" s="6" t="inlineStr">
+      <c r="E62" s="8" t="inlineStr">
+        <is>
+          <t>从被封禁账号绑定的原 agent_id 智能体定义中抽取待迁移资产：人设标签、提示词版本、记忆数据。</t>
+        </is>
+      </c>
+      <c r="F62" s="8" t="inlineStr">
+        <is>
+          <t>抽取人设标签/提示词版本/记忆数据；资产完整性校验</t>
+        </is>
+      </c>
+      <c r="G62" s="8" t="inlineStr">
         <is>
           <t>SRS R-MC-007</t>
         </is>
       </c>
-      <c r="H59" s="6" t="inlineStr"/>
-    </row>
-    <row r="60" ht="66" customHeight="1">
-      <c r="A60" s="4" t="inlineStr">
+      <c r="H62" s="8" t="inlineStr">
+        <is>
+          <t>从原 F-MC-09-09 封号迁移拆出，聚焦资产抽取</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="8" t="inlineStr">
+        <is>
+          <t>③功能</t>
+        </is>
+      </c>
+      <c r="B63" s="8" t="inlineStr">
+        <is>
+          <t>F-MC-09-11</t>
+        </is>
+      </c>
+      <c r="C63" s="8" t="inlineStr">
+        <is>
+          <t>迁移目标账号校验</t>
+        </is>
+      </c>
+      <c r="D63" s="8" t="inlineStr">
+        <is>
+          <t>R-MC-007</t>
+        </is>
+      </c>
+      <c r="E63" s="8" t="inlineStr">
+        <is>
+          <t>校验目标账号（新注册且未绑定 agent_id）是否满足迁移条件：未绑定、状态正常、满足账号-终端绑定规则（移动端须有可用终端或后续绑定）。</t>
+        </is>
+      </c>
+      <c r="F63" s="8" t="inlineStr">
+        <is>
+          <t>目标账号未绑定校验；账号状态正常校验；终端绑定规则校验；不满足则拒绝并提示</t>
+        </is>
+      </c>
+      <c r="G63" s="8" t="inlineStr">
+        <is>
+          <t>SRS R-MC-007</t>
+        </is>
+      </c>
+      <c r="H63" s="8" t="inlineStr">
+        <is>
+          <t>从原 F-MC-09-09 封号迁移拆出，聚焦目标账号合规校验</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="8" t="inlineStr">
+        <is>
+          <t>③功能</t>
+        </is>
+      </c>
+      <c r="B64" s="8" t="inlineStr">
+        <is>
+          <t>F-MC-09-12</t>
+        </is>
+      </c>
+      <c r="C64" s="8" t="inlineStr">
+        <is>
+          <t>继承写入与绑定切换</t>
+        </is>
+      </c>
+      <c r="D64" s="8" t="inlineStr">
+        <is>
+          <t>R-MC-007</t>
+        </is>
+      </c>
+      <c r="E64" s="8" t="inlineStr">
+        <is>
+          <t>将抽取的资产整体继承写入目标账号的新 agent_id，激活新绑定；旧 agent_id↔旧账号解绑并休眠，保证人格连贯性。</t>
+        </is>
+      </c>
+      <c r="F64" s="8" t="inlineStr">
+        <is>
+          <t>资产整体继承写入新agent_id；新绑定激活；旧绑定解绑休眠；人格连贯</t>
+        </is>
+      </c>
+      <c r="G64" s="8" t="inlineStr">
+        <is>
+          <t>SRS R-MC-007</t>
+        </is>
+      </c>
+      <c r="H64" s="8" t="inlineStr">
+        <is>
+          <t>从原 F-MC-09-09 封号迁移拆出，聚焦继承写入与绑定切换</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="11" t="inlineStr">
         <is>
           <t>②模块</t>
         </is>
       </c>
-      <c r="B60" s="4" t="inlineStr">
+      <c r="B65" s="11" t="inlineStr">
         <is>
           <t>M-MC-10</t>
         </is>
       </c>
-      <c r="C60" s="5" t="inlineStr">
+      <c r="C65" s="11" t="inlineStr">
         <is>
           <t>智能体执行宿主与同步（智能体执行宿主）</t>
         </is>
       </c>
-      <c r="D60" s="4" t="inlineStr">
+      <c r="D65" s="11" t="inlineStr">
         <is>
           <t>R-MC-008</t>
         </is>
       </c>
-      <c r="E60" s="5" t="inlineStr">
+      <c r="E65" s="11" t="inlineStr">
         <is>
           <t>接收并持存 SWM 同步来的智能体定义(agent_id，含人设/提示词/记忆/作业策略)，任务执行时调用并在执行前校验人设一致性；确立「SWM为定义与记忆中心、MC为执行宿主」分工。</t>
         </is>
       </c>
-      <c r="F60" s="5" t="inlineStr">
+      <c r="F65" s="11" t="inlineStr">
         <is>
           <t>F-MC-10-01 智能体定义接收与持存；F-MC-10-02 四元绑定关系维护；F-MC-10-03 人设一致性校验；F-MC-10-04 智能体定义调用执行；F-MC-10-05 智能体定义更新生效；F-MC-10-06 OCC编排智能体节点来源</t>
         </is>
       </c>
-      <c r="G60" s="5" t="inlineStr">
+      <c r="G65" s="11" t="inlineStr">
         <is>
           <t>SRS R-MC-008</t>
         </is>
       </c>
-      <c r="H60" s="5" t="inlineStr">
+      <c r="H65" s="11" t="inlineStr">
         <is>
           <t>对应 R-MC-008，智能体执行宿主职责。</t>
         </is>
       </c>
     </row>
-    <row r="61" ht="33" customHeight="1">
-      <c r="A61" s="6" t="inlineStr">
-        <is>
-          <t>③功能</t>
-        </is>
-      </c>
-      <c r="B61" s="6" t="inlineStr">
+    <row r="66">
+      <c r="A66" s="8" t="inlineStr">
+        <is>
+          <t>③功能</t>
+        </is>
+      </c>
+      <c r="B66" s="8" t="inlineStr">
         <is>
           <t>F-MC-10-01</t>
         </is>
       </c>
-      <c r="C61" s="6" t="inlineStr">
+      <c r="C66" s="8" t="inlineStr">
         <is>
           <t>智能体定义接收与持存</t>
         </is>
       </c>
-      <c r="D61" s="6" t="inlineStr">
+      <c r="D66" s="8" t="inlineStr">
         <is>
           <t>R-MC-008</t>
         </is>
       </c>
-      <c r="E61" s="6" t="inlineStr">
+      <c r="E66" s="8" t="inlineStr">
         <is>
           <t>以 agent_id 为主键接收 SWM 同步的智能体定义(人设标签/提示词/记忆/作业策略)并持存，作为任务执行调用依据。</t>
         </is>
       </c>
-      <c r="F61" s="6" t="inlineStr">
+      <c r="F66" s="8" t="inlineStr">
         <is>
           <t>agent_id主键接收持存</t>
         </is>
       </c>
-      <c r="G61" s="6" t="inlineStr">
+      <c r="G66" s="8" t="inlineStr">
         <is>
           <t>SRS R-MC-008</t>
         </is>
       </c>
-      <c r="H61" s="6" t="inlineStr">
+      <c r="H66" s="8" t="inlineStr">
         <is>
           <t>对接 II-15</t>
         </is>
       </c>
     </row>
-    <row r="62" ht="33" customHeight="1">
-      <c r="A62" s="6" t="inlineStr">
-        <is>
-          <t>③功能</t>
-        </is>
-      </c>
-      <c r="B62" s="6" t="inlineStr">
+    <row r="67">
+      <c r="A67" s="8" t="inlineStr">
+        <is>
+          <t>③功能</t>
+        </is>
+      </c>
+      <c r="B67" s="8" t="inlineStr">
         <is>
           <t>F-MC-10-02</t>
         </is>
       </c>
-      <c r="C62" s="6" t="inlineStr">
+      <c r="C67" s="8" t="inlineStr">
         <is>
           <t>四元绑定关系维护</t>
         </is>
       </c>
-      <c r="D62" s="6" t="inlineStr">
+      <c r="D67" s="8" t="inlineStr">
         <is>
           <t>R-MC-008</t>
         </is>
       </c>
-      <c r="E62" s="6" t="inlineStr">
+      <c r="E67" s="8" t="inlineStr">
         <is>
           <t>记录并维护 agent_id↔account_id↔终端↔代理IP 四元绑定关系，形成1:1:1:1作战单元。</t>
         </is>
       </c>
-      <c r="F62" s="6" t="inlineStr">
+      <c r="F67" s="8" t="inlineStr">
         <is>
           <t>四元绑定；1:1:1:1作战单元</t>
         </is>
       </c>
-      <c r="G62" s="6" t="inlineStr">
+      <c r="G67" s="8" t="inlineStr">
         <is>
           <t>SRS R-MC-008</t>
         </is>
       </c>
-      <c r="H62" s="6" t="inlineStr"/>
-    </row>
-    <row r="63" ht="49.5" customHeight="1">
-      <c r="A63" s="6" t="inlineStr">
-        <is>
-          <t>③功能</t>
-        </is>
-      </c>
-      <c r="B63" s="6" t="inlineStr">
+      <c r="H67" s="8" t="n"/>
+    </row>
+    <row r="68">
+      <c r="A68" s="8" t="inlineStr">
+        <is>
+          <t>③功能</t>
+        </is>
+      </c>
+      <c r="B68" s="8" t="inlineStr">
         <is>
           <t>F-MC-10-03</t>
         </is>
       </c>
-      <c r="C63" s="6" t="inlineStr">
+      <c r="C68" s="8" t="inlineStr">
         <is>
           <t>人设一致性校验</t>
         </is>
       </c>
-      <c r="D63" s="6" t="inlineStr">
+      <c r="D68" s="8" t="inlineStr">
         <is>
           <t>R-MC-008</t>
         </is>
       </c>
-      <c r="E63" s="6" t="inlineStr">
+      <c r="E68" s="8" t="inlineStr">
         <is>
           <t>智能体模式下任务执行前校验「当前account_id绑定的人设标签」与「agent_id定义中的人设标签」是否一致，一致方可调用并经网关落地，不一致拒绝执行并告警。</t>
         </is>
       </c>
-      <c r="F63" s="6" t="inlineStr">
+      <c r="F68" s="8" t="inlineStr">
         <is>
           <t>执行前人设一致性校验；不一致拒绝并告警</t>
         </is>
       </c>
-      <c r="G63" s="6" t="inlineStr">
+      <c r="G68" s="8" t="inlineStr">
         <is>
           <t>SRS R-MC-008</t>
         </is>
       </c>
-      <c r="H63" s="6" t="inlineStr"/>
-    </row>
-    <row r="64" ht="33" customHeight="1">
-      <c r="A64" s="6" t="inlineStr">
-        <is>
-          <t>③功能</t>
-        </is>
-      </c>
-      <c r="B64" s="6" t="inlineStr">
+      <c r="H68" s="8" t="n"/>
+    </row>
+    <row r="69">
+      <c r="A69" s="8" t="inlineStr">
+        <is>
+          <t>③功能</t>
+        </is>
+      </c>
+      <c r="B69" s="8" t="inlineStr">
         <is>
           <t>F-MC-10-04</t>
         </is>
       </c>
-      <c r="C64" s="6" t="inlineStr">
+      <c r="C69" s="8" t="inlineStr">
         <is>
           <t>智能体定义调用执行</t>
         </is>
       </c>
-      <c r="D64" s="6" t="inlineStr">
+      <c r="D69" s="8" t="inlineStr">
         <is>
           <t>R-MC-008</t>
         </is>
       </c>
-      <c r="E64" s="6" t="inlineStr">
+      <c r="E69" s="8" t="inlineStr">
         <is>
           <t>任务执行时按智能体定义中的提示词/记忆/作业策略调用 IRS 本地大模型视觉推理，产出动作指令再经执行网关落地。</t>
         </is>
       </c>
-      <c r="F64" s="6" t="inlineStr">
+      <c r="F69" s="8" t="inlineStr">
         <is>
           <t>按定义调用IRS推理；动作经网关落地</t>
         </is>
       </c>
-      <c r="G64" s="6" t="inlineStr">
+      <c r="G69" s="8" t="inlineStr">
         <is>
           <t>SRS R-MC-008</t>
         </is>
       </c>
-      <c r="H64" s="6" t="inlineStr"/>
-    </row>
-    <row r="65" ht="33" customHeight="1">
-      <c r="A65" s="6" t="inlineStr">
-        <is>
-          <t>③功能</t>
-        </is>
-      </c>
-      <c r="B65" s="6" t="inlineStr">
+      <c r="H69" s="8" t="n"/>
+    </row>
+    <row r="70">
+      <c r="A70" s="8" t="inlineStr">
+        <is>
+          <t>③功能</t>
+        </is>
+      </c>
+      <c r="B70" s="8" t="inlineStr">
         <is>
           <t>F-MC-10-05</t>
         </is>
       </c>
-      <c r="C65" s="6" t="inlineStr">
+      <c r="C70" s="8" t="inlineStr">
         <is>
           <t>智能体定义更新生效</t>
         </is>
       </c>
-      <c r="D65" s="6" t="inlineStr">
+      <c r="D70" s="8" t="inlineStr">
         <is>
           <t>R-MC-008</t>
         </is>
       </c>
-      <c r="E65" s="6" t="inlineStr">
+      <c r="E70" s="8" t="inlineStr">
         <is>
           <t>智能体定义更新时(SWM以同一agent_id重新同步)更新持存版本，保证执行使用最新定义。</t>
         </is>
       </c>
-      <c r="F65" s="6" t="inlineStr">
+      <c r="F70" s="8" t="inlineStr">
         <is>
           <t>更新持存版本；使用最新定义</t>
         </is>
       </c>
-      <c r="G65" s="6" t="inlineStr">
+      <c r="G70" s="8" t="inlineStr">
         <is>
           <t>SRS R-MC-008</t>
         </is>
       </c>
-      <c r="H65" s="6" t="inlineStr"/>
-    </row>
-    <row r="66" ht="33" customHeight="1">
-      <c r="A66" s="6" t="inlineStr">
-        <is>
-          <t>③功能</t>
-        </is>
-      </c>
-      <c r="B66" s="6" t="inlineStr">
+      <c r="H70" s="8" t="n"/>
+    </row>
+    <row r="71">
+      <c r="A71" s="8" t="inlineStr">
+        <is>
+          <t>③功能</t>
+        </is>
+      </c>
+      <c r="B71" s="8" t="inlineStr">
         <is>
           <t>F-MC-10-06</t>
         </is>
       </c>
-      <c r="C66" s="6" t="inlineStr">
+      <c r="C71" s="8" t="inlineStr">
         <is>
           <t>OCC编排智能体节点来源</t>
         </is>
       </c>
-      <c r="D66" s="6" t="inlineStr">
+      <c r="D71" s="8" t="inlineStr">
         <is>
           <t>R-MC-008</t>
         </is>
       </c>
-      <c r="E66" s="6" t="inlineStr">
+      <c r="E71" s="8" t="inlineStr">
         <is>
           <t>作为 OCC 作战编排的执行节点来源——编排中智能体节点以 agent_id 引用本子系统持存的智能体。</t>
         </is>
       </c>
-      <c r="F66" s="6" t="inlineStr">
+      <c r="F71" s="8" t="inlineStr">
         <is>
           <t>以agent_id供OCC编排引用</t>
         </is>
       </c>
-      <c r="G66" s="6" t="inlineStr">
+      <c r="G71" s="8" t="inlineStr">
         <is>
           <t>SRS R-MC-008</t>
         </is>
       </c>
-      <c r="H66" s="6" t="inlineStr">
+      <c r="H71" s="8" t="inlineStr">
         <is>
           <t>对接 II-11</t>
         </is>
@@ -8926,8 +9198,8 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H36"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="18"/>
+  <dimension ref="A1:H37"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
@@ -8940,1428 +9212,1474 @@
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="9" t="inlineStr">
         <is>
           <t>层级</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="9" t="inlineStr">
         <is>
           <t>编号</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" s="9" t="inlineStr">
         <is>
           <t>名称</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" s="9" t="inlineStr">
         <is>
           <t>对应需求</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" s="9" t="inlineStr">
         <is>
           <t>职责简述</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" s="9" t="inlineStr">
         <is>
           <t>关键能力点（功能）</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" s="9" t="inlineStr">
         <is>
           <t>来源依据</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" s="9" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="115.5" customHeight="1">
-      <c r="A2" s="2" t="inlineStr">
+    <row r="2">
+      <c r="A2" s="10" t="inlineStr">
         <is>
           <t>①子系统</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="B2" s="10" t="inlineStr">
         <is>
           <t>M-OCC-00</t>
         </is>
       </c>
-      <c r="C2" s="3" t="inlineStr">
+      <c r="C2" s="10" t="inlineStr">
         <is>
           <t>舆情作战业务子系统</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="D2" s="10" t="inlineStr">
         <is>
           <t>R-OCC-001~005</t>
         </is>
       </c>
-      <c r="E2" s="3" t="inlineStr">
+      <c r="E2" s="10" t="inlineStr">
         <is>
           <t>全链路指挥大脑：构建「目标识别→作战编排→效果评估」作战闭环，并承担内容资源统一管理(唯一权威源)；基于DC分析结果与IRS推理产出作战方案，以作战编排直接编排MC中智能体节点与自动化脚本节点形成执行流程落地。</t>
         </is>
       </c>
-      <c r="F2" s="3" t="inlineStr">
+      <c r="F2" s="10" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G2" s="3" t="inlineStr">
+      <c r="G2" s="10" t="inlineStr">
         <is>
           <t>SRS §引言/OCC</t>
         </is>
       </c>
-      <c r="H2" s="3" t="inlineStr">
+      <c r="H2" s="10" t="inlineStr">
         <is>
           <t>R-OCC-001(目标识别)含目标实体CRUD与目标关联网络(图结构)两个异构关注点，拆2；R-OCC-002(作战编排)含方案规划与编排执行引擎两类，拆2；R-OCC-005(内容管理)含主数据排期与审核风控两类，拆2。</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="49.5" customHeight="1">
-      <c r="A3" s="4" t="inlineStr">
+    <row r="3">
+      <c r="A3" s="11" t="inlineStr">
         <is>
           <t>②模块</t>
         </is>
       </c>
-      <c r="B3" s="4" t="inlineStr">
+      <c r="B3" s="11" t="inlineStr">
         <is>
           <t>M-OCC-01</t>
         </is>
       </c>
-      <c r="C3" s="5" t="inlineStr">
+      <c r="C3" s="11" t="inlineStr">
         <is>
           <t>目标档案与状态管理（目标数据管家）</t>
         </is>
       </c>
-      <c r="D3" s="4" t="inlineStr">
+      <c r="D3" s="11" t="inlineStr">
         <is>
           <t>R-OCC-001(实体)</t>
         </is>
       </c>
-      <c r="E3" s="5" t="inlineStr">
+      <c r="E3" s="11" t="inlineStr">
         <is>
           <t>识别舆情事件目标要素并建档为数据对象，支持建档、属性修改、状态流转与删除；目标即数据，可随事件演进而更新；本期以人工识别为主、系统提供数据维护支撑。</t>
         </is>
       </c>
-      <c r="F3" s="5" t="inlineStr">
+      <c r="F3" s="11" t="inlineStr">
         <is>
           <t>F-OCC-01-01 目标建档与标识；F-OCC-01-02 目标属性维护；F-OCC-01-03 目标状态生命周期；F-OCC-01-04 目标多维信息融合；F-OCC-01-05 目标变更事件广播</t>
         </is>
       </c>
-      <c r="G3" s="5" t="inlineStr">
+      <c r="G3" s="11" t="inlineStr">
         <is>
           <t>SRS R-OCC-001(实体)</t>
         </is>
       </c>
-      <c r="H3" s="5" t="inlineStr">
+      <c r="H3" s="11" t="inlineStr">
         <is>
           <t>R-OCC-001 的目标实体CRUD/状态机与目标关联网络(图结构建模)是不同数据范式，故拆。</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="6" t="inlineStr">
-        <is>
-          <t>③功能</t>
-        </is>
-      </c>
-      <c r="B4" s="6" t="inlineStr">
+      <c r="A4" s="8" t="inlineStr">
+        <is>
+          <t>③功能</t>
+        </is>
+      </c>
+      <c r="B4" s="8" t="inlineStr">
         <is>
           <t>F-OCC-01-01</t>
         </is>
       </c>
-      <c r="C4" s="6" t="inlineStr">
+      <c r="C4" s="8" t="inlineStr">
         <is>
           <t>目标建档与标识</t>
         </is>
       </c>
-      <c r="D4" s="6" t="inlineStr">
+      <c r="D4" s="8" t="inlineStr">
         <is>
           <t>R-OCC-001</t>
         </is>
       </c>
-      <c r="E4" s="6" t="inlineStr">
+      <c r="E4" s="8" t="inlineStr">
         <is>
           <t>每个识别出的目标建档为一条目标数据，赋予全局唯一target_id。</t>
         </is>
       </c>
-      <c r="F4" s="6" t="inlineStr">
+      <c r="F4" s="8" t="inlineStr">
         <is>
           <t>目标建档；全局唯一target_id</t>
         </is>
       </c>
-      <c r="G4" s="6" t="inlineStr">
+      <c r="G4" s="8" t="inlineStr">
         <is>
           <t>SRS R-OCC-001</t>
         </is>
       </c>
-      <c r="H4" s="6" t="inlineStr"/>
-    </row>
-    <row r="5" ht="33" customHeight="1">
-      <c r="A5" s="6" t="inlineStr">
-        <is>
-          <t>③功能</t>
-        </is>
-      </c>
-      <c r="B5" s="6" t="inlineStr">
+      <c r="H4" s="8" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="8" t="inlineStr">
+        <is>
+          <t>③功能</t>
+        </is>
+      </c>
+      <c r="B5" s="8" t="inlineStr">
         <is>
           <t>F-OCC-01-02</t>
         </is>
       </c>
-      <c r="C5" s="6" t="inlineStr">
+      <c r="C5" s="8" t="inlineStr">
         <is>
           <t>目标属性维护</t>
         </is>
       </c>
-      <c r="D5" s="6" t="inlineStr">
+      <c r="D5" s="8" t="inlineStr">
         <is>
           <t>R-OCC-001</t>
         </is>
       </c>
-      <c r="E5" s="6" t="inlineStr">
+      <c r="E5" s="8" t="inlineStr">
         <is>
           <t>目标档案各属性(事件主体/争议点/画像属性/干预切入点等)支持新增/修改/删除，可随事件演进更新。</t>
         </is>
       </c>
-      <c r="F5" s="6" t="inlineStr">
+      <c r="F5" s="8" t="inlineStr">
         <is>
           <t>属性增删改；可随事件演进更新</t>
         </is>
       </c>
-      <c r="G5" s="6" t="inlineStr">
+      <c r="G5" s="8" t="inlineStr">
         <is>
           <t>SRS R-OCC-001</t>
         </is>
       </c>
-      <c r="H5" s="6" t="inlineStr"/>
-    </row>
-    <row r="6" ht="33" customHeight="1">
-      <c r="A6" s="6" t="inlineStr">
-        <is>
-          <t>③功能</t>
-        </is>
-      </c>
-      <c r="B6" s="6" t="inlineStr">
+      <c r="H5" s="8" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="8" t="inlineStr">
+        <is>
+          <t>③功能</t>
+        </is>
+      </c>
+      <c r="B6" s="8" t="inlineStr">
         <is>
           <t>F-OCC-01-03</t>
         </is>
       </c>
-      <c r="C6" s="6" t="inlineStr">
+      <c r="C6" s="8" t="inlineStr">
         <is>
           <t>目标状态生命周期</t>
         </is>
       </c>
-      <c r="D6" s="6" t="inlineStr">
+      <c r="D6" s="8" t="inlineStr">
         <is>
           <t>R-OCC-001</t>
         </is>
       </c>
-      <c r="E6" s="6" t="inlineStr">
+      <c r="E6" s="8" t="inlineStr">
         <is>
           <t>目标具备状态生命周期(待核实/已确认/已锁定/已处置/已归档)，支持状态流转。</t>
         </is>
       </c>
-      <c r="F6" s="6" t="inlineStr">
+      <c r="F6" s="8" t="inlineStr">
         <is>
           <t>目标状态机流转</t>
         </is>
       </c>
-      <c r="G6" s="6" t="inlineStr">
+      <c r="G6" s="8" t="inlineStr">
         <is>
           <t>SRS R-OCC-001</t>
         </is>
       </c>
-      <c r="H6" s="6" t="inlineStr"/>
-    </row>
-    <row r="7" ht="33" customHeight="1">
-      <c r="A7" s="6" t="inlineStr">
-        <is>
-          <t>③功能</t>
-        </is>
-      </c>
-      <c r="B7" s="6" t="inlineStr">
+      <c r="H6" s="8" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="8" t="inlineStr">
+        <is>
+          <t>③功能</t>
+        </is>
+      </c>
+      <c r="B7" s="8" t="inlineStr">
         <is>
           <t>F-OCC-01-04</t>
         </is>
       </c>
-      <c r="C7" s="6" t="inlineStr">
+      <c r="C7" s="8" t="inlineStr">
         <is>
           <t>目标多维信息融合</t>
         </is>
       </c>
-      <c r="D7" s="6" t="inlineStr">
+      <c r="D7" s="8" t="inlineStr">
         <is>
           <t>R-OCC-001</t>
         </is>
       </c>
-      <c r="E7" s="6" t="inlineStr">
+      <c r="E7" s="8" t="inlineStr">
         <is>
           <t>识别过程综合事件主体/传播源头与链路/事件群体账号传播画像/干预切入点与薄弱点，形成完整目标档案。</t>
         </is>
       </c>
-      <c r="F7" s="6" t="inlineStr">
+      <c r="F7" s="8" t="inlineStr">
         <is>
           <t>多维信息融合；本期人工识别+系统维护</t>
         </is>
       </c>
-      <c r="G7" s="6" t="inlineStr">
+      <c r="G7" s="8" t="inlineStr">
         <is>
           <t>SRS R-OCC-001</t>
         </is>
       </c>
-      <c r="H7" s="6" t="inlineStr"/>
-    </row>
-    <row r="8" ht="33" customHeight="1">
-      <c r="A8" s="6" t="inlineStr">
-        <is>
-          <t>③功能</t>
-        </is>
-      </c>
-      <c r="B8" s="6" t="inlineStr">
+      <c r="H7" s="8" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="8" t="inlineStr">
+        <is>
+          <t>③功能</t>
+        </is>
+      </c>
+      <c r="B8" s="8" t="inlineStr">
         <is>
           <t>F-OCC-01-05</t>
         </is>
       </c>
-      <c r="C8" s="6" t="inlineStr">
+      <c r="C8" s="8" t="inlineStr">
         <is>
           <t>目标变更事件广播</t>
         </is>
       </c>
-      <c r="D8" s="6" t="inlineStr">
+      <c r="D8" s="8" t="inlineStr">
         <is>
           <t>R-OCC-001</t>
         </is>
       </c>
-      <c r="E8" s="6" t="inlineStr">
+      <c r="E8" s="8" t="inlineStr">
         <is>
           <t>目标变更经事件总线广播 target.changed 事件，使用方(作战编排/效果评估)订阅响应。</t>
         </is>
       </c>
-      <c r="F8" s="6" t="inlineStr">
+      <c r="F8" s="8" t="inlineStr">
         <is>
           <t>target.changed事件广播；使用方订阅</t>
         </is>
       </c>
-      <c r="G8" s="6" t="inlineStr">
+      <c r="G8" s="8" t="inlineStr">
         <is>
           <t>SRS R-OCC-001</t>
         </is>
       </c>
-      <c r="H8" s="6" t="inlineStr"/>
-    </row>
-    <row r="9" ht="66" customHeight="1">
-      <c r="A9" s="4" t="inlineStr">
+      <c r="H8" s="8" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="11" t="inlineStr">
         <is>
           <t>②模块</t>
         </is>
       </c>
-      <c r="B9" s="4" t="inlineStr">
+      <c r="B9" s="11" t="inlineStr">
         <is>
           <t>M-OCC-02</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
+      <c r="C9" s="11" t="inlineStr">
         <is>
           <t>目标关联网络（目标关系图谱）</t>
         </is>
       </c>
-      <c r="D9" s="4" t="inlineStr">
+      <c r="D9" s="11" t="inlineStr">
         <is>
           <t>R-OCC-001(图结构)</t>
         </is>
       </c>
-      <c r="E9" s="5" t="inlineStr">
+      <c r="E9" s="11" t="inlineStr">
         <is>
           <t>目标之间建立关联关系（如一个事件主体关联多个传播源头、一个干预目标关联多个薄弱点），形成目标关系网络，支持关系网络查询。</t>
         </is>
       </c>
-      <c r="F9" s="5" t="inlineStr">
+      <c r="F9" s="11" t="inlineStr">
         <is>
           <t>F-OCC-02-01 目标关联关系建模；F-OCC-02-02 关系网络查询</t>
         </is>
       </c>
-      <c r="G9" s="5" t="inlineStr">
+      <c r="G9" s="11" t="inlineStr">
         <is>
           <t>SRS R-OCC-001(图结构)</t>
         </is>
       </c>
-      <c r="H9" s="5" t="inlineStr">
+      <c r="H9" s="11" t="inlineStr">
         <is>
           <t>R-OCC-001 的目标关联是图结构建模(关系类型/网络查询)，与目标实体CRUD是不同数据范式，故拆。</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="6" t="inlineStr">
-        <is>
-          <t>③功能</t>
-        </is>
-      </c>
-      <c r="B10" s="6" t="inlineStr">
+      <c r="A10" s="8" t="inlineStr">
+        <is>
+          <t>③功能</t>
+        </is>
+      </c>
+      <c r="B10" s="8" t="inlineStr">
         <is>
           <t>F-OCC-02-01</t>
         </is>
       </c>
-      <c r="C10" s="6" t="inlineStr">
+      <c r="C10" s="8" t="inlineStr">
         <is>
           <t>目标关联关系建模</t>
         </is>
       </c>
-      <c r="D10" s="6" t="inlineStr">
+      <c r="D10" s="8" t="inlineStr">
         <is>
           <t>R-OCC-001</t>
         </is>
       </c>
-      <c r="E10" s="6" t="inlineStr">
+      <c r="E10" s="8" t="inlineStr">
         <is>
           <t>目标之间建立关联关系，形成目标关系网络。</t>
         </is>
       </c>
-      <c r="F10" s="6" t="inlineStr">
+      <c r="F10" s="8" t="inlineStr">
         <is>
           <t>关联关系建模；关系网络</t>
         </is>
       </c>
-      <c r="G10" s="6" t="inlineStr">
+      <c r="G10" s="8" t="inlineStr">
         <is>
           <t>SRS R-OCC-001</t>
         </is>
       </c>
-      <c r="H10" s="6" t="inlineStr"/>
+      <c r="H10" s="8" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="6" t="inlineStr">
-        <is>
-          <t>③功能</t>
-        </is>
-      </c>
-      <c r="B11" s="6" t="inlineStr">
+      <c r="A11" s="8" t="inlineStr">
+        <is>
+          <t>③功能</t>
+        </is>
+      </c>
+      <c r="B11" s="8" t="inlineStr">
         <is>
           <t>F-OCC-02-02</t>
         </is>
       </c>
-      <c r="C11" s="6" t="inlineStr">
+      <c r="C11" s="8" t="inlineStr">
         <is>
           <t>关系网络查询</t>
         </is>
       </c>
-      <c r="D11" s="6" t="inlineStr">
+      <c r="D11" s="8" t="inlineStr">
         <is>
           <t>R-OCC-001</t>
         </is>
       </c>
-      <c r="E11" s="6" t="inlineStr">
+      <c r="E11" s="8" t="inlineStr">
         <is>
           <t>支持对目标关系网络的查询与探索；目标关联断裂时标注断点。</t>
         </is>
       </c>
-      <c r="F11" s="6" t="inlineStr">
+      <c r="F11" s="8" t="inlineStr">
         <is>
           <t>关系网络查询；断点标注</t>
         </is>
       </c>
-      <c r="G11" s="6" t="inlineStr">
+      <c r="G11" s="8" t="inlineStr">
         <is>
           <t>SRS R-OCC-001</t>
         </is>
       </c>
-      <c r="H11" s="6" t="inlineStr"/>
-    </row>
-    <row r="12" ht="49.5" customHeight="1">
-      <c r="A12" s="4" t="inlineStr">
+      <c r="H11" s="8" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="11" t="inlineStr">
         <is>
           <t>②模块</t>
         </is>
       </c>
-      <c r="B12" s="4" t="inlineStr">
+      <c r="B12" s="11" t="inlineStr">
         <is>
           <t>M-OCC-03</t>
         </is>
       </c>
-      <c r="C12" s="5" t="inlineStr">
+      <c r="C12" s="11" t="inlineStr">
         <is>
           <t>作战方案规划（作战参谋）</t>
         </is>
       </c>
-      <c r="D12" s="4" t="inlineStr">
+      <c r="D12" s="11" t="inlineStr">
         <is>
           <t>R-OCC-002(决策)</t>
         </is>
       </c>
-      <c r="E12" s="5" t="inlineStr">
+      <c r="E12" s="11" t="inlineStr">
         <is>
           <t>根据目标档案中的干预切入点匹配干预策略，生成具体的作业方案（含内容/账号/时间/节奏）；本期以人工匹配为主。</t>
         </is>
       </c>
-      <c r="F12" s="5" t="inlineStr">
+      <c r="F12" s="11" t="inlineStr">
         <is>
           <t>F-OCC-03-01 干预策略匹配；F-OCC-03-02 作业方案生成</t>
         </is>
       </c>
-      <c r="G12" s="5" t="inlineStr">
+      <c r="G12" s="11" t="inlineStr">
         <is>
           <t>SRS R-OCC-002(决策)</t>
         </is>
       </c>
-      <c r="H12" s="5" t="inlineStr">
+      <c r="H12" s="11" t="inlineStr">
         <is>
           <t>R-OCC-002 的方案规划(业务决策域)与编排执行(工作流建模+运行域)是不同职责域，故拆。</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="6" t="inlineStr">
-        <is>
-          <t>③功能</t>
-        </is>
-      </c>
-      <c r="B13" s="7" t="inlineStr">
+      <c r="A13" s="8" t="inlineStr">
+        <is>
+          <t>③功能</t>
+        </is>
+      </c>
+      <c r="B13" s="8" t="inlineStr">
         <is>
           <t>F-OCC-03-01</t>
         </is>
       </c>
-      <c r="C13" s="6" t="inlineStr">
+      <c r="C13" s="8" t="inlineStr">
         <is>
           <t>干预策略匹配</t>
         </is>
       </c>
-      <c r="D13" s="6" t="inlineStr">
+      <c r="D13" s="8" t="inlineStr">
         <is>
           <t>R-OCC-002</t>
         </is>
       </c>
-      <c r="E13" s="6" t="inlineStr">
+      <c r="E13" s="8" t="inlineStr">
         <is>
           <t>根据目标档案中的干预切入点匹配干预策略(本期以人工匹配为主)。</t>
         </is>
       </c>
-      <c r="F13" s="6" t="inlineStr">
+      <c r="F13" s="8" t="inlineStr">
         <is>
           <t>切入点→策略匹配；本期人工为主</t>
         </is>
       </c>
-      <c r="G13" s="6" t="inlineStr">
+      <c r="G13" s="8" t="inlineStr">
         <is>
           <t>SRS R-OCC-002</t>
         </is>
       </c>
-      <c r="H13" s="6" t="inlineStr"/>
+      <c r="H13" s="8" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="6" t="inlineStr">
-        <is>
-          <t>③功能</t>
-        </is>
-      </c>
-      <c r="B14" s="7" t="inlineStr">
+      <c r="A14" s="8" t="inlineStr">
+        <is>
+          <t>③功能</t>
+        </is>
+      </c>
+      <c r="B14" s="8" t="inlineStr">
         <is>
           <t>F-OCC-03-02</t>
         </is>
       </c>
-      <c r="C14" s="6" t="inlineStr">
+      <c r="C14" s="8" t="inlineStr">
         <is>
           <t>作业方案生成</t>
         </is>
       </c>
-      <c r="D14" s="6" t="inlineStr">
+      <c r="D14" s="8" t="inlineStr">
         <is>
           <t>R-OCC-002</t>
         </is>
       </c>
-      <c r="E14" s="6" t="inlineStr">
+      <c r="E14" s="8" t="inlineStr">
         <is>
           <t>生成具体作业方案(含内容/账号/时间/节奏)。</t>
         </is>
       </c>
-      <c r="F14" s="6" t="inlineStr">
+      <c r="F14" s="8" t="inlineStr">
         <is>
           <t>内容/账号/时间/节奏方案</t>
         </is>
       </c>
-      <c r="G14" s="6" t="inlineStr">
+      <c r="G14" s="8" t="inlineStr">
         <is>
           <t>SRS R-OCC-002</t>
         </is>
       </c>
-      <c r="H14" s="6" t="inlineStr"/>
-    </row>
-    <row r="15" ht="66" customHeight="1">
-      <c r="A15" s="4" t="inlineStr">
+      <c r="H14" s="8" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="11" t="inlineStr">
         <is>
           <t>②模块</t>
         </is>
       </c>
-      <c r="B15" s="4" t="inlineStr">
+      <c r="B15" s="11" t="inlineStr">
         <is>
           <t>M-OCC-04</t>
         </is>
       </c>
-      <c r="C15" s="5" t="inlineStr">
+      <c r="C15" s="11" t="inlineStr">
         <is>
           <t>编排执行引擎（编排执行引擎）</t>
         </is>
       </c>
-      <c r="D15" s="4" t="inlineStr">
+      <c r="D15" s="11" t="inlineStr">
         <is>
           <t>R-OCC-002(建模+运行)</t>
         </is>
       </c>
-      <c r="E15" s="5" t="inlineStr">
+      <c r="E15" s="11" t="inlineStr">
         <is>
           <t>将作业方案编排为执行流程：以MC中智能体节点/自动化脚本节点为编排实体，按内容/账号/时间/节奏组织节点前后序/并行/分支关系形成可执行流程图；编排落地后由MC统一执行网关收口，节点失败按定义回滚/跳过/转人工。</t>
         </is>
       </c>
-      <c r="F15" s="5" t="inlineStr">
-        <is>
-          <t>F-OCC-04-01 执行流程编排；F-OCC-04-02 编排落地与执行跟踪</t>
-        </is>
-      </c>
-      <c r="G15" s="5" t="inlineStr">
+      <c r="F15" s="11" t="inlineStr">
+        <is>
+          <t>F-OCC-04-01 编排建模；F-OCC-04-02 节点参数填充；F-OCC-04-03 编排落地与执行跟踪</t>
+        </is>
+      </c>
+      <c r="G15" s="11" t="inlineStr">
         <is>
           <t>SRS R-OCC-002(建模+运行)</t>
         </is>
       </c>
-      <c r="H15" s="5" t="inlineStr">
+      <c r="H15" s="11" t="inlineStr">
         <is>
           <t>R-OCC-002 的流程编排(DAG建模)与执行调度(落地跟踪/回滚)紧耦合，合并为编排执行引擎。</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="49.5" customHeight="1">
-      <c r="A16" s="6" t="inlineStr">
-        <is>
-          <t>③功能</t>
-        </is>
-      </c>
-      <c r="B16" s="6" t="inlineStr">
+    <row r="16">
+      <c r="A16" s="8" t="inlineStr">
+        <is>
+          <t>③功能</t>
+        </is>
+      </c>
+      <c r="B16" s="8" t="inlineStr">
         <is>
           <t>F-OCC-04-01</t>
         </is>
       </c>
-      <c r="C16" s="6" t="inlineStr">
-        <is>
-          <t>执行流程编排</t>
-        </is>
-      </c>
-      <c r="D16" s="6" t="inlineStr">
+      <c r="C16" s="8" t="inlineStr">
+        <is>
+          <t>编排建模</t>
+        </is>
+      </c>
+      <c r="D16" s="8" t="inlineStr">
         <is>
           <t>R-OCC-002</t>
         </is>
       </c>
-      <c r="E16" s="6" t="inlineStr">
-        <is>
-          <t>将作业方案编排为执行流程：以MC中智能体节点/自动化脚本节点为编排实体，组织节点前后序/并行/分支关系形成可执行流程图；节点类型后续可扩充。</t>
-        </is>
-      </c>
-      <c r="F16" s="6" t="inlineStr">
-        <is>
-          <t>智能体节点+脚本节点编排为流程图；节点可扩充</t>
-        </is>
-      </c>
-      <c r="G16" s="6" t="inlineStr">
+      <c r="E16" s="8" t="inlineStr">
+        <is>
+          <t>将作业方案编排为执行流程图（DAG）：以 MC 中智能体节点/自动化脚本节点为编排实体，定义节点间的前后序、并行与分支关系；节点类型后续可扩充。</t>
+        </is>
+      </c>
+      <c r="F16" s="8" t="inlineStr">
+        <is>
+          <t>DAG流程图建模；智能体节点+脚本节点；前后序/并行/分支关系；节点类型可扩充</t>
+        </is>
+      </c>
+      <c r="G16" s="8" t="inlineStr">
         <is>
           <t>SRS R-OCC-002</t>
         </is>
       </c>
-      <c r="H16" s="6" t="inlineStr"/>
-    </row>
-    <row r="17" ht="33" customHeight="1">
-      <c r="A17" s="6" t="inlineStr">
-        <is>
-          <t>③功能</t>
-        </is>
-      </c>
-      <c r="B17" s="6" t="inlineStr">
+      <c r="H16" s="8" t="inlineStr">
+        <is>
+          <t>从原 F-OCC-04-01 拆出，聚焦流程图建模</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="8" t="inlineStr">
+        <is>
+          <t>③功能</t>
+        </is>
+      </c>
+      <c r="B17" s="8" t="inlineStr">
         <is>
           <t>F-OCC-04-02</t>
         </is>
       </c>
-      <c r="C17" s="6" t="inlineStr">
+      <c r="C17" s="8" t="inlineStr">
+        <is>
+          <t>节点参数填充</t>
+        </is>
+      </c>
+      <c r="D17" s="8" t="inlineStr">
+        <is>
+          <t>R-OCC-002</t>
+        </is>
+      </c>
+      <c r="E17" s="8" t="inlineStr">
+        <is>
+          <t>为编排流程图中的各节点填充具体执行参数：智能体节点的 agent_id 引用、脚本节点的通道与目标、内容/账号/时间/节奏等作业参数。</t>
+        </is>
+      </c>
+      <c r="F17" s="8" t="inlineStr">
+        <is>
+          <t>智能体节点agent_id引用；脚本节点通道与目标；内容/账号/时间/节奏参数填充</t>
+        </is>
+      </c>
+      <c r="G17" s="8" t="inlineStr">
+        <is>
+          <t>SRS R-OCC-002</t>
+        </is>
+      </c>
+      <c r="H17" s="8" t="inlineStr">
+        <is>
+          <t>从原 F-OCC-04-01 拆出，聚焦节点参数实例化</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="8" t="inlineStr">
+        <is>
+          <t>③功能</t>
+        </is>
+      </c>
+      <c r="B18" s="8" t="inlineStr">
+        <is>
+          <t>F-OCC-04-03</t>
+        </is>
+      </c>
+      <c r="C18" s="8" t="inlineStr">
         <is>
           <t>编排落地与执行跟踪</t>
         </is>
       </c>
-      <c r="D17" s="6" t="inlineStr">
+      <c r="D18" s="8" t="inlineStr">
         <is>
           <t>R-OCC-002</t>
         </is>
       </c>
-      <c r="E17" s="6" t="inlineStr">
+      <c r="E18" s="8" t="inlineStr">
         <is>
           <t>编排落地后由MC统一执行网关收口所有节点动作；节点执行失败时按编排定义回滚/跳过/转人工。</t>
         </is>
       </c>
-      <c r="F17" s="6" t="inlineStr">
+      <c r="F18" s="8" t="inlineStr">
         <is>
           <t>经MC执行网关落地；失败回滚/跳过/转人工</t>
         </is>
       </c>
-      <c r="G17" s="6" t="inlineStr">
+      <c r="G18" s="8" t="inlineStr">
         <is>
           <t>SRS R-OCC-002</t>
         </is>
       </c>
-      <c r="H17" s="6" t="inlineStr">
+      <c r="H18" s="8" t="inlineStr">
         <is>
           <t>对接 II-11</t>
         </is>
       </c>
     </row>
-    <row r="18" ht="49.5" customHeight="1">
-      <c r="A18" s="4" t="inlineStr">
+    <row r="19">
+      <c r="A19" s="11" t="inlineStr">
         <is>
           <t>②模块</t>
         </is>
       </c>
-      <c r="B18" s="4" t="inlineStr">
+      <c r="B19" s="11" t="inlineStr">
         <is>
           <t>M-OCC-05</t>
         </is>
       </c>
-      <c r="C18" s="5" t="inlineStr">
+      <c r="C19" s="11" t="inlineStr">
         <is>
           <t>效果评估（作战复盘官）</t>
         </is>
       </c>
-      <c r="D18" s="4" t="inlineStr">
+      <c r="D19" s="11" t="inlineStr">
         <is>
           <t>R-OCC-003</t>
         </is>
       </c>
-      <c r="E18" s="5" t="inlineStr">
+      <c r="E19" s="11" t="inlineStr">
         <is>
           <t>完成单轮干预成效统计、舆论走势修正、策略迭代反馈与作业复盘，支持中短期与长期效果评估；数据来源于DC采集分析结果与MC可观测性作业数据，不自行重复采集。</t>
         </is>
       </c>
-      <c r="F18" s="5" t="inlineStr">
+      <c r="F19" s="11" t="inlineStr">
         <is>
           <t>F-OCC-05-01 单轮成效统计；F-OCC-05-02 舆论走势修正评估；F-OCC-05-03 策略迭代反馈；F-OCC-05-04 作业复盘；F-OCC-05-05 中短期与长期效果评估</t>
         </is>
       </c>
-      <c r="G18" s="5" t="inlineStr">
+      <c r="G19" s="11" t="inlineStr">
         <is>
           <t>SRS R-OCC-003</t>
         </is>
       </c>
-      <c r="H18" s="5" t="inlineStr">
+      <c r="H19" s="11" t="inlineStr">
         <is>
           <t>对应 R-OCC-003，各评估维度同属评估分析能力域，内聚不拆。</t>
         </is>
       </c>
     </row>
-    <row r="19" ht="33" customHeight="1">
-      <c r="A19" s="6" t="inlineStr">
-        <is>
-          <t>③功能</t>
-        </is>
-      </c>
-      <c r="B19" s="7" t="inlineStr">
+    <row r="20">
+      <c r="A20" s="8" t="inlineStr">
+        <is>
+          <t>③功能</t>
+        </is>
+      </c>
+      <c r="B20" s="8" t="inlineStr">
         <is>
           <t>F-OCC-05-01</t>
         </is>
       </c>
-      <c r="C19" s="6" t="inlineStr">
+      <c r="C20" s="8" t="inlineStr">
         <is>
           <t>单轮成效统计</t>
         </is>
       </c>
-      <c r="D19" s="6" t="inlineStr">
+      <c r="D20" s="8" t="inlineStr">
         <is>
           <t>R-OCC-003</t>
         </is>
       </c>
-      <c r="E19" s="6" t="inlineStr">
+      <c r="E20" s="8" t="inlineStr">
         <is>
           <t>基于DC舆情数据与MC作业数据完成单轮干预成效统计(触达/互动/立场变化等)。</t>
         </is>
       </c>
-      <c r="F19" s="6" t="inlineStr">
+      <c r="F20" s="8" t="inlineStr">
         <is>
           <t>DC舆情+MC作业数据；成效统计</t>
         </is>
       </c>
-      <c r="G19" s="6" t="inlineStr">
+      <c r="G20" s="8" t="inlineStr">
         <is>
           <t>SRS R-OCC-003</t>
         </is>
       </c>
-      <c r="H19" s="6" t="inlineStr">
+      <c r="H20" s="8" t="inlineStr">
         <is>
           <t>数据来自 DC/MC</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="6" t="inlineStr">
-        <is>
-          <t>③功能</t>
-        </is>
-      </c>
-      <c r="B20" s="7" t="inlineStr">
+    <row r="21">
+      <c r="A21" s="8" t="inlineStr">
+        <is>
+          <t>③功能</t>
+        </is>
+      </c>
+      <c r="B21" s="8" t="inlineStr">
         <is>
           <t>F-OCC-05-02</t>
         </is>
       </c>
-      <c r="C20" s="6" t="inlineStr">
+      <c r="C21" s="8" t="inlineStr">
         <is>
           <t>舆论走势修正评估</t>
         </is>
       </c>
-      <c r="D20" s="6" t="inlineStr">
+      <c r="D21" s="8" t="inlineStr">
         <is>
           <t>R-OCC-003</t>
         </is>
       </c>
-      <c r="E20" s="6" t="inlineStr">
+      <c r="E21" s="8" t="inlineStr">
         <is>
           <t>基于DC前后舆情对比对舆论走势进行修正评估。</t>
         </is>
       </c>
-      <c r="F20" s="6" t="inlineStr">
+      <c r="F21" s="8" t="inlineStr">
         <is>
           <t>前后舆情对比；走势修正</t>
         </is>
       </c>
-      <c r="G20" s="6" t="inlineStr">
+      <c r="G21" s="8" t="inlineStr">
         <is>
           <t>SRS R-OCC-003</t>
         </is>
       </c>
-      <c r="H20" s="6" t="inlineStr"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="6" t="inlineStr">
-        <is>
-          <t>③功能</t>
-        </is>
-      </c>
-      <c r="B21" s="7" t="inlineStr">
+      <c r="H21" s="8" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="8" t="inlineStr">
+        <is>
+          <t>③功能</t>
+        </is>
+      </c>
+      <c r="B22" s="8" t="inlineStr">
         <is>
           <t>F-OCC-05-03</t>
         </is>
       </c>
-      <c r="C21" s="6" t="inlineStr">
+      <c r="C22" s="8" t="inlineStr">
         <is>
           <t>策略迭代反馈</t>
         </is>
       </c>
-      <c r="D21" s="6" t="inlineStr">
+      <c r="D22" s="8" t="inlineStr">
         <is>
           <t>R-OCC-003</t>
         </is>
       </c>
-      <c r="E21" s="6" t="inlineStr">
+      <c r="E22" s="8" t="inlineStr">
         <is>
           <t>将评估结果反馈至策略库以迭代优化。</t>
         </is>
       </c>
-      <c r="F21" s="6" t="inlineStr">
+      <c r="F22" s="8" t="inlineStr">
         <is>
           <t>评估反馈策略库迭代</t>
         </is>
       </c>
-      <c r="G21" s="6" t="inlineStr">
+      <c r="G22" s="8" t="inlineStr">
         <is>
           <t>SRS R-OCC-003</t>
         </is>
       </c>
-      <c r="H21" s="6" t="inlineStr"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="6" t="inlineStr">
-        <is>
-          <t>③功能</t>
-        </is>
-      </c>
-      <c r="B22" s="7" t="inlineStr">
+      <c r="H22" s="8" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="8" t="inlineStr">
+        <is>
+          <t>③功能</t>
+        </is>
+      </c>
+      <c r="B23" s="8" t="inlineStr">
         <is>
           <t>F-OCC-05-04</t>
         </is>
       </c>
-      <c r="C22" s="6" t="inlineStr">
+      <c r="C23" s="8" t="inlineStr">
         <is>
           <t>作业复盘</t>
         </is>
       </c>
-      <c r="D22" s="6" t="inlineStr">
+      <c r="D23" s="8" t="inlineStr">
         <is>
           <t>R-OCC-003</t>
         </is>
       </c>
-      <c r="E22" s="6" t="inlineStr">
+      <c r="E23" s="8" t="inlineStr">
         <is>
           <t>结合MC作业执行记录进行作业复盘总结经验。</t>
         </is>
       </c>
-      <c r="F22" s="6" t="inlineStr">
+      <c r="F23" s="8" t="inlineStr">
         <is>
           <t>MC作业记录复盘</t>
         </is>
       </c>
-      <c r="G22" s="6" t="inlineStr">
+      <c r="G23" s="8" t="inlineStr">
         <is>
           <t>SRS R-OCC-003</t>
         </is>
       </c>
-      <c r="H22" s="6" t="inlineStr"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="6" t="inlineStr">
-        <is>
-          <t>③功能</t>
-        </is>
-      </c>
-      <c r="B23" s="7" t="inlineStr">
+      <c r="H23" s="8" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="8" t="inlineStr">
+        <is>
+          <t>③功能</t>
+        </is>
+      </c>
+      <c r="B24" s="8" t="inlineStr">
         <is>
           <t>F-OCC-05-05</t>
         </is>
       </c>
-      <c r="C23" s="6" t="inlineStr">
+      <c r="C24" s="8" t="inlineStr">
         <is>
           <t>中短期与长期效果评估</t>
         </is>
       </c>
-      <c r="D23" s="6" t="inlineStr">
+      <c r="D24" s="8" t="inlineStr">
         <is>
           <t>R-OCC-003</t>
         </is>
       </c>
-      <c r="E23" s="6" t="inlineStr">
+      <c r="E24" s="8" t="inlineStr">
         <is>
           <t>提供中短期实网绩效评估与长期舆论塑造效果评估接口，实现效果联动。</t>
         </is>
       </c>
-      <c r="F23" s="6" t="inlineStr">
+      <c r="F24" s="8" t="inlineStr">
         <is>
           <t>中短期绩效+长期塑造效果评估接口</t>
         </is>
       </c>
-      <c r="G23" s="6" t="inlineStr">
+      <c r="G24" s="8" t="inlineStr">
         <is>
           <t>SRS R-OCC-003</t>
         </is>
       </c>
-      <c r="H23" s="6" t="inlineStr"/>
-    </row>
-    <row r="24" ht="49.5" customHeight="1">
-      <c r="A24" s="4" t="inlineStr">
+      <c r="H24" s="8" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="11" t="inlineStr">
         <is>
           <t>②模块</t>
         </is>
       </c>
-      <c r="B24" s="4" t="inlineStr">
+      <c r="B25" s="11" t="inlineStr">
         <is>
           <t>M-OCC-06</t>
         </is>
       </c>
-      <c r="C24" s="5" t="inlineStr">
+      <c r="C25" s="11" t="inlineStr">
         <is>
           <t>舆论作业策略库（策略资产库）</t>
         </is>
       </c>
-      <c r="D24" s="4" t="inlineStr">
+      <c r="D25" s="11" t="inlineStr">
         <is>
           <t>R-OCC-004</t>
         </is>
       </c>
-      <c r="E24" s="5" t="inlineStr">
+      <c r="E25" s="11" t="inlineStr">
         <is>
           <t>搭建并迭代多语种/多场景/多风格舆论作业策略库，为作战提供可复用、可演进的策略资产。</t>
         </is>
       </c>
-      <c r="F24" s="5" t="inlineStr">
+      <c r="F25" s="11" t="inlineStr">
         <is>
           <t>F-OCC-06-01 多语种多场景多风格策略库；F-OCC-06-02 策略分类管理与版本控制；F-OCC-06-03 策略迭代优化；F-OCC-06-04 策略场景适配与动态调用</t>
         </is>
       </c>
-      <c r="G24" s="5" t="inlineStr">
+      <c r="G25" s="11" t="inlineStr">
         <is>
           <t>SRS R-OCC-004</t>
         </is>
       </c>
-      <c r="H24" s="5" t="inlineStr">
+      <c r="H25" s="11" t="inlineStr">
         <is>
           <t>对应 R-OCC-004，单一策略资产的治理(组织/版本/迭代/适配)内聚不拆。</t>
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="6" t="inlineStr">
-        <is>
-          <t>③功能</t>
-        </is>
-      </c>
-      <c r="B25" s="7" t="inlineStr">
+    <row r="26">
+      <c r="A26" s="8" t="inlineStr">
+        <is>
+          <t>③功能</t>
+        </is>
+      </c>
+      <c r="B26" s="8" t="inlineStr">
         <is>
           <t>F-OCC-06-01</t>
         </is>
       </c>
-      <c r="C25" s="6" t="inlineStr">
+      <c r="C26" s="8" t="inlineStr">
         <is>
           <t>多语种多场景多风格策略库</t>
         </is>
       </c>
-      <c r="D25" s="6" t="inlineStr">
+      <c r="D26" s="8" t="inlineStr">
         <is>
           <t>R-OCC-004</t>
         </is>
       </c>
-      <c r="E25" s="6" t="inlineStr">
+      <c r="E26" s="8" t="inlineStr">
         <is>
           <t>按多语种/多场景/多风格组织舆论作业策略库。</t>
         </is>
       </c>
-      <c r="F25" s="6" t="inlineStr">
+      <c r="F26" s="8" t="inlineStr">
         <is>
           <t>多语种/多场景/多风格</t>
         </is>
       </c>
-      <c r="G25" s="6" t="inlineStr">
+      <c r="G26" s="8" t="inlineStr">
         <is>
           <t>SRS R-OCC-004</t>
         </is>
       </c>
-      <c r="H25" s="6" t="inlineStr"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="6" t="inlineStr">
-        <is>
-          <t>③功能</t>
-        </is>
-      </c>
-      <c r="B26" s="7" t="inlineStr">
+      <c r="H26" s="8" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="8" t="inlineStr">
+        <is>
+          <t>③功能</t>
+        </is>
+      </c>
+      <c r="B27" s="8" t="inlineStr">
         <is>
           <t>F-OCC-06-02</t>
         </is>
       </c>
-      <c r="C26" s="6" t="inlineStr">
+      <c r="C27" s="8" t="inlineStr">
         <is>
           <t>策略分类管理与版本控制</t>
         </is>
       </c>
-      <c r="D26" s="6" t="inlineStr">
+      <c r="D27" s="8" t="inlineStr">
         <is>
           <t>R-OCC-004</t>
         </is>
       </c>
-      <c r="E26" s="6" t="inlineStr">
+      <c r="E27" s="8" t="inlineStr">
         <is>
           <t>对策略进行分类管理与版本控制。</t>
         </is>
       </c>
-      <c r="F26" s="6" t="inlineStr">
+      <c r="F27" s="8" t="inlineStr">
         <is>
           <t>分类管理；版本控制</t>
         </is>
       </c>
-      <c r="G26" s="6" t="inlineStr">
+      <c r="G27" s="8" t="inlineStr">
         <is>
           <t>SRS R-OCC-004</t>
         </is>
       </c>
-      <c r="H26" s="6" t="inlineStr"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="6" t="inlineStr">
-        <is>
-          <t>③功能</t>
-        </is>
-      </c>
-      <c r="B27" s="7" t="inlineStr">
+      <c r="H27" s="8" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="8" t="inlineStr">
+        <is>
+          <t>③功能</t>
+        </is>
+      </c>
+      <c r="B28" s="8" t="inlineStr">
         <is>
           <t>F-OCC-06-03</t>
         </is>
       </c>
-      <c r="C27" s="6" t="inlineStr">
+      <c r="C28" s="8" t="inlineStr">
         <is>
           <t>策略迭代优化</t>
         </is>
       </c>
-      <c r="D27" s="6" t="inlineStr">
+      <c r="D28" s="8" t="inlineStr">
         <is>
           <t>R-OCC-004</t>
         </is>
       </c>
-      <c r="E27" s="6" t="inlineStr">
+      <c r="E28" s="8" t="inlineStr">
         <is>
           <t>根据作业效果反馈对策略进行迭代优化。</t>
         </is>
       </c>
-      <c r="F27" s="6" t="inlineStr">
+      <c r="F28" s="8" t="inlineStr">
         <is>
           <t>效果反馈迭代优化</t>
         </is>
       </c>
-      <c r="G27" s="6" t="inlineStr">
+      <c r="G28" s="8" t="inlineStr">
         <is>
           <t>SRS R-OCC-004</t>
         </is>
       </c>
-      <c r="H27" s="6" t="inlineStr"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="6" t="inlineStr">
-        <is>
-          <t>③功能</t>
-        </is>
-      </c>
-      <c r="B28" s="7" t="inlineStr">
+      <c r="H28" s="8" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="8" t="inlineStr">
+        <is>
+          <t>③功能</t>
+        </is>
+      </c>
+      <c r="B29" s="8" t="inlineStr">
         <is>
           <t>F-OCC-06-04</t>
         </is>
       </c>
-      <c r="C28" s="6" t="inlineStr">
+      <c r="C29" s="8" t="inlineStr">
         <is>
           <t>策略场景适配与动态调用</t>
         </is>
       </c>
-      <c r="D28" s="6" t="inlineStr">
+      <c r="D29" s="8" t="inlineStr">
         <is>
           <t>R-OCC-004</t>
         </is>
       </c>
-      <c r="E28" s="6" t="inlineStr">
+      <c r="E29" s="8" t="inlineStr">
         <is>
           <t>支持策略的场景适配与动态调用。</t>
         </is>
       </c>
-      <c r="F28" s="6" t="inlineStr">
+      <c r="F29" s="8" t="inlineStr">
         <is>
           <t>场景适配；动态调用</t>
         </is>
       </c>
-      <c r="G28" s="6" t="inlineStr">
+      <c r="G29" s="8" t="inlineStr">
         <is>
           <t>SRS R-OCC-004</t>
         </is>
       </c>
-      <c r="H28" s="6" t="inlineStr"/>
-    </row>
-    <row r="29" ht="82.5" customHeight="1">
-      <c r="A29" s="4" t="inlineStr">
+      <c r="H29" s="8" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="11" t="inlineStr">
         <is>
           <t>②模块</t>
         </is>
       </c>
-      <c r="B29" s="4" t="inlineStr">
+      <c r="B30" s="11" t="inlineStr">
         <is>
           <t>M-OCC-07</t>
         </is>
       </c>
-      <c r="C29" s="5" t="inlineStr">
+      <c r="C30" s="11" t="inlineStr">
         <is>
           <t>内容主数据与排期（权威源）（内容资源权威源）</t>
         </is>
       </c>
-      <c r="D29" s="4" t="inlineStr">
+      <c r="D30" s="11" t="inlineStr">
         <is>
           <t>R-OCC-005(资产+调度)</t>
         </is>
       </c>
-      <c r="E29" s="5" t="inlineStr">
+      <c r="E30" s="11" t="inlineStr">
         <is>
           <t>唯一维护内容主数据(原始素材/分类/审核状态/来源)，content_id全局唯一引用；管理素材分类与平台适配；按素材/账号/时间制定发布排期；向各使用方主动分发content_id。</t>
         </is>
       </c>
-      <c r="F29" s="5" t="inlineStr">
+      <c r="F30" s="11" t="inlineStr">
         <is>
           <t>F-OCC-07-01 内容主数据维护；F-OCC-07-02 素材分类与平台适配；F-OCC-07-03 发布排期；F-OCC-07-04 内容变更事件与分发</t>
         </is>
       </c>
-      <c r="G29" s="5" t="inlineStr">
+      <c r="G30" s="11" t="inlineStr">
         <is>
           <t>SRS R-OCC-005(资产+调度)</t>
         </is>
       </c>
-      <c r="H29" s="5" t="inlineStr">
+      <c r="H30" s="11" t="inlineStr">
         <is>
           <t>R-OCC-005 的内容主数据(CMS资产域)与审核风控(合规域)是异构关注点，故拆；排期是主数据的时间调度，归入主数据管理。</t>
         </is>
       </c>
     </row>
-    <row r="30" ht="33" customHeight="1">
-      <c r="A30" s="6" t="inlineStr">
-        <is>
-          <t>③功能</t>
-        </is>
-      </c>
-      <c r="B30" s="6" t="inlineStr">
+    <row r="31">
+      <c r="A31" s="8" t="inlineStr">
+        <is>
+          <t>③功能</t>
+        </is>
+      </c>
+      <c r="B31" s="8" t="inlineStr">
         <is>
           <t>F-OCC-07-01</t>
         </is>
       </c>
-      <c r="C30" s="6" t="inlineStr">
+      <c r="C31" s="8" t="inlineStr">
         <is>
           <t>内容主数据维护</t>
         </is>
       </c>
-      <c r="D30" s="6" t="inlineStr">
+      <c r="D31" s="8" t="inlineStr">
         <is>
           <t>R-OCC-005</t>
         </is>
       </c>
-      <c r="E30" s="6" t="inlineStr">
-        <is>
-          <t>唯一维护内容主数据(原始素材/分类/审核状态/来源)；content_id为全局唯一引用，使用方不复制主数据。</t>
-        </is>
-      </c>
-      <c r="F30" s="6" t="inlineStr">
-        <is>
-          <t>主数据唯一维护；content_id全局唯一；使用方不复制</t>
-        </is>
-      </c>
-      <c r="G30" s="6" t="inlineStr">
+      <c r="E31" s="8" t="inlineStr">
+        <is>
+          <t>唯一维护内容主数据（原始素材、分类、审核状态、来源）的 CRUD；content_id 为全局唯一引用，使用方不复制主数据。聚焦主数据的新增/修改/删除/查询，权威源分发约束见 F-OCC-07-04。</t>
+        </is>
+      </c>
+      <c r="F31" s="8" t="inlineStr">
+        <is>
+          <t>主数据CRUD；content_id全局唯一；使用方不复制主数据；凭据加密</t>
+        </is>
+      </c>
+      <c r="G31" s="8" t="inlineStr">
         <is>
           <t>SRS R-OCC-005</t>
         </is>
       </c>
-      <c r="H30" s="6" t="inlineStr">
-        <is>
-          <t>权威源；对接 II-13</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="6" t="inlineStr">
-        <is>
-          <t>③功能</t>
-        </is>
-      </c>
-      <c r="B31" s="6" t="inlineStr">
+      <c r="H31" s="8" t="inlineStr">
+        <is>
+          <t>权威源主数据CRUD；分发约束归 F-OCC-07-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="8" t="inlineStr">
+        <is>
+          <t>③功能</t>
+        </is>
+      </c>
+      <c r="B32" s="8" t="inlineStr">
         <is>
           <t>F-OCC-07-02</t>
         </is>
       </c>
-      <c r="C31" s="6" t="inlineStr">
+      <c r="C32" s="8" t="inlineStr">
         <is>
           <t>素材分类与平台适配</t>
         </is>
       </c>
-      <c r="D31" s="6" t="inlineStr">
+      <c r="D32" s="8" t="inlineStr">
         <is>
           <t>R-OCC-005</t>
         </is>
       </c>
-      <c r="E31" s="6" t="inlineStr">
+      <c r="E32" s="8" t="inlineStr">
         <is>
           <t>对素材分类管理，支持标签/平台分类与账号适配。</t>
         </is>
       </c>
-      <c r="F31" s="6" t="inlineStr">
+      <c r="F32" s="8" t="inlineStr">
         <is>
           <t>素材分类；标签/平台分类/账号适配</t>
         </is>
       </c>
-      <c r="G31" s="6" t="inlineStr">
+      <c r="G32" s="8" t="inlineStr">
         <is>
           <t>SRS R-OCC-005</t>
         </is>
       </c>
-      <c r="H31" s="6" t="inlineStr"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="6" t="inlineStr">
-        <is>
-          <t>③功能</t>
-        </is>
-      </c>
-      <c r="B32" s="6" t="inlineStr">
+      <c r="H32" s="8" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="8" t="inlineStr">
+        <is>
+          <t>③功能</t>
+        </is>
+      </c>
+      <c r="B33" s="8" t="inlineStr">
         <is>
           <t>F-OCC-07-03</t>
         </is>
       </c>
-      <c r="C32" s="6" t="inlineStr">
+      <c r="C33" s="8" t="inlineStr">
         <is>
           <t>发布排期</t>
         </is>
       </c>
-      <c r="D32" s="6" t="inlineStr">
+      <c r="D33" s="8" t="inlineStr">
         <is>
           <t>R-OCC-005</t>
         </is>
       </c>
-      <c r="E32" s="6" t="inlineStr">
+      <c r="E33" s="8" t="inlineStr">
         <is>
           <t>支持按素材/账号/时间制定定时发布排期；排期冲突时提示调整。</t>
         </is>
       </c>
-      <c r="F32" s="6" t="inlineStr">
+      <c r="F33" s="8" t="inlineStr">
         <is>
           <t>定时发布排期；冲突提示</t>
         </is>
       </c>
-      <c r="G32" s="6" t="inlineStr">
+      <c r="G33" s="8" t="inlineStr">
         <is>
           <t>SRS R-OCC-005</t>
         </is>
       </c>
-      <c r="H32" s="6" t="inlineStr"/>
-    </row>
-    <row r="33" ht="33" customHeight="1">
-      <c r="A33" s="6" t="inlineStr">
-        <is>
-          <t>③功能</t>
-        </is>
-      </c>
-      <c r="B33" s="6" t="inlineStr">
+      <c r="H33" s="8" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="8" t="inlineStr">
+        <is>
+          <t>③功能</t>
+        </is>
+      </c>
+      <c r="B34" s="8" t="inlineStr">
         <is>
           <t>F-OCC-07-04</t>
         </is>
       </c>
-      <c r="C33" s="6" t="inlineStr">
+      <c r="C34" s="8" t="inlineStr">
         <is>
           <t>内容变更事件与分发</t>
         </is>
       </c>
-      <c r="D33" s="6" t="inlineStr">
+      <c r="D34" s="8" t="inlineStr">
         <is>
           <t>R-OCC-005</t>
         </is>
       </c>
-      <c r="E33" s="6" t="inlineStr">
+      <c r="E34" s="8" t="inlineStr">
         <is>
           <t>内容新增或状态变更经事件总线广播content.changed事件，使用方订阅响应；作为权威源向使用方主动分发content_id。</t>
         </is>
       </c>
-      <c r="F33" s="6" t="inlineStr">
+      <c r="F34" s="8" t="inlineStr">
         <is>
           <t>content.changed事件广播；主动分发content_id</t>
         </is>
       </c>
-      <c r="G33" s="6" t="inlineStr">
+      <c r="G34" s="8" t="inlineStr">
         <is>
           <t>SRS R-OCC-005</t>
         </is>
       </c>
-      <c r="H33" s="6" t="inlineStr">
+      <c r="H34" s="8" t="inlineStr">
         <is>
           <t>对接 II-13a</t>
         </is>
       </c>
     </row>
-    <row r="34" ht="66" customHeight="1">
-      <c r="A34" s="4" t="inlineStr">
+    <row r="35">
+      <c r="A35" s="11" t="inlineStr">
         <is>
           <t>②模块</t>
         </is>
       </c>
-      <c r="B34" s="4" t="inlineStr">
+      <c r="B35" s="11" t="inlineStr">
         <is>
           <t>M-OCC-08</t>
         </is>
       </c>
-      <c r="C34" s="5" t="inlineStr">
+      <c r="C35" s="11" t="inlineStr">
         <is>
           <t>内容审核与敏感词风控（内容合规守门人）</t>
         </is>
       </c>
-      <c r="D34" s="4" t="inlineStr">
+      <c r="D35" s="11" t="inlineStr">
         <is>
           <t>R-OCC-005(合规)</t>
         </is>
       </c>
-      <c r="E34" s="5" t="inlineStr">
+      <c r="E35" s="11" t="inlineStr">
         <is>
           <t>发布前对内容进行审核与敏感词检测；敏感词命中拦截并标记待人工复核；素材上传失败时支持断点续传。</t>
         </is>
       </c>
-      <c r="F34" s="5" t="inlineStr">
+      <c r="F35" s="11" t="inlineStr">
         <is>
           <t>F-OCC-08-01 发布前内容审核；F-OCC-08-02 敏感词检测与拦截</t>
         </is>
       </c>
-      <c r="G34" s="5" t="inlineStr">
+      <c r="G35" s="11" t="inlineStr">
         <is>
           <t>SRS R-OCC-005(合规)</t>
         </is>
       </c>
-      <c r="H34" s="5" t="inlineStr">
+      <c r="H35" s="11" t="inlineStr">
         <is>
           <t>R-OCC-005 的审核与敏感词检测是合规风控域(敏感词库+拦截策略)，与主数据CRUD异构，故拆。</t>
         </is>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="6" t="inlineStr">
-        <is>
-          <t>③功能</t>
-        </is>
-      </c>
-      <c r="B35" s="6" t="inlineStr">
+    <row r="36">
+      <c r="A36" s="8" t="inlineStr">
+        <is>
+          <t>③功能</t>
+        </is>
+      </c>
+      <c r="B36" s="8" t="inlineStr">
         <is>
           <t>F-OCC-08-01</t>
         </is>
       </c>
-      <c r="C35" s="6" t="inlineStr">
+      <c r="C36" s="8" t="inlineStr">
         <is>
           <t>发布前内容审核</t>
         </is>
       </c>
-      <c r="D35" s="6" t="inlineStr">
+      <c r="D36" s="8" t="inlineStr">
         <is>
           <t>R-OCC-005</t>
         </is>
       </c>
-      <c r="E35" s="6" t="inlineStr">
+      <c r="E36" s="8" t="inlineStr">
         <is>
           <t>发布前对内容进行审核。</t>
         </is>
       </c>
-      <c r="F35" s="6" t="inlineStr">
+      <c r="F36" s="8" t="inlineStr">
         <is>
           <t>发布前审核</t>
         </is>
       </c>
-      <c r="G35" s="6" t="inlineStr">
+      <c r="G36" s="8" t="inlineStr">
         <is>
           <t>SRS R-OCC-005</t>
         </is>
       </c>
-      <c r="H35" s="6" t="inlineStr"/>
-    </row>
-    <row r="36">
-      <c r="A36" s="6" t="inlineStr">
-        <is>
-          <t>③功能</t>
-        </is>
-      </c>
-      <c r="B36" s="6" t="inlineStr">
+      <c r="H36" s="8" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="8" t="inlineStr">
+        <is>
+          <t>③功能</t>
+        </is>
+      </c>
+      <c r="B37" s="8" t="inlineStr">
         <is>
           <t>F-OCC-08-02</t>
         </is>
       </c>
-      <c r="C36" s="6" t="inlineStr">
+      <c r="C37" s="8" t="inlineStr">
         <is>
           <t>敏感词检测与拦截</t>
         </is>
       </c>
-      <c r="D36" s="6" t="inlineStr">
+      <c r="D37" s="8" t="inlineStr">
         <is>
           <t>R-OCC-005</t>
         </is>
       </c>
-      <c r="E36" s="6" t="inlineStr">
+      <c r="E37" s="8" t="inlineStr">
         <is>
           <t>对内容进行敏感词检测；敏感词命中时拦截并标记待人工复核。</t>
         </is>
       </c>
-      <c r="F36" s="6" t="inlineStr">
+      <c r="F37" s="8" t="inlineStr">
         <is>
           <t>敏感词检测；命中拦截待复核</t>
         </is>
       </c>
-      <c r="G36" s="6" t="inlineStr">
+      <c r="G37" s="8" t="inlineStr">
         <is>
           <t>SRS R-OCC-005</t>
         </is>
       </c>
-      <c r="H36" s="6" t="inlineStr"/>
+      <c r="H37" s="8" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/公司项目/认知作战/文档/软件概要设计-模块功能拆分.xlsx
+++ b/公司项目/认知作战/文档/软件概要设计-模块功能拆分.xlsx
@@ -4114,7 +4114,7 @@
       </c>
       <c r="C5" s="8" t="inlineStr">
         <is>
-          <t>浏览器 Profile 创建与 CDP 接入</t>
+          <t>浏览器 Profile 创建与 API 接入</t>
         </is>
       </c>
       <c r="D5" s="8" t="inlineStr">
@@ -4124,12 +4124,12 @@
       </c>
       <c r="E5" s="8" t="inlineStr">
         <is>
-          <t>基于开源 BotBrowser 定制内核创建浏览器 Profile，经 CDP 向服务端注册，记录 Profile 标识、Chromium 内核版本、分组与标签。</t>
+          <t>经商用指纹浏览器 API 创建浏览器 Profile（下发指纹模板、代理、分组、标签），商用产品返回 Profile 标识与调试端口；记录 Profile 标识、内核版本、调试端口、分组与标签。</t>
         </is>
       </c>
       <c r="F5" s="8" t="inlineStr">
         <is>
-          <t>Profile 创建；CDP 注册；分组与标签管理</t>
+          <t>调用商用API创建Profile；指纹模板/代理下发；返回调试端口(CDP)；记录Profile台账</t>
         </is>
       </c>
       <c r="G5" s="8" t="inlineStr">
@@ -4137,7 +4137,11 @@
           <t>SRS R-MC-001；CON-12</t>
         </is>
       </c>
-      <c r="H5" s="8" t="n"/>
+      <c r="H5" s="8" t="inlineStr">
+        <is>
+          <t>对接 EI-07 指纹浏览器服务接口</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="8" t="inlineStr">
@@ -4274,7 +4278,7 @@
       </c>
       <c r="C9" s="8" t="inlineStr">
         <is>
-          <t>浏览器 Profile 指纹固化</t>
+          <t>浏览器 Profile 指纹固化（经商用API）</t>
         </is>
       </c>
       <c r="D9" s="8" t="inlineStr">
@@ -4284,12 +4288,12 @@
       </c>
       <c r="E9" s="8" t="inlineStr">
         <is>
-          <t>Profile 创建时生成并固化 20+ 维渲染层指纹(Canvas/WebGL/字体/时区/Audio/UA)，使 Profile 长期呈现一致的设备身份；一Profile对应一套固化指纹与一账号身份。</t>
+          <t>经商用指纹浏览器 API 配置 Profile 指纹模板（Canvas/WebGL/字体/时区/Audio/UA 等 20+ 维），由商用产品生成并固化指纹，使 Profile 长期呈现一致的设备身份；一Profile对应一套固化指纹与一账号身份。</t>
         </is>
       </c>
       <c r="F9" s="8" t="inlineStr">
         <is>
-          <t>20+维指纹固化；指纹长期一致；一Profile一身份</t>
+          <t>20+维指纹模板经API下发；商用产品生成固化；指纹长期一致；一Profile一身份</t>
         </is>
       </c>
       <c r="G9" s="8" t="inlineStr">
@@ -4297,7 +4301,11 @@
           <t>SRS R-MC-001；CON-12</t>
         </is>
       </c>
-      <c r="H9" s="8" t="n"/>
+      <c r="H9" s="8" t="inlineStr">
+        <is>
+          <t>指纹生成与固化由商用产品负责</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="8" t="inlineStr">
@@ -4596,7 +4604,7 @@
       </c>
       <c r="E17" s="11" t="inlineStr">
         <is>
-          <t>对单台及多台终端提供低延迟实时画面预览与输入控制，支持多终端同屏监控；移动端用 WebRTC、桌面端浏览器 Profile 用 RDP。</t>
+          <t>对单台及多台终端提供低延迟实时画面预览与输入控制，支持多终端同屏监控；移动端用 WebRTC、桌面端指纹浏览器 Profile 用商用 API 画面预览。</t>
         </is>
       </c>
       <c r="F17" s="11" t="inlineStr">
@@ -4670,7 +4678,7 @@
       </c>
       <c r="C19" s="8" t="inlineStr">
         <is>
-          <t>桌面端 RDP 远控</t>
+          <t>桌面端商用 API 画面远控</t>
         </is>
       </c>
       <c r="D19" s="8" t="inlineStr">
@@ -4680,12 +4688,12 @@
       </c>
       <c r="E19" s="8" t="inlineStr">
         <is>
-          <t>桌面端浏览器 Profile 基于 RDP 传输画面，鼠标点击与键盘输入映射为桌面事件；远控通道与任务执行通道相互分离。</t>
+          <t>桌面端指纹浏览器 Profile 经商用产品 API 获取页面/窗口画面预览流；鼠标点击与键盘输入经 CDP 注入为页面事件；远控通道与任务执行通道相互分离。</t>
         </is>
       </c>
       <c r="F19" s="8" t="inlineStr">
         <is>
-          <t>RDP画面传输；鼠标键盘映射；远控与执行通道分离</t>
+          <t>商用API画面预览流；CDP注入页面事件；远控与执行通道分离</t>
         </is>
       </c>
       <c r="G19" s="8" t="inlineStr">
@@ -4693,7 +4701,11 @@
           <t>SRS R-MC-002</t>
         </is>
       </c>
-      <c r="H19" s="8" t="n"/>
+      <c r="H19" s="8" t="inlineStr">
+        <is>
+          <t>对接 EI-07；替代原 RDP 方案</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="8" t="inlineStr">
@@ -4916,12 +4928,12 @@
       </c>
       <c r="E25" s="8" t="inlineStr">
         <is>
-          <t>两种模式按终端类型适配底层控制通道：移动端用 ADB/无障碍，桌面端浏览器Profile用 CDP；通道对上层透明。</t>
+          <t>两种模式按终端类型适配底层控制通道：移动端用 ADB/无障碍，桌面端浏览器Profile启动后用 CDP（经商用产品返回的调试端口）；通道对上层透明。</t>
         </is>
       </c>
       <c r="F25" s="8" t="inlineStr">
         <is>
-          <t>移动端ADB/无障碍；桌面端CDP；对上层透明</t>
+          <t>移动端ADB/无障碍；桌面端CDP(商用产品调试端口)；对上层透明</t>
         </is>
       </c>
       <c r="G25" s="8" t="inlineStr">
@@ -4929,7 +4941,7 @@
           <t>SRS R-MC-003</t>
         </is>
       </c>
-      <c r="H25" s="8" t="n"/>
+      <c r="H25" s="8" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="8" t="inlineStr">
